--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links. ACCESS ROUTE (re-checked 2026-08-01): browser-UA curl from Dave's machine reaches the page (HTTP 200, 47KB of static HTML) while server-side WebFetch was refused 403 and the scanner's plain/Playwright fetches were connection-reset -- so retry with a browser User-Agent rather than treating a reset or a 403 as a dead URL. Re-verified 2026-09-05: WebFetch 403 once more while browser-UA curl got a clean 200 (47KB) listing board-paper-30th-july-2026 and forward dates into Nov 2026 - the browser-UA static route remains the reliable one, so keep treating a 403 or reset as a path problem rather than a dead URL.</t>
+          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links. ACCESS ROUTE (re-checked 2026-08-01): browser-UA curl from Dave's machine reaches the page (HTTP 200, 47KB of static HTML) while server-side WebFetch was refused 403 and the scanner's plain/Playwright fetches were connection-reset -- so retry with a browser User-Agent rather than treating a reset or a 403 as a dead URL. Re-verified 2026-09-05: WebFetch 403 once more while browser-UA curl got a clean 200 (47KB) listing board-paper-30th-july-2026 and forward dates into Nov 2026 - the browser-UA static route remains the reliable one, so keep treating a 403 or reset as a path problem rather than a dead URL. Re-verified 2026-09-12: the reset is intermittent, not persistent - the first browser-UA curl was connection-reset and a straight retry got HTTP 200 (47KB) with /documents/512-board-paper-30th-july-2026 still the newest pack and scheduled dates running to January 2028, so retry once before treating a reset as a dead URL.</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-05: server-side WebFetch was refused 403 again, but browser-UA curl returned HTTP 200 (47KB) with the archive intact - newest link /documents/512-board-paper-30th-july-2026 plus scheduled Sept and Nov 2026 dates.</t>
+          <t>2026-09-12: the first browser-UA curl was connection-reset and an immediate retry returned HTTP 200 (47KB) with the archive intact - newest pack /documents/512-board-paper-30th-july-2026, forward meeting dates listed to January 2028.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The live landing /about-us/board-of-directors/meetings-in-public/ lists one entry per meeting ('Meeting papers: &lt;date&gt;') as sub-pages, newest first, spanning 2025 and 2026 in a single flat list (no per-year archives). Each sub-page links to the single combined public board pack PDF. Packs also live at a predictable direct path www.qvh.nhs.uk/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;...&gt;.pdf, so a crawler can grab those directly. WebFetch renders the full meeting list statically, so Playwright is not required; prefer the one large combined 'Papers-PUBLIC-Board' PDF per meeting and skip individual annexes.</t>
+          <t>The live landing /about-us/board-of-directors/meetings-in-public/ lists one entry per meeting ('Meeting papers: &lt;date&gt;') as sub-pages, newest first, spanning 2025 and 2026 in a single flat list (no per-year archives). Each sub-page links to the single combined public board pack PDF. Packs also live at a predictable direct path www.qvh.nhs.uk/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;...&gt;.pdf, so a crawler can grab those directly. WebFetch renders the full meeting list statically, so Playwright is not required; prefer the one large combined 'Papers-PUBLIC-Board' PDF per meeting and skip individual annexes. Re-verified 2026-09-12 by browser-UA curl (200, 99KB): meeting sub-pages still listed newest-first, latest held 23 July 2026 with dates scheduled into March 2027.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; papers and minutes offered through date dropdowns covering 2014-2026, newest 23 July 2026.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (99KB); the flat meeting list is intact with 23 July 2026 the newest held meeting and 16 September 2026, 12 November 2026, 21 January 2027 and 11 March 2027 scheduled ahead.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
+          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 841-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The human landing www.uhb.nhs.uk/about/trust-management/bod/papers/ links to the Nextcloud public share at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. The share is JS-rendered (static fetch shows 'No files in here' -- the no_papers_visible false-negative), so Playwright is required. Navigate via ?path= query params: root lists year folders (2008-2026); each year has month folders; each month contains 'Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf' plus sometimes a '(background reading)' variant. Direct deep-links work, e.g. ?path=%2F2026%2FJune. PDFs download via /download?path=...&amp;files=... . NON-BROWSER ROUTE FOUND 2026-09-05: the share no longer requires Playwright to enumerate. Nextcloud exposes the public share over WebDAV - PROPFIND https://docs.uhb.nhs.uk/public.php/webdav/ with HTTP basic auth of username = the share token (prTEizKrRnYnjaD) and an EMPTY password, header 'Depth: 1', returns 207 Multi-Status listing the year folders; repeat against /public.php/webdav/2026/ for month folders and /public.php/webdav/2026/July/ for the files. Confirmed this run: years 2019-2026, 2026 holding January/March/June/July, and 'Board of Directors meeting pack, July 2026.pdf' alongside its '(background reading)' variant. Download the file itself with the same basic-auth credentials at that WebDAV path. The HTML share page is still a JS shell (?path= query params return the same 30KB SPA skeleton), so use WebDAV first and keep Playwright only as fallback.</t>
+          <t>The human landing www.uhb.nhs.uk/about/trust-management/bod/papers/ links to the Nextcloud public share at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. The share is JS-rendered (static fetch shows 'No files in here' -- the no_papers_visible false-negative), so Playwright is required. Navigate via ?path= query params: root lists year folders (2008-2026); each year has month folders; each month contains 'Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf' plus sometimes a '(background reading)' variant. Direct deep-links work, e.g. ?path=%2F2026%2FJune. PDFs download via /download?path=...&amp;files=... . NON-BROWSER ROUTE FOUND 2026-09-05: the share no longer requires Playwright to enumerate. Nextcloud exposes the public share over WebDAV - PROPFIND https://docs.uhb.nhs.uk/public.php/webdav/ with HTTP basic auth of username = the share token (prTEizKrRnYnjaD) and an EMPTY password, header 'Depth: 1', returns 207 Multi-Status listing the year folders; repeat against /public.php/webdav/2026/ for month folders and /public.php/webdav/2026/July/ for the files. Confirmed this run: years 2019-2026, 2026 holding January/March/June/July, and 'Board of Directors meeting pack, July 2026.pdf' alongside its '(background reading)' variant. Download the file itself with the same basic-auth credentials at that WebDAV path. The HTML share page is still a JS shell (?path= query params return the same 30KB SPA skeleton), so use WebDAV first and keep Playwright only as fallback. Re-verified 2026-09-12: PROPFIND on /public.php/webdav/ (basic auth, username = the share token prTEizKrRnYnjaD, blank password, header Depth: 1) returned 207 listing year folders 2008-2026; 2026 holds January, March, June and July, with July containing 'Board of Directors meeting pack, July 2026.pdf' and its '(background reading)' sibling. Note the PROPFIND response orders folders ALPHABETICALLY, not chronologically, so sort month names yourself rather than taking the last href. The HTML share page remains a 31KB JS shell.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-09-05: the Nextcloud share is live (HTTP 200) and a public-WebDAV PROPFIND enumerated year folders 2019-2026 with 2026 holding January, March, June and July, including 'Board of Directors meeting pack, July 2026.pdf'.</t>
+          <t>2026-09-12: the public-WebDAV PROPFIND route still works - year folders 2008-2026 enumerated, with 2026 holding January, March, June and July and the July folder carrying 'Board of Directors meeting pack, July 2026.pdf' plus its background-reading variant.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
+          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Static server-rendered TYPO3 page; no Playwright needed. Upcoming-meeting table at top lists each 2026 Board of Directors meeting with a direct 'Agenda and Papers' link to a single combined PDF (visible in raw HTML). Past years (2025 back to 2015) sit in collapsed 'Show+' accordions that expand client-side; to enumerate historic packs click the year header or derive from the folder pattern. Prefer this /publications/ landing over the /about-us/board-of-directors bio page. PDF pattern: /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Weekday&gt;_&lt;D&gt;_&lt;Month&gt;_&lt;YYYY&gt;_WEBSITE.pdf Confirmed 2026-09-05 by browser-UA curl (200, 104KB): the archive is complete and current to Sept/Nov 2026. Note for summarisers - a WebFetch of this page tends to report only the first year block (e.g. 'newest 15 January 2026') because the per-year sections are long; parse the whole document rather than trusting a truncated read.</t>
+          <t>Static server-rendered TYPO3 page; no Playwright needed. Upcoming-meeting table at top lists each 2026 Board of Directors meeting with a direct 'Agenda and Papers' link to a single combined PDF (visible in raw HTML). Past years (2025 back to 2015) sit in collapsed 'Show+' accordions that expand client-side; to enumerate historic packs click the year header or derive from the folder pattern. Prefer this /publications/ landing over the /about-us/board-of-directors bio page. PDF pattern: /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Weekday&gt;_&lt;D&gt;_&lt;Month&gt;_&lt;YYYY&gt;_WEBSITE.pdf Confirmed 2026-09-05 by browser-UA curl (200, 104KB): the archive is complete and current to Sept/Nov 2026. Note for summarisers - a WebFetch of this page tends to report only the first year block (e.g. 'newest 15 January 2026') because the per-year sections are long; parse the whole document rather than trusting a truncated read. Re-verified 2026-09-12 by browser-UA curl (200, 104KB): 126 PDF hrefs on the page, the /fileadmin/.../BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;date&gt;_WEBSITE.pdf pattern unchanged and current.</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (104KB) with dated links running through September and November 2026; packs are Combined_-_Public_Board_of_Directors_-_{date}_WEBSITE.pdf under /fileadmin/.../BoardPapers/{year}/.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (104KB) with 126 PDF links; the Combined_-_Public_Board_of_Directors_-_*_WEBSITE.pdf series runs current with dates into 2027.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Legacy ASP CMS but fully live and current. The landing /about/trustboard/index.asp lists forthcoming meetings and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp linking a single combined PDF at /about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf. All pages render statically -- no Playwright. To find the newest pack, read the landing for the latest YYYY_MM then hit that month's Combined_paper_pack.pdf. Papers carry a press embargo until after the meeting.</t>
+          <t>Legacy ASP CMS but fully live and current. The landing /about/trustboard/index.asp lists forthcoming meetings and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp linking a single combined PDF at /about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf. All pages render statically -- no Playwright. To find the newest pack, read the landing for the latest YYYY_MM then hit that month's Combined_paper_pack.pdf. Papers carry a press embargo until after the meeting. Re-verified 2026-09-12 by browser-UA curl (200): landing and month dropdown intact, forthcoming meetings listed to 4 March 2027; the per-month /about/trustboard/YYYY_MM/ gateway pages still hold the combined pack, which is why the landing itself shows no PDFs.</t>
         </is>
       </c>
       <c r="J101" t="b">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; month dropdown covers 2020-2027 and the next meeting 3 September 2026 links to /about/trustboard/2026_09/index.asp - PDFs sit on those per-month gateway pages, not the landing.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200; the legacy ASP landing still lists forthcoming meetings 3 September 2026, 5 November 2026, 7 January 2027 and 4 March 2027 with the month dropdown intact.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Static HTML page, no Playwright and no 403. Full archive grouped by fiscal year (2026/27 back to 2019/20); each meeting date links directly to a single combined agenda-and-papers PDF via the trust's /download_file/view/&lt;uuid&gt;/668 handler. WebFetch renders fine; prefer plain static fetch. Separate legacy governor/predecessor-trust pages (South Tyneside STFT, Sunderland CHSFT) under /meeting-times-agendas-and-papers are council-of-governors, not the main Board -- skip.</t>
+          <t>Static HTML page, no Playwright and no 403. Full archive grouped by fiscal year (2026/27 back to 2019/20); each meeting date links directly to a single combined agenda-and-papers PDF via the trust's /download_file/view/&lt;uuid&gt;/668 handler. WebFetch renders fine; prefer plain static fetch. Separate legacy governor/predecessor-trust pages (South Tyneside STFT, Sunderland CHSFT) under /meeting-times-agendas-and-papers are council-of-governors, not the main Board -- skip. Re-verified 2026-09-12 by browser-UA curl (200, 155KB): 42 /download_file/view/&lt;uuid&gt;/668 pack links across the fiscal-year groupings, newest meeting 6 August 2026.</t>
         </is>
       </c>
       <c r="J134" t="b">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 40+ dated entries to August 2026, packs served as /download_file/view/{uuid}/668 handler links.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (155KB) with 42 /download_file/ pack links, newest the 6 August 2026 meeting.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
+          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The DB URL is correct and the page is one of the better-maintained board archives (every meeting back to September 2021 with papers, approved minutes and recordings, all inline on one server-rendered Concrete5 page - zero hops, no Playwright). CRITICAL FETCH QUIRK confirmed 2026-07-30: the edge serves a synthetic HTTP 502 to the ClaudeBot User-Agent on every path, while curl, python-requests, Googlebot, Chrome and a no-UA request all get 200. If you see a 502 here it is a User-Agent denylist, not an outage - retry with a browser User-Agent. Structure: 'Upcoming Board Meeting Dates' is BARE TEXT not links (a link-only scraper sees nothing there - parse body text); 'Watch the Board of Directors Meetings' carries the one or two newest meetings; 'Previous Board of Directors meetings' is reverse-chronological under financial-year headings. Paper links are /download_file/view/{fileID}/875 and 303-redirect to /application/files/{4}/{4}/{4}/{Name}.pdf, so follow redirects to recover the filename. Do NOT infer recency from file ID - old minutes get re-uploaded under new IDs. THE TRAP: the document-library block at the page foot (/navigate/19297/28xx) holds only legacy 2019-2021 Committee-in-Common folders, so a validator parsing only that block concludes the page is stale; the live content sits in free-text paragraphs above it. Note robots.txt disallows /download_file/* and /application/files/* with crawl-delay 20. Papers appear the Friday before each meeting. One pack PDF plus a separate, later-published minutes PDF per meeting; 'Part 1' denotes the public session. Re-verified 2026-09-05: the ClaudeBot 502 denylist is still in force - server-side WebFetch got 502 on two attempts while browser-UA curl returned 200 (293KB) with /download_file/view/{id}/875 paper links and dates running to September 2026. A 502 here continues to mean User-Agent, not outage.</t>
+          <t>The DB URL is correct and the page is one of the better-maintained board archives (every meeting back to September 2021 with papers, approved minutes and recordings, all inline on one server-rendered Concrete5 page - zero hops, no Playwright). CRITICAL FETCH QUIRK confirmed 2026-07-30: the edge serves a synthetic HTTP 502 to the ClaudeBot User-Agent on every path, while curl, python-requests, Googlebot, Chrome and a no-UA request all get 200. If you see a 502 here it is a User-Agent denylist, not an outage - retry with a browser User-Agent. Structure: 'Upcoming Board Meeting Dates' is BARE TEXT not links (a link-only scraper sees nothing there - parse body text); 'Watch the Board of Directors Meetings' carries the one or two newest meetings; 'Previous Board of Directors meetings' is reverse-chronological under financial-year headings. Paper links are /download_file/view/{fileID}/875 and 303-redirect to /application/files/{4}/{4}/{4}/{Name}.pdf, so follow redirects to recover the filename. Do NOT infer recency from file ID - old minutes get re-uploaded under new IDs. THE TRAP: the document-library block at the page foot (/navigate/19297/28xx) holds only legacy 2019-2021 Committee-in-Common folders, so a validator parsing only that block concludes the page is stale; the live content sits in free-text paragraphs above it. Note robots.txt disallows /download_file/* and /application/files/* with crawl-delay 20. Papers appear the Friday before each meeting. One pack PDF plus a separate, later-published minutes PDF per meeting; 'Part 1' denotes the public session. Re-verified 2026-09-05: the ClaudeBot 502 denylist is still in force - server-side WebFetch got 502 on two attempts while browser-UA curl returned 200 (293KB) with /download_file/view/{id}/875 paper links and dates running to September 2026. A 502 here continues to mean User-Agent, not outage. Re-verified 2026-09-12 by browser-UA curl (200, 293KB): 78 /download_file/ paper links present and dates running to 3 March 2027, so the browser-UA route remains the reliable one here.</t>
         </is>
       </c>
       <c r="J157" t="b">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch got the synthetic 502 twice (the ClaudeBot User-Agent denylist) while browser-UA curl returned HTTP 200 (293KB) with meeting dates through September 2026.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (293KB) with 78 /download_file/ links and meeting dates running from 4 March 2026 through 2 September 2026 and on to 3 March 2027.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Static HTML landing on the org domain; WebFetch renders fully, no Playwright. Lists Board of Directors public meetings grouped by year, each dated meeting exposing a 'Meeting papers' link to a single combined PDF bundle under /media/board/Papers/&lt;year&gt;/. Upcoming meetings appear without links until the bundle is published. An archive section links prior years. Prefer WebFetch then follow the media PDF hrefs directly.</t>
+          <t>Static HTML landing on the org domain; WebFetch renders fully, no Playwright. Lists Board of Directors public meetings grouped by year, each dated meeting exposing a 'Meeting papers' link to a single combined PDF bundle under /media/board/Papers/&lt;year&gt;/. Upcoming meetings appear without links until the bundle is published. An archive section links prior years. Prefer WebFetch then follow the media PDF hrefs directly. Re-verified 2026-09-12 by browser-UA curl (200, 143KB): /media/board/Papers/2026/ bundles are current to 'Board of Directors public meeting bundle - August 2026 - updated.pdf'. Filename shape is inconsistent across meetings ('Public Bundle 04.02.26 RFS', 'public bundle 01.04.26 RFS', 'meeting bundle - Public meeting 17.06.26 RFS', 'public meeting bundle - August 2026 - updated'), so match on the /media/board/Papers/&lt;year&gt;/ path plus 'public' rather than on a fixed filename template.</t>
         </is>
       </c>
       <c r="J160" t="b">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 2026 packs at /media/board/Papers/2026/, newest the 5 August 2026 public bundle.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (143KB); 2026 bundles at /media/board/Papers/2026/ run to the August 2026 public meeting bundle (updated version), with 7 October and 2 December 2026 scheduled.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Static HTML, renders fine via plain fetch -- no Playwright. The landing shows the current/latest month's combined board pack (currently 'July 2026 Board Papers') plus an acronyms glossary. Older meetings sit under a 'Previous board papers' folder at /about-us/our-board/board-papers/navigate/758/9379, one combined PDF per meeting (bi-monthly) back to 2022. Each pack is a single large combined PDF (20MB+) served from an opaque /download_file/&lt;uuid&gt;/368 URL with no dated filename -- this opacity is why the validator saw weak evidence. Prefer the landing for the newest pack and the navigate/758/9379 folder for the dated archive.</t>
+          <t>Static HTML, renders fine via plain fetch -- no Playwright. The landing shows the current/latest month's combined board pack (currently 'July 2026 Board Papers') plus an acronyms glossary. Older meetings sit under a 'Previous board papers' folder at /about-us/our-board/board-papers/navigate/758/9379, one combined PDF per meeting (bi-monthly) back to 2022. Each pack is a single large combined PDF (20MB+) served from an opaque /download_file/&lt;uuid&gt;/368 URL with no dated filename -- this opacity is why the validator saw weak evidence. Prefer the landing for the newest pack and the navigate/758/9379 folder for the dated archive. Re-verified 2026-09-12 by browser-UA curl (200, 54KB): landing now carries the September 2026 pack; still only two download_file links on the page, which is the expected shape and why the validator keeps scoring it partial.</t>
         </is>
       </c>
       <c r="J169" t="b">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22 and upgraded from papers_partial: landing carries 'July 2026 Board Papers' (21.09MB) plus the 'Previous board papers' folder; the opaque /download_file/&lt;uuid&gt;/368 URLs are why the validator scores it weakly.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (54KB) carrying the September 2026 board pack behind the usual opaque /download_file/&lt;uuid&gt;/368 link plus the 'Previous board papers' folder.</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move. Confirmed 2026-09-05 by browser-UA curl (200, 74KB). IMPORTANT STRUCTURE NOTE: /publications_type/board-papers/ is a PAGINATED WordPress archive - page 1 carries only the newest pack and older ones sit at /publications_type/board-papers/page/2/, /page/3/ and so on. A crawler that reads page 1 only will see a single PDF and wrongly conclude the archive is thin (this is the recurring papers_partial false positive). Follow the pagination links. Newest pack on this run was Trust-board-meeting-2nd-April-2026.pdf; nothing later than 2 April 2026 was published yet.</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move. Confirmed 2026-09-05 by browser-UA curl (200, 74KB). IMPORTANT STRUCTURE NOTE: /publications_type/board-papers/ is a PAGINATED WordPress archive - page 1 carries only the newest pack and older ones sit at /publications_type/board-papers/page/2/, /page/3/ and so on. A crawler that reads page 1 only will see a single PDF and wrongly conclude the archive is thin (this is the recurring papers_partial false positive). Follow the pagination links. Newest pack on this run was Trust-board-meeting-2nd-April-2026.pdf; nothing later than 2 April 2026 was published yet. Re-verified 2026-09-12: pagination confirmed working (page 1, /page/2/ and /page/3/ each return one dated pack), but the newest pack is STILL Trust-board-meeting-2nd-April-2026.pdf, unchanged since the 2026-09-05 run - so the thin listing is now a genuine publication gap on top of the pagination quirk, not just a crawler artefact. The legacy Concrete5 listing at /about-us/our-board/publications now 404s and /about/trust/board/meeting/ carries no PDFs, so there is no alternate location holding the missing June/August packs.</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (74KB); newest pack Trust-board-meeting-2nd-April-2026.pdf (26MB). The listing is PAGINATED, which is why the validator sees a single dated PDF and scores it partial.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (75KB) and pagination works (pages 1-3 each list one pack), but the newest pack is still Trust-board-meeting-2nd-April-2026.pdf - no June or August 2026 pack has appeared in five months.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages. Confirmed 2026-09-05 by browser-UA curl (200, 102KB): packs are /download_file/{id}/1439 handler links, newest 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Nothing later than April 2026 was on the page this run - worth re-checking rather than assuming a fetch fault.</t>
+          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages. Confirmed 2026-09-05 by browser-UA curl (200, 102KB): packs are /download_file/{id}/1439 handler links, newest 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Nothing later than April 2026 was on the page this run - worth re-checking rather than assuming a fetch fault. Re-verified 2026-09-12 by browser-UA curl (200, 102KB): 37 /download_file/&lt;id&gt;/1439 links with dated labels through 03.09.2026, so the April-2026 ceiling flagged last run has cleared and publication is current.</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (102KB); newest pack 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Archive live but nothing newer than April 2026 published yet.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (102KB) with 37 /download_file/ links and dated labels running to 03.09.2026 - the April-2026 ceiling seen on the last run has cleared.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
+          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
+          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 841-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them.</t>
+          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them. Re-verified 2026-09-12: the POST action=dlp_load_posts admin-ajax recipe still works with no nonce or cookie. This run the ids were dlp_2d9d010977ed5dba_1 (empty), dlp_c5c27bbaddfd4cd9_1 (the archive, 22 dated entries, newest 'Board papers - 3 September 2026') and dlp_ae972c33f72aee98_2. Note the NUMERIC SUFFIX moves too - the archive table was _2 last run and _1 this run - so identify the table by which id returns dated board-paper rows, never by hash and never by suffix position.</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-09-05: the documented admin-ajax route still works - the archive table returned 25 documents spanning January 2023 to 3 June 2026, newest 'Board papers - 3 June 2026'. The empty static tables remain by design.</t>
+          <t>2026-09-12: the admin-ajax route still works and returned the archive table with 22 dated entries, newest 'Board papers - 3 September 2026'; the table id hashes AND their numeric suffixes had both changed again since the last run.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (99KB); the flat meeting list is intact with 23 July 2026 the newest held meeting and 16 September 2026, 12 November 2026, 21 January 2027 and 11 March 2027 scheduled ahead.</t>
+          <t>Re-confirmed 2026-09-19 by search-index evidence: the DB landing is live and indexed, and the documented predictable pack path resolves (e.g. /wp-content/uploads/2026/02/Papers-PUBLIC-Board-12-February-2026.pdf). Direct fetch was refused from this machine.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 40+ dated links, newest 'Board of Directors open meeting pack 28 July 2026' with 1 October 2026 scheduled.</t>
+          <t>Re-confirmed 2026-09-19 via server-side WebFetch: monthly meeting packs listed back to Jun 2024, latest '28 July 2026 Board of Directors meeting papers - version 2'. The local scanner's SSL error is a local-path artefact, not a dead URL.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; document-library folders for 2025 and 2026 plus 'Previous meetings', next meeting 8 October 2026.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: landing is the schedule hub (next meeting 8 October 2026) with packs one hop down in the 2025/2026/Previous meetings folders, exactly as recorded.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (65KB) with the group-board archive live; newest pack /wp-content/uploads/2026/07/Group-Board-Public-9-July-2026.pdf.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: group-board packs grouped by fiscal year, latest 11 September 2026 at /wp-content/uploads/2026/09/11-September-2026-1.pdf. Local ERR_CONNECTION_RESET is a local-path block only.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl with retries returned HTTP 200 (32KB) after two initial connection failures; per-year pages /about-us/2020-board-papers/ through /about-us/2026-board-papers/ are all present and dates run to November 2026.</t>
+          <t>Re-confirmed 2026-09-19 by search-index evidence: the DB landing is live and the documented per-year pages /about-us/2026-board-papers/ and /about-us/2025-board-papers/ both resolve. Direct fetch stayed WAF-blocked from this machine.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (104KB) with 126 PDF links; the Combined_-_Public_Board_of_Directors_-_*_WEBSITE.pdf series runs current with dates into 2027.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: combined Public Board of Directors PDFs under /fileadmin/.../BoardPapers/2026/, 2026 schedule running through November, archive back to 2015.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: meeting-papers page live, latest Public agenda and papers 28 July 2026 under /wp-content/uploads/2026/07/. The local 403 was a WAF false positive.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: latest 28 July 2026 agenda+papers at /wp-content/uploads/2026/07/, archive back to 2008. The no_papers_visible flag was a local-fetch false negative.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200; the legacy ASP landing still lists forthcoming meetings 3 September 2026, 5 November 2026, 7 January 2027 and 4 March 2027 with the month dropdown intact.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: month dropdown current to Thursday 3 September 2026, each month page linking a combined pack. no_papers_visible reflects that the PDFs sit one hop down, not on the landing.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Landing page is live and current but the site sits behind a WAF that returns HTTP 403 to WebFetch; use Playwright/headless browser, which loads it cleanly. The page lists the current calendar year's meetings inline with a 'Board papers and minutes' section giving, per meeting date, a meeting-pack PDF link plus a separate 'Minutes' PDF link, all served from the /media/{hash}/ path on the org domain. Older years live at .../board-meetings-papers-minutes/archive/. Match the meeting-pack PDF (filenames contain 'pack' or 'meeting-book' or 'meeting-pack'), not the minutes. UPDATE 5 Aug 2026: Playwright is no longer required. Archive.org Save Page Now (GET https://web.archive.org/save/&lt;landing&gt;) returns the live page with document links (direct fetch 403s with a 473-byte body; SPN returned 200 / 88KB / 8 doc links). SPN is much cheaper than a browser launch - try it first, keep Playwright as the backstop.</t>
+          <t>Landing page is live and current but the site sits behind a WAF that returns HTTP 403 to WebFetch; use Playwright/headless browser, which loads it cleanly. The page lists the current calendar year's meetings inline with a 'Board papers and minutes' section giving, per meeting date, a meeting-pack PDF link plus a separate 'Minutes' PDF link, all served from the /media/{hash}/ path on the org domain. Older years live at .../board-meetings-papers-minutes/archive/. Match the meeting-pack PDF (filenames contain 'pack' or 'meeting-book' or 'meeting-pack'), not the minutes. UPDATE 5 Aug 2026: Playwright is no longer required. Archive.org Save Page Now (GET https://web.archive.org/save/&lt;landing&gt;) returns the live page with document links (direct fetch 403s with a 473-byte body; SPN returned 200 / 88KB / 8 doc links). SPN is much cheaper than a browser launch - try it first, keep Playwright as the backstop. UPDATE 2026-09-19: server-side WebFetch reached the landing and enumerated the 29 July 2026 pack without a 403 this week, so try WebFetch before Playwright; the archive_org_save_page_now route stays available as the backstop.</t>
         </is>
       </c>
       <c r="J105" t="b">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; newest pack /media/h22kzsn0/rduh-public-board-20260729-meeting-book-for-the-public-updated-20260729.pdf (29 July 2026).</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch, which reached the page cleanly this week: latest pack rduh-public-board-20260729-meeting-book-for-the-public-updated-20260729.pdf (29 July 2026), plus minutes and Vimeo recordings.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (155KB) with 42 /download_file/ pack links, newest the 6 August 2026 meeting.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: fiscal-year archive back to 2019/20, each meeting linking a combined pack via the /download_file/view/&lt;uuid&gt;/668 handler. no_papers_visible was a local-fetch false negative.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (143KB); 2026 bundles at /media/board/Papers/2026/ run to the August 2026 public meeting bundle (updated version), with 7 October and 2 December 2026 scheduled.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: latest Board of Directors public bundle for 05 August 2026 under /media/board/Papers/2026/. no_papers_visible was a local-fetch false negative.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 20+ dated meetings, newest /wp-content/uploads/2026/09/0-Meeting-in-Public-03.09.2026-compressed.pdf.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: latest 'Meeting in Public 03.09.2026' compressed pack under /wp-content/uploads/2026/09/. Local 403 is a local-path block only.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (54KB) carrying the September 2026 board pack behind the usual opaque /download_file/&lt;uuid&gt;/368 link plus the 'Previous board papers' folder.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: landing carries the current 'September 2026 board papers' pack (26.67MB) plus the acronyms glossary, with older meetings under Previous board papers.</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Cloudflare blocks WebFetch (403 on every hpft.nhs.uk URL incl. PDFs) so Playwright is required. The often-cited /about-us/board-of-directors-meetings/ and /our-board-papers-and-publications/ paths are 404. The real archive is a JS FAQ accordion titled 'Board papers and publications' on this corporate-information-and-governance page: the panel is initially collapsed (no anchors in static DOM) — click the .faq-panel-question whose text is 'Board papers and publications' to reveal a list of dated 'meeting book' PDF links back to 2021. PDFs are hosted on-domain under /media/{slug}/...meeting-book-public-board-of-directors-*.pdf.</t>
+          <t>Cloudflare blocks WebFetch (403 on every hpft.nhs.uk URL incl. PDFs) so Playwright is required. The often-cited /about-us/board-of-directors-meetings/ and /our-board-papers-and-publications/ paths are 404. The real archive is a JS FAQ accordion titled 'Board papers and publications' on this corporate-information-and-governance page: the panel is initially collapsed (no anchors in static DOM) — click the .faq-panel-question whose text is 'Board papers and publications' to reveal a list of dated 'meeting book' PDF links back to 2021. PDFs are hosted on-domain under /media/{slug}/...meeting-book-public-board-of-directors-*.pdf. UPDATE 2026-09-19: server-side WebFetch reached this page and the /media/ pack links cleanly this week, so try WebFetch FIRST and treat the Cloudflare 403 as intermittent rather than absolute; Playwright remains the fallback.</t>
         </is>
       </c>
       <c r="J171" t="b">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 31 dated links 2021-2026, newest /media/ccrbvx33/meeting-book-public-board-of-directors-16726.pdf (16 July 2026).</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch, which reached the page this week despite the previously recorded Cloudflare 403: latest 'Meeting Book PUBLIC Board Of Directors 16.7.26' at /media/ccrbvx33/, archive back to 2021.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (75KB) and pagination works (pages 1-3 each list one pack), but the newest pack is still Trust-board-meeting-2nd-April-2026.pdf - no June or August 2026 pack has appeared in five months.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: paginated publications_type archive, page 1 currently showing the 23 June 2026 Extraordinary Trust Board pack. The single-pack-per-page layout is what trips the papers_partial heuristic.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (102KB) with 37 /download_file/ links and dated labels running to 03.09.2026 - the April-2026 ceiling seen on the last run has cleared.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: dated Board of Directors public meeting packs listed via numeric /download_file/&lt;id&gt;/1439 links, archive spanning 2020-2026.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl with retries returned HTTP 200 (97KB) after an initial connection failure; the board-summary index is current, newest /board/board-summary-wednesday-29-july-2026.</t>
+          <t>Re-confirmed 2026-09-19 by search-index evidence: the /board summaries index and its short per-meeting slugs are live (e.g. /mar26 for 25 March 2026). Cloudflare still 403s both local fetch and WebFetch.</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -15175,17 +15175,17 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-09-12: the admin-ajax route still works and returned the archive table with 22 dated entries, newest 'Board papers - 3 September 2026'; the table id hashes AND their numeric suffixes had both changed again since the last run.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: landing loads and lists the next meeting (5 November 2026), but the Document Library Pro paper tables are serverSide AJAX and render empty to any static fetch - browser render still required.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; ~99 dated meeting sub-pages from 2013 to 2026, newest 'Trust Board 22nd July 2026' at /board-meetings/3661-trust-board-22nd-july-2026.</t>
+          <t>Re-confirmed 2026-09-26 via server-side WebFetch: /board-meetings past-meetings index current to 'Trust Board 23rd September 2026' (/board-meetings/3767-trust-board-23rd-september-2026), with 22 July, 3 June, 25 March and 28 January 2026 meetings listed. Local 403 is a local-path block only.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1227,13 +1227,39 @@
           <t>https://www.sussexpartnership.nhs.uk/about-us/how-our-trust-run/board-meetings</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pattern E2 - blocked on every simple route, reachable via one specific Playwright recipe. www.sussexpartnership.nhs.uk sits behind Imperva/Incapsula (CNAME 8gdsmqk.ng.impervadns.net, X-CDN: Imperva), which drops or 503s HTML for plain curl, browser-UA curl, HTTP/1.1- and TLS1.2-forced curl, port 80, server-side WebFetch (socket hang up), the Jina reader and public CORS proxies alike. Archive.org Save Page Now now requires a login so that fallback is closed, and Wayback's last good HTML capture of this page is 2026-02-02 (403 from 2026-02-21 on). WHAT WORKS (confirmed 2026-09-26): local headless Playwright Chromium with a real Chrome UA, locale en-GB, and HTTP/2 LEFT ENABLED (--disable-http2 makes it worse: ERR_EMPTY_RESPONSE). GET /robots.txt first - it is whitelisted, returns 200 even to bare curl, and sets visid_incap_3332221 + incap_ses_576_3332221 - then wait at least 20s, because robots.txt declares crawl-delay: 20 and Imperva enforces it; then navigate to the board page retrying up to 4x with ~24s gaps (attempt 0 is typically 503, attempt 1 ERR_HTTP2_PROTOCOL_ERROR, and a later attempt returns 200 once Chromium has executed /_Incapsula_Resource?SWJIYLWA=...). Reuse that same browser context for the PDF GETs with Referer set to the board page and &gt;=20s between requests. Single-attempt crawls always fail. The DB URL IS the archive: one level, no year drilldown and no per-meeting sub-pages, and no separate document-library subdomain. Content is server-rendered despite a closed accordion (button aria-expanded=false, id=single-accordion-34271; optional deep link ?open=34271), so no JS is needed to extract links once past the WAF - financial-year h2 headings (2026/27 back to 2023/24) each wrap a ul of one-per-item links in two interchangeable forms: direct /application/files/{4d}/{4d}/{4d}/{Name}.pdf, and indirect /download_file/view/{id}/292 which 303s to an /application/files path (292 is the board-papers file set; ids increment chronologically). Each meeting carries a 'Papers' entry - the combined pack, prefer this - plus a 'Minutes' entry added about two months later; do not mistake Minutes for the pack. Filenames are wildly inconsistent (Published_Board_Pack.pdf, Board_Pack.pdf, 00_-_BoD_Agenda_June_2026_PUBLIC-combined_5.pdf, 2025.08.07_-_Public_Board_of_Directors_-_Combined_Pack_V2.pdf, Board_of_Directors_-_October_2025.pdf), so NEVER construct a URL from a date - scrape the anchor text, which is the only reliable date source. Before a meeting the entry may be agenda-only (the 8 Oct 2026 link is currently a 2-page DRAFT agenda, swapped for the ~450-page pack around the meeting date), so re-check file size / page count rather than just link presence. Scheduled dates slip - trust the Meeting Papers list over the 'Future Meetings' block (Feb 2026 advertised 11 June 2026; the meeting actually ran 18 June). Packs are 350-460pp and 10-16MB, so allow &gt;240s timeouts. Bi-monthly single-trust Board of Directors, not a cluster board; next public boards 8 October 2026, 10 December 2026, 11 February 2027. Council of Governors papers are a separate sibling page at /about-us/how-our-trust-run/council-governors/council-governors-meetings. Recordings at youtube.com/@SussexPartnershipNHS/videos; governance contact spft.corporategovernance@nhs.net.</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>/application/files/{4d}/{4d}/{4d}/{Name}.pdf;/download_file/view/{id}/292 (303-redirects to /application/files/...);anchor text 'Board of Directors Papers - {D Month YYYY}';Published_Board_Pack.pdf;Board_Pack.pdf;Combined_Pack;PUBLIC-combined;large combined pack: 350-460pp, 10-16MB</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Minutes;DRAFT_BoD_Agenda (agenda-only pre-meeting stub);/council-governors/;dates from the 'Future Meetings' block (they slip)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-09-26: first full validation, via step-3a escalation. Local headless Playwright Chromium (robots.txt first, 20s crawl-delay, retries) returned HTTP 200 (121KB, title 'Board meetings :: Sussex Partnership NHS Foundation Trust'); confirmed by download the 18 June 2026 combined public pack (462pp, 11.4MB) and the 8 October 2026 draft agenda. Every non-Playwright route (plain and browser-UA curl, WebFetch, Jina, CORS proxies, Archive.org Save Page Now) is dropped by Imperva - the scan's 'broken' is a routing block, not a dead page.</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -2781,7 +2807,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2799,7 +2825,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2809,7 +2835,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 841-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
+          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3865,7 +3891,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3875,7 +3901,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-09-12: the public-WebDAV PROPFIND route still works - year folders 2008-2026 enumerated, with 2026 holding January, March, June and July and the July folder carrying 'Board of Directors meeting pack, July 2026.pdf' plus its background-reading variant.</t>
+          <t>Re-confirmed 2026-09-26: the human landing uhb.nhs.uk/about/trust-management/bod/papers/ fetched cleanly via WebFetch and still points at exactly the Nextcloud share in the DB (docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD), so the share id has not rotated. The share itself stays JS-rendered - no_papers_visible is the expected false negative for a static fetch of it.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -5243,7 +5269,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -5261,7 +5287,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5271,7 +5297,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
+          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5475,7 +5501,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5485,7 +5511,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 40+ dated links in per-year tabs, newest 'Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf'.</t>
+          <t>Re-confirmed 2026-09-26 via server-side WebFetch: year-tabbed landing current to the 2 September 2026 public board (Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf), with 1 July, 6 May, 4 March and 14 January 2026 packs all present under /wp-content/uploads/. No WAF on this route; the scan's 403 is local-path only.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -7237,7 +7263,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7247,7 +7273,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: year-index page live listing 2017-2026 sub-pages. The local connection-reset was a WAF false positive; WebFetch reaches it cleanly.</t>
+          <t>Re-confirmed 2026-09-26 via server-side WebFetch of the year page /board-of-directors-meetings/2026-board-of-directors-meetings/: quarterly 2026 meetings listed as /events/ pages (11 March, 10 June, 9 September, 9 December 2026). The landing index itself was ECONNRESET on every route this run, so go straight to the year page if the index refuses; the local connection-reset remains a WAF artefact, not a move.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -8067,7 +8093,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8077,7 +8103,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; per-financial-year links into the doclibrary-rcht.cornwall.nhs.uk document library, next meeting 3 September 2026.</t>
+          <t>Re-confirmed 2026-09-26 via server-side WebFetch: landing live with the Annual Public Meeting on 17 September 2026 and per-financial-year links into doclibrary-rcht (BoardMeetings2627.aspx through BoardMeetings2223.aspx) intact. Note the 2026-27 year link is currently wrapped in an Outlook safelinks redirect - unwrap the url= parameter before following it. Local 403 is a local-path block only.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -11093,7 +11119,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -11111,7 +11137,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11121,7 +11147,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
+          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11909,7 +11935,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11919,7 +11945,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (293KB) with 78 /download_file/ links and meeting dates running from 4 March 2026 through 2 September 2026 and on to 3 March 2027.</t>
+          <t>Route re-check 2026-09-26: server-side WebFetch again received the documented synthetic HTTP 502, confirming the ClaudeBot User-Agent denylist on this edge is still in force (it is a UA denylist, not an outage). Last content confirmation stands from 2026-09-12 browser-UA curl (200, 293KB, 78 /download_file/ links, meeting dates 4 March 2026 to 2 September 2026 and on to 3 March 2027) - retry with a browser UA rather than treating 502 as down.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -14329,7 +14355,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -14347,7 +14373,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14357,7 +14383,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 845-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
+          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14463,7 +14489,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -14481,7 +14507,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14491,7 +14517,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-09-12: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local browser-UA requests got only the 841-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body; treat as a routing block, not a withdrawal of papers.</t>
+          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-12: the first browser-UA curl was connection-reset and an immediate retry returned HTTP 200 (47KB) with the archive intact - newest pack /documents/512-board-paper-30th-july-2026, forward meeting dates listed to January 2028.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (two connection resets, third try 200, 48KB): newest pack /documents/518-board-paper-24-september-2026/file.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The live landing /about-us/board-of-directors/meetings-in-public/ lists one entry per meeting ('Meeting papers: &lt;date&gt;') as sub-pages, newest first, spanning 2025 and 2026 in a single flat list (no per-year archives). Each sub-page links to the single combined public board pack PDF. Packs also live at a predictable direct path www.qvh.nhs.uk/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;...&gt;.pdf, so a crawler can grab those directly. WebFetch renders the full meeting list statically, so Playwright is not required; prefer the one large combined 'Papers-PUBLIC-Board' PDF per meeting and skip individual annexes. Re-verified 2026-09-12 by browser-UA curl (200, 99KB): meeting sub-pages still listed newest-first, latest held 23 July 2026 with dates scheduled into March 2027.</t>
+          <t>The live landing /about-us/board-of-directors/meetings-in-public/ lists one entry per meeting ('Meeting papers: &lt;date&gt;') as sub-pages, newest first, spanning 2025 and 2026 in a single flat list (no per-year archives). Each sub-page links to the single combined public board pack PDF. Packs also live at a predictable direct path www.qvh.nhs.uk/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;...&gt;.pdf, so a crawler can grab those directly. WebFetch renders the full meeting list statically, so Playwright is not required; prefer the one large combined 'Papers-PUBLIC-Board' PDF per meeting and skip individual annexes. Re-verified 2026-09-12 by browser-UA curl (200, 99KB): meeting sub-pages still listed newest-first, latest held 23 July 2026 with dates scheduled into March 2027. Update 2026-10-03: the meeting list is now a &lt;select&gt; dropdown form (name=ddselect, numeric option values) that POSTs to /ddselect.php and 302-redirects to /download/meetings-in-public/meeting-papers-&lt;d-month-yyyy&gt;/, which serves the pack file directly - a link-only crawler sees no meeting hrefs, so either submit the form or use the direct /download/meetings-in-public/meeting-papers-&lt;d-month-yyyy&gt;/ pattern. Latest pack 16 September 2026.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 by search-index evidence: the DB landing is live and indexed, and the documented predictable pack path resolves (e.g. /wp-content/uploads/2026/02/Papers-PUBLIC-Board-12-February-2026.pdf). Direct fetch was refused from this machine.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 99KB): dropdown lists 16 Sep, 23 Jul, 9 Jul and 14 May 2026; POST ddselect=15365 redirected to /download/meetings-in-public/meeting-papers-16-september-2026/ (18.8MB pack).</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via server-side WebFetch: /board-meetings past-meetings index current to 'Trust Board 23rd September 2026' (/board-meetings/3767-trust-board-23rd-september-2026), with 22 July, 3 June, 25 March and 28 January 2026 meetings listed. Local 403 is a local-path block only.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 91KB): /board-meetings lists 2026 meetings up to 23 September 2026, whose page carries 45 ashfordstpeters.info/images/board-papers/2026-09-23/ PDFs.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Current URL is correct and live (static WebFetch works, no WAF). The Board of Directors page embeds the full meeting-pack archive organised by month back to June 2024, plus a 'Reading the Signals' oversight group archive. PDFs are served from a relative /s3/assets/files/board_of_directors_docs/bod-meeting-packs/{month}{year}/ path on-domain. Crawl the board-of-directors page and scrape /s3/assets/.../bod-meeting-packs/ links; note some recent meetings split the pack into multiple PDFs and a few items are .docx/.pptx rather than PDF.</t>
+          <t>Current URL is correct and live (static fetch works via WebFetch and local curl with a Chrome UA, no WAF). The Board of Directors page embeds the full meeting-pack archive organised by month back to June 2024, plus a 'Reading the Signals' oversight group archive. PDFs are served from a relative /s3/assets/files/board_of_directors_docs/bod-meeting-packs/ path on-domain, usually inside a {month}{year}/ sub-folder, but the folder month does not reliably match the meeting date: the 1 Oct 2026 pack sits in september2026/ (board-of-directors-meeting-pack-01.10.26.pdf) and the 28 Jul 2026 pack sits loose in the root bod-meeting-packs/ folder (board-of-directors-open-meeting-pack---28-july-2026-version-2.pdf). So scrape every /bod-meeting-packs/ link and read the date from the filename instead of building folder paths. Some meetings split the pack into multiple PDFs (e.g. April 2026 is per-item), and a few items are .docx/.pptx rather than PDF. The occasional local SSL error in the validator is a local-path artefact.</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via server-side WebFetch: monthly meeting packs listed back to Jun 2024, latest '28 July 2026 Board of Directors meeting papers - version 2'. The local scanner's SSL error is a local-path artefact, not a dead URL.</t>
+          <t>Re-verified 2026-10-03 by local curl (200, 272KB): newest pack board-of-directors-meeting-pack-01.10.26.pdf (1 October 2026) under september2026/, plus the 28 Jul and 4 Jun 2026 packs.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2003,13 +2003,39 @@
           <t>https://www.nhft.nhs.uk/board/</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pattern B/C hybrid (static). The /board/ landing (NHFT 'Our board') has a share-my-box folder list near the bottom with year folders for two boards: '20XX Trust Board Papers' (NHFT Board of Directors; 2026 = ?smbfolder=3215) and '20XX Group Board Papers' (the joint NHFT + Leicestershire Partnership NHS Trust Group Board; 2026 = ?smbfolder=3216). Folders run from 2023 Trust and 2025 Group to the present. Hop 1: open the year folder (https://www.nhft.nhs.uk/board?smbfolder=NNNN), which lists per-meeting subfolders named e.g. 'M09 - 24 September 2026 Board Papers' (NHFT meets every two months: Jan, Mar, May, Jul, Sep, Nov) and 'M09 - 29 September 2026 Group Board Papers' (Group meets about three times a year: Jan, May, Sep). Hop 2: open the meeting subfolder to get download.cfm?doc=docm93jijm4n&lt;id&gt;.pdf&amp;ver=&lt;n&gt; links. The Group Board folder has a single 'Group Public Board - DD.MM.YY Combined Paper Pack' plus an agenda - take the combined pack. The NHFT Trust Board folder has NO combined pack, only lettered individual papers ('00 - NHFT Board Public Agenda', 'A - Minutes', 'D - Chair's Report', 'F - Integrated Organisational Report' ...), so a crawler must collect all of them. Skip the ?smba2z= A-Z links and the ?resetpass link. Future meeting dates appear as plain text on the landing. Static curl with a browser User-Agent works.</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Combined Paper Pack;Group Public Board;Board Papers;NHFT Board Public Agenda;download.cfm?doc=docm93jijm4n;smbfolder=</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>smba2z=;resetpass;Council of Governors;Declaration of Interests Register;Annual Workplan;Action Sheet</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Found 5 NHFT Trust Board meeting folders in 2026 (Jan to 24 Sep, individual papers) and 3 Group Board folders (Jan, May, 29 Sep 2026); the 29 Sep 2026 Group Combined Paper Pack downloaded as a 2.9MB PDF.</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -2059,7 +2085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward meeting timetable (Feb 2026 through Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The packs themselves sit one hop down in a 'Previous meetings' folder and per-year folders (2025, 2026) that must be opened to reach the dated agenda/report PDFs; past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch - the local deep scan's SSL-verify failure on lpft.nhs.uk is a local-path artefact, not a dead page. Crawl the landing for the schedule, then follow the year/previous-meetings folder links for packs.</t>
+          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward 2026/27 timetable (12 Feb, 9 Apr, 11 Jun, 13 Aug, 8 Oct, 10 Dec 2026, 11 Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The papers sit three hops down in a Concrete CMS document library: landing -&gt; 'Previous meetings' / '2025' / '2026' year folder (/navigate/{folderId}/53923; 2026 = /navigate/13049/53923) -&gt; one dated folder per meeting (e.g. '13 August 2026' = /navigate/13654/53923) -&gt; numbered per-item papers ('1) Public Board of Directors Agenda - 13 August 2026', '2.1) Chief Executive Report...') served as /download_file/{uuid}/382 links with no .pdf extension. There is no single combined pack, so collect every item in the meeting folder and take titles from the anchor/table text. Past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch and, as of 2026-10-03, also via local curl with a Chrome UA (the page carries an 'incapsula' string but serves normally). The validator's local SSL-verify failure is a local-path artefact, not a dead page.</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2067,7 +2093,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Agenda;Board of Directors;Trust Board;papers</t>
+          <t>/navigate/13049/53923 (2026 year folder);per-meeting folder named '{D Month YYYY}';/download_file/{uuid}/382;Public Board of Directors Agenda</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2077,7 +2103,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2087,7 +2113,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: landing is the schedule hub (next meeting 8 October 2026) with packs one hop down in the 2025/2026/Previous meetings folders, exactly as recorded.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): the 2026 folder holds meeting folders 12 Feb, 9 Apr, 11 Jun and 13 Aug 2026 with numbered download_file items; 8 Oct 2026 not yet posted.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2271,13 +2297,39 @@
           <t>https://www.ulh.nhs.uk/about/board-meetings/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages, static). The landing lists meetings newest-first (future ones first, then past ones from 2026 back to 2019). Each title is a date ('Tuesday 1 September 2026') linking to /about/board-meetings/&lt;weekday-d-month-yyyy&gt;/. Slugs are not always reliable (the 6 January 2026 meeting sits at /tuesday-6-january-2025/), so follow the link text rather than building slugs. Each meeting sub-page has ONE combined PDF under /wp-content/uploads/YYYY/MM/; the upload folder date does not match the meeting date (2026 packs sit under /2026/02/). Names vary: 'Lincolnshire-Community-and-Hopsitals-Group-board-papers-September-2026.pdf' (note the 'Hopsitals' typo), 'LCHG-Board-papers-March-2026.pdf', 'Agenda-bundle-2026-07-07.pdf', 'Agenda-bundle-May-2026-V2.pdf'. Since 2025 these are joint Lincolnshire Community and Hospitals Group (LCHS + ULTH) Board papers. Skip the 'LCHS and ULTH Annual Public Meetings' entries. Future meeting pages (3 Nov 2026 onwards) have no PDFs until about a week before the meeting. Packs are large (Sep 2026 is about 37MB). Static fetch works.</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Group-board-papers;LCHG-Board-papers;Agenda-bundle;/wp-content/uploads/</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Annual Public Meeting;annual-public-meetings;Council of Governors</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Found 5 combined 2026 packs (Jan, Mar, May, Jul, 1 Sep 2026) on per-meeting sub-pages, meeting pages back to 2019; the Sep 2026 pack is a 36.7MB PDF.</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -2407,7 +2459,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The registered URL /board-and-board-papers/ is only an info page (meeting dates + governance contact) and correctly shows no PDFs. The actual papers live one level down at /board-papers (linked in that page's sidebar). That index lists year folders as query-string links: /board-papers?media_folder=1422&amp;root_folder=2025/26 and /board-papers?media_folder=1466&amp;root_folder=2026/27. A crawler must follow the media_folder query params to reach per-meeting PDFs (folder contents load dynamically, so render or fetch the folder URLs). Coverage current to 2026/27. Prefer the full board pack/'supporting documents' bundle per meeting; filter out minutes-only and agenda-only files and pre-2025 folders. Point the crawler at root_folder=2026/27 for the latest papers. RETRIEVAL 5 Aug 2026: papers live at /board-papers in a MEDIA BROWSER, not as direct links. Navigate /board-papers?media_folder=&lt;id&gt;&amp;root_folder=&lt;year&gt; to a financial-year folder, then one sub-folder PER MEETING, each containing the pack. 2026/27 = media_folder=1466. Plain requests reads it fine - Playwright not needed.</t>
+          <t>The registered info page /board-and-board-papers/ only gives meeting dates and a governance contact. The papers live at /board-papers in a server-rendered media browser that plain requests/curl read fine, so no Playwright is needed. Navigate /board-papers?media_folder=&lt;id&gt;&amp;root_folder=&lt;label&gt;: financial-year folders 2025/26 = media_folder=1422 and 2026/27 = media_folder=1466. Inside each year is one sub-folder PER MEETING (2026/27 so far: 1467 '1. Thursday 14th May 2026', 1470 '22nd June 2026 - Extraordinary Board', 1471 '25 June 2026 - Extraordinary Public Board Meeting', 1474 '4. Thursday 9 July 2026', 1480 'Thursday 10 September 2026'). Each meeting folder lists files as /download/{slug}.pdf?ver={n} links, e.g. /download/trust-board-open-meeting-thursday-10-september-2026-combined-paperspdf.pdf. Prefer the 'combined-papers' PDF; skip the .docx agenda, minutes-only files and pre-2025 folders.</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2415,7 +2467,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>/board-papers?media_folder=;root_folder=2026/27;root_folder=2025/26</t>
+          <t>/board-papers?media_folder=;root_folder=2026/27;/download/trust-board-open-meeting-{date}-combined-paperspdf.pdf;combined-papers</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2425,17 +2477,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Papers are present in dynamically-loaded year folders (2025/26 and 2026/27) reached via media_folder query params off /board-papers; individual PDFs require rendering the folder view to enumerate.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): media_folder=1480 ('Thursday 10 September 2026') contains trust-board-open-meeting-thursday-10-september-2026-combined-paperspdf.pdf.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2835,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
+          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3145,7 +3197,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3155,7 +3207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-09-05: shallow check reset again, but browser-UA curl returned HTTP 200 (43KB); newest pack is 'Combined Public Board Papers v2 6 August 2026-compressed.pdf'.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 43KB; WebFetch got ECONNRESET): combined public board packs for 2 Apr, 4 Jun, 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3225,7 +3277,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3235,7 +3287,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2025-2026 year sub-page lists seven dated combined board packs (07.05.2025 through 04.03.2026); 2026-2027 sub-page already created.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): the 2026-2027 sub-page lists packs for 6 May, 1 Jul and 29 Jul 2026 (latest board-of-directors-public-meeting-29072026.pdf).</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3891,7 +3943,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3901,7 +3953,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26: the human landing uhb.nhs.uk/about/trust-management/bod/papers/ fetched cleanly via WebFetch and still points at exactly the Nextcloud share in the DB (docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD), so the share id has not rotated. The share itself stays JS-rendered - no_papers_visible is the expected false negative for a static fetch of it.</t>
+          <t>Re-verified 2026-10-03 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; September contains 'Board of Directors meeting pack, September 2026.pdf'.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4593,7 +4645,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4603,7 +4655,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 18 dated agenda/papers pairs 2023-2026, newest 'Board of Directors meeting papers - Wednesday 22 July 2026' (7.9MB).</t>
+          <t>Re-verified 2026-10-03 via server-side WebFetch (archive.org route not needed this run): agenda and papers /media/&lt;id&gt;/ links for 28 Jan, 29 Apr and 22 Jul 2026. Local requests still get the 403 WAF page.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4811,7 +4863,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4821,7 +4873,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: group-board packs grouped by fiscal year, latest 11 September 2026 at /wp-content/uploads/2026/09/11-September-2026-1.pdf. Local ERR_CONNECTION_RESET is a local-path block only.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 66KB; WebFetch got ECONNRESET): group board PDFs for 8 Jan, 8 May, 9 Jul and 11 Sep 2026 under /wp-content/uploads/.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -5297,7 +5349,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
+          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5501,7 +5553,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5511,7 +5563,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via server-side WebFetch: year-tabbed landing current to the 2 September 2026 public board (Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf), with 1 July, 6 May, 4 March and 14 January 2026 packs all present under /wp-content/uploads/. No WAF on this route; the scan's 403 is local-path only.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 292KB): five 2026 combined packs under /wp-content/uploads/2026/, newest 2 September 2026.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5857,11 +5909,11 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Landing page is live but WebFetch is WAF-blocked (HTTP 403 / connection reset); use Playwright. The landing page lists meeting dates and links to per-year 'Board Papers' pages at /about-us/{YEAR}-board-papers/. The current-year page is an accordion/tablist: each meeting date is a collapsed tab whose individual enclosure PDFs are only revealed when clicked, so Playwright is required to click each tab and harvest links. PDFs are NOT a single pack — each agenda enclosure is a separate PDF (lettered A, B, C...) served from /download/clientfiles/files/ or the older /clientfiles/File/ path with URL-encoded spaces. Re-verified 2026-09-05: the WAF refused the first two attempts (curl exit 000) but a browser-UA request with --retry succeeded (200, 32KB), exposing the /about-us/{YYYY}-board-papers/ per-year links including 2026 and dates through November 2026. Retry before escalating to a browser - the block is intermittent, not absolute.</t>
+          <t>Landing /about-us/board-meetings/ lists meeting dates and links to per-year 'Board Papers' pages at /about-us/{YEAR}-board-papers/ (2020-2026 linked; there is no 2023 link on the landing). Server-side WebFetch is WAF-blocked (HTTP 403), but a local browser-UA static request works: re-verified 2026-10-03, the 2026 page returned 200/36KB and, although the meetings are shown as a collapsed accordion/tablist, every enclosure PDF href is already in the static HTML, so no Playwright click-through is needed - just regex the hrefs. PDFs are NOT a single pack: each agenda enclosure is a separate PDF (lettered A, B, C..., with the agenda prefixed '0 - ' or a YYYYMMDD date) served from /download/clientfiles/files/ (older years use /clientfiles/File/) with URL-encoded spaces. The WAF has been intermittent (curl exit 000 / connection reset on some earlier runs), so retry with --retry before escalating to a browser; Playwright remains the fallback if the static path is refused.</t>
         </is>
       </c>
       <c r="J73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5875,7 +5927,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5885,7 +5937,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 by search-index evidence: the DB landing is live and the documented per-year pages /about-us/2026-board-papers/ and /about-us/2025-board-papers/ both resolve. Direct fetch stayed WAF-blocked from this machine.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; static HTML holds every enclosure PDF for Jan-Jul 2026 plus the 8 September 2026 agenda; WebFetch got 403.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6337,7 +6389,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6347,7 +6399,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: combined Public Board of Directors PDFs under /fileadmin/.../BoardPapers/2026/, 2026 schedule running through November, archive back to 2015.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 104KB): five BoardPapers/2026/Combined_..._WEBSITE.pdf packs (Jan, Mar, May, Jul, 10 Sep 2026).</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6477,13 +6529,39 @@
           <t>https://www.midyorks.nhs.uk/board-meetings/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Pattern A (direct PDFs on landing, static). The /board-meetings/ page lists one combined public pack per meeting newest-first, 2019 to present (meetings every two months: Jan, Mar, May, Jul, Sep, Nov). Links are /download/&lt;slug&gt;.pdf?ver=N&amp;doc=docm93jijm4n&lt;id&gt;.pdf (older entries /download.cfm?doc=...; both serve the PDF after a 302). Link text looks like 'Public Trust Board 10.09.26 - PAPERS - Combined.pdf [pdf] 20MB', with the date as DD.MM.YY or written out. Take the 'Public Trust Board ... PAPERS' file; skip 'Reading Room' / 'Papers for Information' companion bundles; where both 'Single PDF' and 'Portfolio' versions exist (2022 to Jan 2024) prefer 'Single PDF'. Skip the MS Teams join link. Packs are 6-23MB. Static curl works.</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Public Trust Board;PAPERS;Combined;Single PDF;docm93jijm4n</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Reading Room;Papers for Information;Portfolio;teams.microsoft.com</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Found 5 dated 2026 public board packs (15.01.26 to 10.09.26) and archive back to 2019; the 10 Sep 2026 combined pack is a 21MB PDF.</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -6533,7 +6611,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Current URL is live and correct; reported 'broken' was transient/WAF. WordPress site under About us &gt; How we're run &gt; Our Trust Board &gt; Meetings and papers. Page archives meetings chronologically back to 2008, each with agenda+papers PDF and minutes PDF hosted at /wp-content/uploads/YYYY/MM/. Next meeting 30 June 2026. Retry WebFetch on 403; no JS rendering needed.</t>
+          <t>Current URL is live and correct; reported 'broken' was transient/WAF. WordPress site under About us &gt; How we're run &gt; Our Trust Board &gt; Meetings and papers. Page archives meetings chronologically back to 2008, each with agenda+papers PDF and minutes PDF hosted at /wp-content/uploads/YYYY/MM/. Latest pack 29 September 2026 (re-verified 2026-10-03). Retry WebFetch on 403; no JS rendering needed.</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -6551,7 +6629,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6561,7 +6639,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: latest 28 July 2026 agenda+papers at /wp-content/uploads/2026/07/, archive back to 2008. The no_papers_visible flag was a local-fetch false negative.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 477KB): 13 /wp-content/uploads/2026 PDFs, newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6822,16 +6900,42 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.qehkl.nhs.uk/about-us/meetings-of-the-board-of-directors/</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+          <t>https://nw-uhg.org.uk/p/about-us/meetings-and-agendas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pattern F (wrong URL fixed 2026-10-03) plus group board. The former DB URL (qehkl.nhs.uk/about-us/meetings-of-the-board-of-directors/) is stale: its newest QEH-only board meeting is 25 September 2025, and the page now says QEH is governed by the Norfolk and Waveney University Hospitals Group (QEH + NNUH + JPUH) Board, linking to https://nw-uhg.org.uk/p/about-us/meetings-and-agendas (the same address as this entry's group_board_url). That group page is static and shows only the CURRENT/NEXT public Group Board: a 'Read the full board papers' link (/assets/5772c785/group_board_meeting_in_public_DD.MM.YY_-_full_pack.pdf) plus 'supplementary documents', and future dates (2 Dec 2026, 3 Feb 2027, 7 Apr 2027). Meetings every two months, rotating venue between JPUH, QEHKL and NNUH. Past packs drop off the page, so a crawler must snapshot each time. Older 2026 packs survive elsewhere: the 5 Aug 2026 pack via the news post /p/latest-news/group-board-meetings-in-public-1 (group_board_meeting_in_public_05.08.26_iw.pdf); the 1 Apr 2026 pack on NNUH's site (www.nnuh.nhs.uk/wp-content/uploads/2026/03/Group-Board-in-Public-01.04.26-Meeting-papers.pdf); the inaugural 17 Dec 2025 pack also on nnuh.nhs.uk. Take 'full pack' / 'Meeting papers'; skip supplementary / Reading Room packs and GPJC items. The same group page serves RM1 and RGP. Static fetch works.</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>group_board_meeting_in_public;full_pack;Group-Board-in-Public;Meeting-papers;/assets/5772c785/</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>supplementary;Reading-Room;GPJC;Council of Governors;Annual Members</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Re-verified 2026-10-03 by local curl: the group page links the 7 Oct 2026 Group Board full pack (19MB PDF); the 5 Aug 2026 and 1 Apr 2026 group packs also verified, while the old QEH page has nothing after Sep 2025.</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -6967,13 +7071,39 @@
           <t>https://royalpapworth.nhs.uk/our-hospital/how-we-are-run/our-board-directors/board-directors-meetings</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Pattern A with accordions (static). The landing has a 'Minutes, agendas and papers' section with one collapsed accordion per meeting (e.g. 'Thursday 1 October 2026'), newest-first, Feb 2024 to present; meetings are monthly on the first Thursday. The accordions are only CSS-collapsed, so every link is in the static HTML and no clicking is needed. Recent meetings (Jul, Sep, Oct 2026) have one combined PDF titled e.g. 'Combined meeting and reference packs - 1 October 2026 (.PDF)' or '26-07-02 RPH Trust Board Part I - Combined Papers' at /download_file/view/&lt;id&gt;/937 (303 redirect to the PDF). Earlier meetings (e.g. Jan-Jun 2026) have NO combined pack, only individual 'Item NN.x ...' files at /download_file/&lt;id&gt;/937, so collect the items or treat the agenda as the marker. Read the date from the accordion heading or the YYMMDD/YYYYMMDD in the agenda filename. Some items are .docx. Skip 'Declarations of Interest', 'Conflicts of Interest', 'Glossary of terms' and the 'Minutes archive' section. Static curl works.</t>
+        </is>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Combined meeting and reference packs;Combined Papers;Part I;/download_file/view/;Item 00 Agenda</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Declarations of Interest;Conflict of Interest;Glossary of terms;Minutes archive;Part II</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Found 10 dated 2026 meeting accordions (8 Jan to 1 Oct 2026) with combined packs for 2 Jul, 3 Sep and 1 Oct 2026 (Oct pack 7.2MB) and individual item PDFs for earlier meetings.</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -7245,7 +7375,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>The current landing URL is correct; the ERR_CONNECTION_RESET on direct fetch and Playwright is a WAF/anti-bot block, not a moved page -- WebFetch (different infra) reaches it fine, so prefer plain static fetch/WebFetch and skip headless Playwright (also reset). The landing is an index of year links (2017-2026); no PDFs on it. Drill down: index -&gt; year page (e.g. /2026-board-of-directors-meetings/) lists meeting dates -&gt; each links to an /events/board-of-directors-meeting-DD-month-YYYY/ page -&gt; that event page holds the single 'Meeting papers' full-pack PDF. A scan must follow two hops.</t>
+          <t>The current landing URL is correct. cuh.nhs.uk has historically reset connections (ERR_CONNECTION_RESET) from datacenter IPs and headless Playwright; WebFetch (different infra) reaches it reliably and remains the recorded working route - skip headless Playwright. On 2026-10-03 local curl with a Chrome UA also worked (one TLS reset, curl exit 35, cleared on retry), so retry before falling back to WebFetch. The landing is an index of year links (2017-2026) with no PDFs on it. Drill down: index -&gt; year page (e.g. /2026-board-of-directors-meetings/) lists meeting dates -&gt; each links to an /events/board-of-directors-meeting-{D}-{month}-{YYYY}/ page -&gt; that event page holds the single full-pack PDF. Recent links have the form /documents/{id}/Item_00-_Board_held_in_public_-_{D}_{Mon}_{YYYY}.pdf, which 302-redirects to media.cuh.nhs.uk/documents/... A scan must follow two hops plus the redirect. Meetings are roughly quarterly (Mar, Jun, Sep, Dec).</t>
         </is>
       </c>
       <c r="J92" t="b">
@@ -7253,7 +7383,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>year sub-pages /board-of-directors-meetings/{YYYY}-board-of-directors-meetings/;event pages /events/board-of-directors-meeting-{DD}-{month}-{YYYY}/;'Full Pack' / 'Meeting papers' labels;meetings ~quarterly (Mar, Jun, Sep, Dec)</t>
+          <t>year sub-pages /board-of-directors-meetings/{YYYY}-board-of-directors-meetings/;event pages /events/board-of-directors-meeting-{D}-{month}-{YYYY}/;/documents/{id}/Item_00-_Board_held_in_public_-_{D}_{Mon}_{YYYY}.pdf (302 to media.cuh.nhs.uk);'Full Pack' / 'Meeting papers' labels</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7263,7 +7393,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7273,7 +7403,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via server-side WebFetch of the year page /board-of-directors-meetings/2026-board-of-directors-meetings/: quarterly 2026 meetings listed as /events/ pages (11 March, 10 June, 9 September, 9 December 2026). The landing index itself was ECONNRESET on every route this run, so go straight to the year page if the index refuses; the local connection-reset remains a WAF artefact, not a move.</t>
+          <t>Re-verified 2026-10-03 by local curl: 2026 year page lists events 11 Mar, 10 Jun, 9 Sep and 9 Dec 2026; the 9 Sep 2026 event page's Item_00-_Board_held_in_public_-_9_Sept_2026.pdf 302s to media.cuh.nhs.uk.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -7915,7 +8045,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Legacy ASP CMS but fully live and current. The landing /about/trustboard/index.asp lists forthcoming meetings and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp linking a single combined PDF at /about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf. All pages render statically -- no Playwright. To find the newest pack, read the landing for the latest YYYY_MM then hit that month's Combined_paper_pack.pdf. Papers carry a press embargo until after the meeting. Re-verified 2026-09-12 by browser-UA curl (200): landing and month dropdown intact, forthcoming meetings listed to 4 March 2027; the per-month /about/trustboard/YYYY_MM/ gateway pages still hold the combined pack, which is why the landing itself shows no PDFs.</t>
+          <t>Legacy ASP CMS but fully live and current; papers are now published as the BSW Hospitals Group Board. The landing /about/trustboard/index.asp lists forthcoming meetings (to 4 March 2027 as of 2026-10-03) and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp, and the PDFs sit only on those month pages, never on the landing. The old single-file name /documents/Combined_paper_pack.pdf is no longer used (404 for 2026_09). Recent months (2026_07 and 2026_09 confirmed) link two files: documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (the main pack) and documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Reading_Room.pdf. Scrape the PDF hrefs off each month page rather than guessing filenames. All pages render statically and plain browser-UA requests and WebFetch both work, so no Playwright is needed. To find the newest pack, read the landing for the latest YYYY_MM, then harvest that month page's PDF links. Papers carry a press embargo until after the meeting.</t>
         </is>
       </c>
       <c r="J101" t="b">
@@ -7923,17 +8053,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>/about/trustboard/YYYY_MM/index.asp per-meeting page;/about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf single combined pack;month dropdown enumerates all meetings</t>
+          <t>/about/trustboard/YYYY_MM/index.asp per-meeting page;/about/trustboard/YYYY_MM/documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf main pack;month dropdown enumerates all meetings</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>/about/trustboard/Archive/ (pre-2020);BSW Group Board packs on gwh.nhs.uk;pdffiller.com and other aggregator copies</t>
+          <t>/about/trustboard/Archive/ (pre-2020);BSW Group Board packs on gwh.nhs.uk;pdffiller.com and other aggregator copies;Reading_Room</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7943,7 +8073,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: month dropdown current to Thursday 3 September 2026, each month page linking a combined pack. no_papers_visible reflects that the PDFs sit one hop down, not on the landing.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl: the 2026_09 month page links 2026_09_03_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (200, 27.4MB) plus a Reading_Room PDF; the documented Combined_paper_pack.pdf name now 404s.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8075,7 +8205,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain.</t>
+          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works.</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -8093,7 +8223,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8103,7 +8233,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via server-side WebFetch: landing live with the Annual Public Meeting on 17 September 2026 and per-financial-year links into doclibrary-rcht (BoardMeetings2627.aspx through BoardMeetings2223.aspx) intact. Note the 2026-27 year link is currently wrapped in an Outlook safelinks redirect - unwrap the url= parameter before following it. Local 403 is a local-path block only.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl: BoardMeetings2627.aspx lists AgendaPacks for 7 May, July, extraordinary July and 3 Sep 2026 (AgendaPackTrustBoardPublic3September26.pdf), plus the 17 Sep 2026 Annual Public Meeting.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8150,12 +8280,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.somersetft.nhs.uk/about-us/trust-board-meetings/</t>
+          <t>https://www.somersetft.nhs.uk/about-us/about-us/our-leadership-and-governance/trust-board-sub-committees/trust-board-meetings/</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing under year headings ('2026 Board Papers', '2025 Board Papers', '2024 board papers') - no year tabs, no per-meeting sub-pages. Each entry links straight to a combined 'Boardbook' PDF in the WordPress media library at /about-us/wp-content/uploads/sites/148/YYYY/MM/. Latest confirmed 14 July 2026. Note two quirks: large meetings are occasionally split into PART 1 / PART 2 files (take both), and the odd entry links a .docx agenda rather than a PDF. Extraordinary meetings appear inline alongside ordinary ones. Static fetch works via server-side WebFetch; the local scan's read-timeout is a local-path artefact. Prefer filenames containing 'Boardbook'.</t>
+          <t>The old URL /about-us/trust-board-meetings/ now 301-redirects to /about-us/about-us/our-leadership-and-governance/trust-board-sub-committees/trust-board-meetings/ (stored 2026-10-03). Strategy: dated board-pack PDFs listed directly on the landing under year headings (2026, 2025, 2024 board papers), with no year tabs and no per-meeting sub-pages. Each entry links straight to a combined PDF in the WordPress media library at /about-us/wp-content/uploads/sites/148/YYYY/MM/, mostly named '...FINAL-Boardbook...'. Latest confirmed is 8 September 2026. Quirks: large meetings are often split into PART 1 / PART 2 files (May and Sep 2026; take both); upload folder month can precede the meeting month; not every filename contains 'Boardbook' (e.g. Jan 2026 '13-January-2026-Public-Board-Meeting-Final-for-website-reduced-size.pdf'); the odd entry links a .docx agenda instead of a PDF (19 Jun 2026 extraordinary). Extraordinary meetings appear inline alongside ordinary ones. Static fetch works via server-side WebFetch and local curl with a Chrome UA. Prefer filenames containing 'Boardbook' or 'Public-Board-Meeting'.</t>
         </is>
       </c>
       <c r="J104" t="b">
@@ -8173,7 +8303,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8183,7 +8313,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Verified 2026-08-15 via WebFetch: Trust board meetings page live with year-grouped Boardbook PDFs, latest 14 July 2026 under /about-us/wp-content/uploads/sites/148/2026/07/. The local read-timeout was a false positive.</t>
+          <t>Re-verified 2026-10-03 by local curl (301 to new path, 200, 155KB): latest pack Public-Board-Meeting-on-8-September-2026_FINAL-Boardbook_Part1-1.pdf plus Part2.</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -8253,7 +8383,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8263,7 +8393,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch, which reached the page cleanly this week: latest pack rduh-public-board-20260729-meeting-book-for-the-public-updated-20260729.pdf (29 July 2026), plus minutes and Vimeo recordings.</t>
+          <t>Re-verified 2026-10-03 via server-side WebFetch (archive.org route not needed this run): /media/ meeting packs for 28 Jan, 25 Mar, 27 May, 29 Jul and 30 Sep 2026; 25 Nov 2026 upcoming. Local requests get 403.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -8865,13 +8995,39 @@
           <t>https://www.oxleas.nhs.uk/board-papers/</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Pattern A (direct PDFs on landing, static). www.oxleas.nhs.uk/board-papers/ redirects to https://oxleas.nhs.uk/board-papers/, which lists one combined pack per public Trust Board meeting newest-first, 2019 to present (every two months: Jan, Mar, May, Jul, Sep, Nov). Link text is 'Trust Board papers - September 2026 [pdf] 5MB' (older: 'Board of Directors Full Board Papers &lt;Mon YYYY&gt;' or 'Board of Directors Part I papers &lt;Month&gt;'). URLs are /download/trust-board-papers-&lt;month&gt;-&lt;yyyy&gt;.pdf?ver=N&amp;doc=docm93jijm4n&lt;id&gt;.pdf. Only month and year are given, no exact meeting date. Skip occasional 'Additional paper' / 'Late Paper' items and .docx files. Packs are 3-12MB. Static curl works.</t>
+        </is>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Trust Board papers;Full Board Papers;Part I papers;docm93jijm4n</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Additional paper;Late Paper;.docx;livestream</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Found 5 2026 Trust Board packs (Jan to Sep 2026) and archive back to 2019; the September 2026 pack downloaded as a PDF.</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
@@ -8996,16 +9152,42 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.slam.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+          <t>https://slam.nhs.uk/trust-board</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Pattern A (direct PDFs on landing, static). The former DB URL www.slam.nhs.uk/about-us/trust-board/ 301-redirects to https://slam.nhs.uk/trust-board (stored as the canonical URL 2026-10-03). The page starts with board member bios (skip the ?letter= and ?consultant= links), then 'Board meeting dates 2026' as text, then 'Board Papers 20XX' sections. Each meeting has two links: the public board pack (e.g. 'Board Pack September 2026', 'July board pack', 'May Public Board Pack Final') and a 'Board Note for Observers' (a short PDF or .docx - exclude). URLs are /download/&lt;slug&gt;.pdf?ver=N&amp;doc=docm93jijm4n&lt;id&gt;.pdf (older /download.cfm?doc=...&amp;ver=). Titles give only month and year, though some slugs carry YYMMDD (260721-public-board-pack). Coverage 2018 to present, every two months. Papers posted about a week before each meeting. Packs are 5-12MB. Static curl works.</t>
+        </is>
+      </c>
+      <c r="J116" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Pack;Board papers;public-board-pack;docm93jijm4n</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Note for Observers;board-note-for-observers;.docx;letter=;consultant=</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Found 5 2026 public board packs (Jan to Sep 2026) and archive back to 2018; the September 2026 pack downloaded as a PDF.</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
@@ -9889,7 +10071,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Landing page is live and even loads via WebFetch (no WAF block observed). The page lists, per meeting date, a single combined 'Download meeting papers {Month YYYY}' PDF plus a 'final minutes' PDF; the combined agenda+papers pack is one file served from the media.gosh.nhs.uk/documents/ subdomain. Take the meeting-papers pack (filenames contain 'Trust_Board_agenda_and_papers_{DDMMYY}'), not the minutes. Older years have their own sub-pages (.../trust-board-papers-{YEAR}/).</t>
+          <t>Landing page is live and even loads via WebFetch (no WAF block observed). The page lists, per meeting date, a single combined 'Download meeting papers {Month YYYY}' PDF plus a 'final minutes' PDF; the combined agenda+papers pack is one file served from the media.gosh.nhs.uk/documents/ subdomain. Take the meeting-papers pack (filenames contain 'Trust_Board_agenda_and_papers_{DDMMYY}'), not the minutes. Older years have their own sub-pages (.../trust-board-papers-{YEAR}/). Re-verified 2026-10-03: the on-page hrefs are www.gosh.nhs.uk/documents/{id}/{file}.pdf which 302-redirect to media.gosh.nhs.uk/documents/, so follow redirects.</t>
         </is>
       </c>
       <c r="J128" t="b">
@@ -9907,7 +10089,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9917,7 +10099,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 26 dated packs listed, newest 'Download meeting papers June 2026' (18 June 2026, 6.1MB).</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 102KB): agenda-and-papers packs for 29 Jan, 18 Mar, 13 May, 18 Jun and 16 Jul 2026; 30 Sep 2026 papers not yet posted, next meeting 19 Nov 2026.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -10345,7 +10527,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10355,7 +10537,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: fiscal-year archive back to 2019/20, each meeting linking a combined pack via the /download_file/view/&lt;uuid&gt;/668 handler. no_papers_visible was a local-fetch false negative.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 155KB): 42 /download_file/view/&lt;uuid&gt;/668 'Agenda and papers' links; 2026/27 group lists 2 Apr, 4 Jun and 6 Aug 2026.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -10551,13 +10733,39 @@
           <t>https://www.newcastle-hospitals.nhs.uk/about/board-of-directors-2/board-of-directors-papers/</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Pattern A (direct PDFs on landing, static). The board-of-directors-papers page lists one combined pack per public Board of Directors meeting newest-first, covering roughly the last two years (Sep 2024 onward); older years are on the linked archive page /about/board-of-directors-2/board-of-directors-papers/board-of-directors-papers-archive/. Link text is e.g. 'Trust Public Board Papers 25 September 2026 (14.22MB PDF)', giving the exact meeting date. Files are /wp-content/uploads/YYYY/MM/Combined-Public-Bo(ar)D-...-Papers-DD-Month-YYYY-vN.pdf. Meetings every two months (Jan, Mar, May, Jul, Sep, Nov). Occasionally a separate 'Appendix' PDF sits under the same title; prefer the 'Combined' file and skip Appendix items. Packs are 10-18MB. Static curl works.</t>
+        </is>
+      </c>
+      <c r="J137" t="b">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Trust Public Board Papers;Combined-Public-Board-of-Directors;Combined-Public-BoD-Papers;/wp-content/uploads/</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>APPENDIX;Appendix;email-protection</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Found 5 combined 2026 public board packs (30 Jan to 25 Sep 2026) and 11 dated packs since Sep 2024 on the landing, plus an archive page; the 25 Sep 2026 pack downloaded as a PDF.</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
@@ -10687,7 +10895,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>South Tees and North Tees now run a single joint 'University Hospitals Tees' (UHT) group board, so the papers are GROUP packs published on the South Tees domain. The current /about/university-hospitals-tees/board-meetings/ landing is just a description page and shows no PDFs directly. The real archive is the resources filter /resources/?topic=board-of-directors, which lists 'Group Board of Directors Agenda - &lt;date&gt;' entries (7 May 2026, 5 Mar 2026, 8 Jan 2026, 6 Nov 2025, 3 Jul 2025...). Each entry is a per-meeting sub-page (e.g. /resources/group-board-of-directors-agenda-5-march-2026/) containing the direct combined papers PDF under /wp-content/uploads/{YYYY}/{MM}/. Crawler path: load the resources filter -&gt; follow each 'group-board-of-directors-agenda-{date}' sub-page -&gt; grab the /wp-content/uploads/.../Board-of-Directors-papers-*.pdf (or UHT-Board-Public-Papers-*.pdf) link. Static fetch sufficient. Prefer the single combined 'papers' PDF; filter committee/quality-assurance items.</t>
+          <t>South Tees and North Tees now run a single joint 'University Hospitals Tees' (UHT) group board, so the papers are GROUP packs published on the South Tees domain. The /about/university-hospitals-tees/board-meetings/ landing is just a description page with no PDFs; the real archive is the resources filter /resources/?topic=board-of-directors, which lists 'Group Board of Directors Agenda - &lt;date&gt;' entries (3 Sep 2026, 2 Jul 2026, 7 May 2026, 5 Mar 2026, 8 Jan 2026, 6 Nov 2025...). Each entry is a per-meeting sub-page (e.g. /resources/group-board-of-directors-agenda-3-september-2026/) containing the direct combined papers PDF under /wp-content/uploads/{YYYY}/{MM}/. Filename casing and wording vary (Board-of-Directors-papers-*.pdf, UHT-Board-Public-Papers-*.pdf, board-of-Directors-Public-papers-{d-month-yyyy}-v1.pdf), so match case-insensitively on 'papers' plus the date. Crawler path: resources filter -&gt; each 'group-board-of-directors-agenda-{date}' sub-page -&gt; the /wp-content/uploads/ PDF. Static fetch is sufficient (local curl with a Chrome UA works). Prefer the single combined 'papers' PDF; filter committee/quality-assurance items.</t>
         </is>
       </c>
       <c r="J139" t="b">
@@ -10695,7 +10903,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>/resources/group-board-of-directors-agenda-{date}/;/wp-content/uploads/{YYYY}/{MM}/Board-of-Directors-papers-{date}.pdf;/wp-content/uploads/{YYYY}/{MM}/UHT-Board-Public-Papers-{date}.pdf</t>
+          <t>/resources/group-board-of-directors-agenda-{date}/;/wp-content/uploads/{YYYY}/{MM}/Board-of-Directors-papers-{date}.pdf;/wp-content/uploads/{YYYY}/{MM}/UHT-Board-Public-Papers-{date}.pdf;/wp-content/uploads/{YYYY}/{MM}/board-of-Directors-Public-papers-{date}-v1.pdf</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10705,7 +10913,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10715,7 +10923,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Resources filter lists dated UHT group board agendas/papers and a confirmed 5 March 2026 papers PDF resolves on the southtees.nhs.uk domain.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): resources filter lists 'Group Board of Directors Agenda - 3 September 2026', whose sub-page links board-of-Directors-Public-papers-3-September-2026-v1.pdf.</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -10930,12 +11138,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/about/team/board/</t>
+          <t>https://www.cntw.nhs.uk/about-us/trust/our-board-and-governors</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>The old publications library (/about/publications/ and the ?filter_publication_type=344 filter, plus per-meeting /about/publications/board-papers-DATE/ pages) has been decommissioned and now returns hard 404s. The current canonical board landing is /about/team/board/ (title 'Board and Governors'), which loads cleanly via static fetch and lists the latest meeting packs (Jan 2026, April 2026, plus Council of Governors packs) as download links of the form /download_file/{uuid}/258 rather than direct .pdf URLs. The trust holds quarterly public board meetings; this page surfaces the most recent few packs, so follow each download_file link. Raw /wp-content/uploads/*.pdf files exist on the CDN but return 403 to bots behind the WAF — prefer the on-page download_file links. Prefer 'Board of Directors PUBLIC papers' over Council of Governors items.</t>
+          <t>The old publications library (/about/publications/, the ?filter_publication_type=344 filter and the per-meeting /about/publications/board-papers-DATE/ pages) was decommissioned and returns hard 404s. The former board landing /about/team/board/ now 301-redirects to /about-us/trust/our-board-and-governors (stored 2026-10-03), which loads cleanly via static fetch (local curl with a Chrome UA works). That page lists the latest meeting packs (Board of Directors Public Papers Jan 2026, April 2026, 'CNTW Board PUBLIC papers July 2026', plus Council of Governors packs) as /download_file/{uuid}/258 links, which 307-redirect to the real file under /application/files/{n}/{n}/{n}/CNTW_Board_PUBLIC_papers_{Month}_{YYYY}.pdf - follow redirects. The trust holds quarterly public board meetings (Jan/Apr/Jul/Oct) and the page surfaces only the most recent few packs. Raw /wp-content/uploads/*.pdf files have previously returned 403 to bots behind the WAF; prefer the on-page download_file links. Prefer 'Board of Directors PUBLIC papers' over Council of Governors items.</t>
         </is>
       </c>
       <c r="J142" t="b">
@@ -10943,7 +11151,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>/download_file/;Board of Directors;PUBLIC papers;/wp-content/uploads/;Month-YYYY</t>
+          <t>/download_file/{uuid}/258;/application/files/;Board of Directors Public Papers;Board PUBLIC papers {Month} {YYYY}</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10953,7 +11161,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10963,7 +11171,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>/about/team/board/ lists 'CNTW Board of Directors Public Papers Jan 2026' and 'April 2026' (posted 17/06/2026) as download_file links; old publications pages return genuine 404.</t>
+          <t>Re-verified 2026-10-03: old URL 301s to /about-us/trust/our-board-and-governors (200, 96KB); latest board pack 'CNTW Board PUBLIC papers July 2026' (download_file link 307s to /application/files/.../CNTW_Board_PUBLIC_papers_July_2026.pdf).</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -11147,7 +11355,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
+          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11935,7 +12143,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11945,7 +12153,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Route re-check 2026-09-26: server-side WebFetch again received the documented synthetic HTTP 502, confirming the ClaudeBot User-Agent denylist on this edge is still in force (it is a UA denylist, not an outage). Last content confirmation stands from 2026-09-12 browser-UA curl (200, 293KB, 78 /download_file/ links, meeting dates 4 March 2026 to 2 September 2026 and on to 3 March 2027) - retry with a browser UA rather than treating 502 as down.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 293KB): 77 /download_file/view/{id}/875 links; newest meeting with papers 2 Sep 2026, upcoming dates to 3 Mar 2027.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12183,7 +12391,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12193,7 +12401,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: latest Board of Directors public bundle for 05 August 2026 under /media/board/Papers/2026/. no_papers_visible was a local-fetch false negative.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 143KB): four /media/board/Papers/2026/ public bundles (Feb, Apr, Jun, Aug 2026).</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12695,7 +12903,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12705,7 +12913,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: latest 'Meeting in Public 03.09.2026' compressed pack under /wp-content/uploads/2026/09/. Local 403 is a local-path block only.</t>
+          <t>Re-verified 2026-10-03 via server-side WebFetch (local curl 403): Meeting-in-Public PDFs for 7 May, 2 Jul and 3 Sep 2026; next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -12841,7 +13049,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12851,7 +13059,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: landing carries the current 'September 2026 board papers' pack (26.67MB) plus the acronyms glossary, with older meetings under Previous board papers.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 54KB): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack; older packs in the navigate/758/9379 folder (the expected thin landing that trips papers_partial).</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13001,7 +13209,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13011,7 +13219,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch, which reached the page this week despite the previously recorded Cloudflare 403: latest 'Meeting Book PUBLIC Board Of Directors 16.7.26' at /media/ccrbvx33/, archive back to 2021.</t>
+          <t>Re-verified 2026-10-03 via server-side WebFetch (local curl 403): the 'Board papers and publications' accordion lists meeting books for 26 Mar, 21 May and 16 Jul 2026 under /media/; no September 2026 book yet.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13251,7 +13459,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>URL PATCHED 2026-07-30: LHCH joined the NHS University Hospitals of Liverpool Group in October 2025 and no longer holds its own board in public - the old lhch.nhs.uk/board-of-directors-meetings page is now a historic archive whose own dated packs stop at 23 September 2025 and which links out to the group board for 2026. The live board is the single UHLG Group Board covering LUHFT, LWH and LHCH (it meets in the LHCH conference room and carries LHCH's integrated performance report), so RBQ now shares this URL with REM and REP - dedupe logic must tolerate three ODS codes on one landing, and pack analysis should be attributed to all three. Strategy: the landing holds a 'Board papers' document-library table of YEAR FOLDERS - 2026 at /navigate/4487/21268, 2025 at /navigate/4487/15006, 2024 at /navigate/4487/9744, plus legacy 'LUHFT archive' (17796) and 'LWH archive' (17800). Inside a year folder, collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}'; those URLs carry no date and no .pdf extension and 303-redirect before serving, so take the date from the anchor text and follow redirects. Future meetings appear as event pages under /about-us/events/details?occurrenceID=... . Contrary to the older REM/REP notes the year folders are NOT JS-rendered - plain curl with a Chrome User-Agent returns fully server-rendered HTML containing every download_file anchor; the only obstacle is a User-Agent WAF that 403s WebFetch and default agents, so Playwright is optional. Bi-monthly: Jan, Mar, May, Jul, Sep, Nov.</t>
+          <t>URL PATCHED 2026-07-30: LHCH joined the NHS University Hospitals of Liverpool Group in October 2025 and no longer holds its own board in public. The old lhch.nhs.uk/board-of-directors-meetings page is now a historic archive whose dated packs stop at 23 September 2025 and which links out to the group board for 2026. The live board is the single UHLG Group Board covering LUHFT, LWH and LHCH (it meets in the LHCH conference room and carries LHCH's integrated performance report). RBQ therefore shares this URL with REM and REP: dedupe logic must tolerate three ODS codes on one landing, and pack analysis should be attributed to all three. Strategy: the landing holds a 'Board papers' document-library table of YEAR FOLDERS (2026 at /navigate/21268/4487, 2025 at /navigate/15006/4487, 2024 at /navigate/9744/4487) plus legacy 'LUHFT archive' (17796) and 'LWH archive' (17800). Inside a year folder, collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}'. The id is usually numeric but can be a UUID (the 17 Sep 2026 pack is /download_file/78f03ac9-.../423). These URLs carry no date and no .pdf extension and 303-redirect before serving, so take the date from the anchor text and follow redirects. Most meetings also have a separate 'UHLG Board of Directors Public Information Pack - {date}'; take the 'Public Pack', not the 'Public Information Pack'. Future meetings appear as event pages under /about-us/events/details?occurrenceID=... The year folders are NOT JS-rendered: plain curl with a Chrome User-Agent returns fully server-rendered HTML with every download_file anchor. The only obstacle is a User-Agent WAF that 403s WebFetch and default agents, so Playwright is optional. Meets bi-monthly: Jan, Mar, May, Jul, Sep, Nov.</t>
         </is>
       </c>
       <c r="J175" t="b">
@@ -13269,7 +13477,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13279,7 +13487,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Group board landing confirmed HTTP 200 (title 'Group Board meetings :: NHS University Hospitals of Liverpool Group'); 16 Jul 2026, 14 May 2026, 12 Mar 2026 and 15 Jan 2026 UHLG public packs verified as live PDFs, the July pack agenda naming LHCH explicitly.</t>
+          <t>Re-verified 2026-10-03 by local Chrome-UA curl (200): the 2026 folder lists 'UHLG Board of Directors Public Pack - 17 September 2026' (UUID download_file id) alongside the Jan, Mar, May and Jul 2026 packs.</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -13339,7 +13547,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move. Confirmed 2026-09-05 by browser-UA curl (200, 74KB). IMPORTANT STRUCTURE NOTE: /publications_type/board-papers/ is a PAGINATED WordPress archive - page 1 carries only the newest pack and older ones sit at /publications_type/board-papers/page/2/, /page/3/ and so on. A crawler that reads page 1 only will see a single PDF and wrongly conclude the archive is thin (this is the recurring papers_partial false positive). Follow the pagination links. Newest pack on this run was Trust-board-meeting-2nd-April-2026.pdf; nothing later than 2 April 2026 was published yet. Re-verified 2026-09-12: pagination confirmed working (page 1, /page/2/ and /page/3/ each return one dated pack), but the newest pack is STILL Trust-board-meeting-2nd-April-2026.pdf, unchanged since the 2026-09-05 run - so the thin listing is now a genuine publication gap on top of the pagination quirk, not just a crawler artefact. The legacy Concrete5 listing at /about-us/our-board/publications now 404s and /about/trust/board/meeting/ carries no PDFs, so there is no alternate location holding the missing June/August packs.</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move. Confirmed 2026-09-05 by browser-UA curl (200, 74KB). IMPORTANT STRUCTURE NOTE: /publications_type/board-papers/ is a PAGINATED WordPress archive - page 1 carries only the newest pack and older ones sit at /publications_type/board-papers/page/2/, /page/3/ and so on. A crawler that reads page 1 only will see a single PDF and wrongly conclude the archive is thin (this is the recurring papers_partial false positive). Follow the pagination links. Newest pack on this run was Trust-board-meeting-2nd-April-2026.pdf; nothing later than 2 April 2026 was published yet. Re-verified 2026-09-12: pagination confirmed working (page 1, /page/2/ and /page/3/ each return one dated pack), but the newest pack is STILL Trust-board-meeting-2nd-April-2026.pdf, unchanged since the 2026-09-05 run - so the thin listing is now a genuine publication gap on top of the pagination quirk, not just a crawler artefact. The legacy Concrete5 listing at /about-us/our-board/publications now 404s and /about/trust/board/meeting/ carries no PDFs, so there is no alternate location holding the missing June/August packs. Update 2026-10-03: the publication gap described above has CLEARED - page 1 now carries the 3 September 2026 Trust Board pack (wp-content/uploads/2026/09/Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf). The pagination guidance still applies.</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -13357,7 +13565,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13367,7 +13575,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: paginated publications_type archive, page 1 currently showing the 23 June 2026 Extraordinary Trust Board pack. The single-pack-per-page layout is what trips the papers_partial heuristic.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 75KB): page 1 carries the 3 September 2026 Trust Board pack under /wp-content/uploads/2026/09/.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -13911,7 +14119,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13921,7 +14129,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 18 dated meetings, newest /media/234524/PAPERS-Board-of-Directors-21st-July-2026-min.pdf.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): latest entry 'Agenda and Papers - September 2026' (PAPERS-Board-of-Driectors-29th-September-2026.pdf), with separate August 2026 IPR Part 1/2 files.</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
@@ -14107,7 +14315,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages. Confirmed 2026-09-05 by browser-UA curl (200, 102KB): packs are /download_file/{id}/1439 handler links, newest 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Nothing later than April 2026 was on the page this run - worth re-checking rather than assuming a fetch fault. Re-verified 2026-09-12 by browser-UA curl (200, 102KB): 37 /download_file/&lt;id&gt;/1439 links with dated labels through 03.09.2026, so the April-2026 ceiling flagged last run has cleared and publication is current.</t>
+          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages. Confirmed 2026-09-05 by browser-UA curl (200, 102KB): packs are /download_file/{id}/1439 handler links, newest 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Nothing later than April 2026 was on the page this run - worth re-checking rather than assuming a fetch fault. Re-verified 2026-09-12 by browser-UA curl (200, 102KB): 37 /download_file/&lt;id&gt;/1439 links with dated labels through 03.09.2026, so the April-2026 ceiling flagged last run has cleared and publication is current. Update 2026-10-03: the newest packs use UUID-style handlers (/download_file/&lt;uuid&gt;/1439) while older entries stay numeric, so match /download_file/[^/]+/1439. Latest pack 'Board of Directors Meeting Papers - 01 10 2026'.</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -14115,7 +14323,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Label 'Board of Directors ... Meeting Papers/Pack - DD.MM.YYYY';PDF hrefs /download_file/&lt;id&gt;/1439;monthly public board cadence, first Thursday;packs are large single PDFs (4-20MB)</t>
+          <t>Label 'Board of Directors ... Meeting Papers/Pack - DD.MM.YYYY';PDF hrefs /download_file/&lt;id-or-uuid&gt;/1439;monthly public board cadence, first Thursday;packs are large single PDFs (4-20MB)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14125,7 +14333,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14135,7 +14343,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: dated Board of Directors public meeting packs listed via numeric /download_file/&lt;id&gt;/1439 links, archive spanning 2020-2026.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 102KB): newest packs 01.10.2026 and 03.09.2026 at the top, 2026 packs back to 05.03.2026.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14205,7 +14413,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14215,7 +14423,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Verified 2026-08-22: whh.nhs.uk and bridgewater.nhs.uk both 301 to the North Cheshire and Mersey board page; 40+ dated packs listed, latest trust-board-agenda-and-papers-5-august-2026.pdf.</t>
+          <t>Re-verified 2026-10-03 by local curl (200): the page already lists the upcoming 7 October 2026 pack (trust-board-agenda-and-papers-7-october-2026.pdf), after the 5 August 2026 pack.</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -14275,7 +14483,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Cloudflare blocks WebFetch (403) so Playwright is needed. The original /board URL is correct — it is the 'Board summaries' index listing each meeting (e.g. 27 May 2026, 25 Mar 2026, 28 Jan 2026) as links to per-meeting HTML summary pages (some via short slugs like /mar26, /boardnov25). The /board landing page itself has NO PDFs; you must open each board-summary page, which contains a single 'Board agenda pack' link to the full PDF hosted on-domain at /application/files/{path}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf. Crawl /board, follow each summary link, scrape the agenda-pack PDF. Re-verified 2026-09-05: Cloudflare refused the first attempt but a browser-UA request with --retry got 200 (97KB), listing board-summary pages including board-summary-wednesday-29-july-2026 and board-summary-may-27-2026 (some via short slugs such as /mar26). Retry with a browser UA before reaching for Playwright.</t>
+          <t>Cloudflare blocks WebFetch (403) so Playwright is needed. The original /board URL is correct — it is the 'Board summaries' index listing each meeting (e.g. 27 May 2026, 25 Mar 2026, 28 Jan 2026) as links to per-meeting HTML summary pages (some via short slugs like /mar26, /boardnov25). The /board landing page itself has NO PDFs; you must open each board-summary page, which contains a single 'Board agenda pack' link to the full PDF hosted on-domain at /application/files/{path}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf. Crawl /board, follow each summary link, scrape the agenda-pack PDF. Re-verified 2026-09-05: Cloudflare refused the first attempt but a browser-UA request with --retry got 200 (97KB), listing board-summary pages including board-summary-wednesday-29-july-2026 and board-summary-may-27-2026 (some via short slugs such as /mar26). Retry with a browser UA before reaching for Playwright. Re-verified 2026-10-03: browser-UA curl with retries AND WebFetch both got 403 this run, but local headless Playwright with a real Chrome UA loaded /board (200) - board summaries for 28 Jan, 25 Mar (/mar26), 27 May, 29 Jul and 30 Sep 2026 (/sept26). The pack filename pattern has changed: the 30 Sep 2026 pack is PUBLIC_Agenda_Pack_BoD_30_09_26_v2.pdf (PUBLIC_Agenda_Pack_BoD_{DD_MM_YY}_v{n}.pdf) rather than PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf, so match on 'Agenda_Pack' generally.</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -14283,7 +14491,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>/application/files/{ids}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf;PUBLIC_BoD_Agenda_Pack;board-summary-{month}-{day}-{year}</t>
+          <t>/application/files/{ids}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf;PUBLIC_BoD_Agenda_Pack;board-summary-{month}-{day}-{year};PUBLIC_Agenda_Pack_BoD_{DD_MM_YY}_v{n}.pdf (from Sep 2026);Agenda_Pack</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14293,7 +14501,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14303,7 +14511,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 by search-index evidence: the /board summaries index and its short per-meeting slugs are live (e.g. /mar26 for 25 March 2026). Cloudflare still 403s both local fetch and WebFetch.</t>
+          <t>Re-verified 2026-10-03 via local headless Playwright (curl and WebFetch 403): /sept26 summary links the 30 Sep 2026 PUBLIC_Agenda_Pack_BoD_30_09_26_v2.pdf.</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14383,7 +14591,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
+          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14517,7 +14725,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-09-26: URL still resolves with no redirect, but both routes tried from this session were refused - server-side WebFetch returned an empty body and the local browser-UA path stayed on the Incapsula/hCaptcha shell. Treat as a routing block, not a withdrawal of papers; the previously-recorded working routes stand and should be tried first.</t>
+          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15201,17 +15409,17 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: landing loads and lists the next meeting (5 November 2026), but the Document Library Pro paper tables are serverSide AJAX and render empty to any static fetch - browser render still required.</t>
+          <t>Re-verified 2026-10-03: the documented admin-ajax dlp_load_posts recipe still returns the archive without nonce or cookie (26 rows, newest 'SCAS public Board papers - 3 September 2026'); next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (two connection resets, third try 200, 48KB): newest pack /documents/518-board-paper-24-september-2026/file.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 48KB; the validator's connection reset is the usual intermittent WAF): newest pack /documents/518-board-paper-24-september-2026/file, no later pack yet.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 99KB): dropdown lists 16 Sep, 23 Jul, 9 Jul and 14 May 2026; POST ddselect=15365 redirected to /download/meetings-in-public/meeting-papers-16-september-2026/ (18.8MB pack).</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 99KB): 'Meeting papers' dropdown lists 16 Sep, 23 Jul, 9 Jul and 14 May 2026; forthcoming meetings 12 Nov 2026 and 21 Jan 2027.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The /meetings page is an overview; the true archive is /board-meetings which lists every Trust Board meeting back to 2013 as month+year links (e.g. /board-meetings/3617-trust-board-3rd-june-2026). Each meeting page renders a numbered table of Agenda + Paper PDFs. Crucially the PDFs are hosted on the sister domain www.ashfordstpeters.info under /images/board-papers/YYYY-MM-DD/ (note .info not .nhs.uk). Static WebFetch works fine, no WAF; crawl /board-meetings, follow each meeting slug, scrape .info PDF links.</t>
+          <t>The /meetings page is an overview; the true archive is /board-meetings which lists every Trust Board meeting back to 2013 as month+year links (e.g. /board-meetings/3617-trust-board-3rd-june-2026). Each meeting page renders a numbered table of Agenda + Paper PDFs. Crucially the PDFs are hosted on the sister domain www.ashfordstpeters.info under /images/board-papers/YYYY-MM-DD/ (note .info not .nhs.uk). Static WebFetch works fine, no WAF; crawl /board-meetings, follow each meeting slug, scrape .info PDF links. Re-verified 2026-10-10: local browser-UA curl was refused with a generic 75KB '403 - Forbidden' page (the same page came back the same morning from airedale-trust, royalcornwallhospitals and swpboard, so it looks like a shared WAF reacting to the scan burst) while server-side WebFetch reached the page normally. On a local 403 try WebFetch before concluding anything; do not repoint the URL.</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 91KB): /board-meetings lists 2026 meetings up to 23 September 2026, whose page carries 45 ashfordstpeters.info/images/board-papers/2026-09-23/ PDFs.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): /board-meetings lists 2026 meetings through Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local curl (200, 272KB): newest pack board-of-directors-meeting-pack-01.10.26.pdf (1 October 2026) under september2026/, plus the 28 Jul and 4 Jun 2026 packs.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 266KB; validator's SSL error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/, plus the 28 Jul and 4 Jun 2026 packs.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pattern A (dated PDFs on landing) / F (wrong-url-fixed). Old DB url (/about-us/board-of-directors/) is just the board membership page; its one-click child /about-us/board-of-directors/board-meetings/ lists the combined bi-monthly 'Board Meeting Papers - [Month Year]' PDFs directly on the page (hosted under /media/...). No per-meeting sub-pages or year archives - all current-year and prior PDFs are inline. Crawler: load this page and harvest the dated 'Board Meeting Papers - Month Year' PDF links directly.</t>
+          <t>Pattern A (dated PDFs on landing). /about-us/board-of-directors/board-meetings/ lists the combined bi-monthly 'Board Meeting Papers - [Month Year]' PDFs directly on the page (hosted under /media/&lt;hash&gt;/..., e.g. board-meeting-papers-october-2026-v2.pdf); no per-meeting sub-pages or year archives - current-year and prior PDFs are inline. Static fetch works (plain curl 200, no WAF). Crawler: load this page and harvest the dated 'Board Meeting Papers - Month Year' PDF links directly; a '-v2' suffix marks a re-issued pack, prefer the highest version. Refreshed 2026-10-10: newest pack October 2026.</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>page lists direct combined board-meeting-papers PDFs through June 2026 (e.g. 0-board-meeting-papers-v3-june-2026.pdf, april-2026, february-2026).</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 50KB): inline 'Board Meeting Papers - October 2026' (v2, 18.5MB) plus Aug, Jun, Apr and Feb 2026 packs under /media/.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward 2026/27 timetable (12 Feb, 9 Apr, 11 Jun, 13 Aug, 8 Oct, 10 Dec 2026, 11 Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The papers sit three hops down in a Concrete CMS document library: landing -&gt; 'Previous meetings' / '2025' / '2026' year folder (/navigate/{folderId}/53923; 2026 = /navigate/13049/53923) -&gt; one dated folder per meeting (e.g. '13 August 2026' = /navigate/13654/53923) -&gt; numbered per-item papers ('1) Public Board of Directors Agenda - 13 August 2026', '2.1) Chief Executive Report...') served as /download_file/{uuid}/382 links with no .pdf extension. There is no single combined pack, so collect every item in the meeting folder and take titles from the anchor/table text. Past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch and, as of 2026-10-03, also via local curl with a Chrome UA (the page carries an 'incapsula' string but serves normally). The validator's local SSL-verify failure is a local-path artefact, not a dead page.</t>
+          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward 2026/27 timetable (12 Feb, 9 Apr, 11 Jun, 13 Aug, 8 Oct, 10 Dec 2026, 11 Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The papers sit three hops down in a Concrete CMS document library: landing -&gt; 'Previous meetings' / '2025' / '2026' year folder (/navigate/{folderId}/53923; 2026 = /navigate/13049/53923) -&gt; one dated folder per meeting (e.g. '13 August 2026' = /navigate/13654/53923) -&gt; numbered per-item papers ('1) Public Board of Directors Agenda - 13 August 2026', '2.1) Chief Executive Report...') served as /download_file/{uuid}/382 links with no .pdf extension. There is no single combined pack, so collect every item in the meeting folder and take titles from the anchor/table text. Past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch and, as of 2026-10-03, also via local curl with a Chrome UA (the page carries an 'incapsula' string but serves normally). The validator's local SSL-verify failure is a local-path artefact, not a dead page. 2026-10-10: the 8 October 2026 meeting folder (/navigate/13814/53923) is now present in the 2026 year folder.</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local curl (200): the 2026 folder holds meeting folders 12 Feb, 9 Apr, 11 Jun and 13 Aug 2026 with numbered download_file items; 8 Oct 2026 not yet posted.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200): the 2026 folder (/navigate/13049/53923) now holds meeting folders 12 Feb, 9 Apr, 11 Jun, 13 Aug and 8 October 2026 (/navigate/13814/53923).</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 43KB; WebFetch got ECONNRESET): combined public board packs for 2 Apr, 4 Jun, 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 44KB; validator saw a connection reset): combined public board packs for 2 Apr, 4 Jun, 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>URL PATCHED 2026-07-30: the site dropped the /about-us/ prefix in favour of /about/, so the old /about-us/our-board/previous-board-meetings/ path now genuinely 404s (reproduced independently, not a WAF artefact - Google still surfaces the dead /about-us/ URLs, so ignore stale search hits). Strategy: the landing /about/our-board/board-meetings/ lists UPCOMING dates (papers appear the Friday before) plus the ~11 most recent past meetings; the full back-catalogue from 2014 is one long page at /about/our-board/board-meetings/board-meeting-archive/. Each past meeting is its own page at /board-meeting-archive/trust-board-meeting-&lt;month&gt;-&lt;year&gt;/ with a 'Meeting downloads' block - but DO NOT construct those slugs, they are inconsistent (March 2026 is trust-board-meeting-march_2026 with an underscore; May 2023 carries a -2 suffix). Scrape hrefs instead. IMPORTANT: on the two most recent meeting pages the Elementor PDF buttons render with NO href attribute at all, so a link-scraper finds zero PDFs for the newest meetings; the reliable route is the WordPress REST media API at /wp-json/wp/v2/media?search=PUBLIC-TRUST-BOARD&amp;per_page=100&amp;orderby=date&amp;order=desc&amp;_fields=source_url,date. Server-rendered WordPress, no JS needed, but the edge resets TLS connections on roughly 60-90% of attempts (ECONNRESET / curl exit 35) and WebFetch fails every time; use a browser User-Agent with a 10-15 attempt retry loop, or the r.jina.ai reader proxy as a fallback. Upload folder does not match meeting month (Jan and Mar 2026 briefings both sit under /uploads/2026/04/). Bi-monthly cadence: Jan, Mar, May, Jul, Sep, Nov, second Thursday. FETCH WARNING (2026-08-01): every route tried this run (requests, local Playwright, browser-UA curl, server-side WebFetch) was connection-reset on /about/our-board/ paths even though the site root answered 200 -- the domain sits behind DDoSX bot mitigation. The page itself is live (Google index shows the landing and a July 2026 meeting archive page). Retry later or from another egress; do not repoint the URL on a reset alone.</t>
+          <t>URL PATCHED 2026-07-30: the site dropped the /about-us/ prefix in favour of /about/, so the old /about-us/our-board/previous-board-meetings/ path now genuinely 404s (reproduced independently, not a WAF artefact - Google still surfaces the dead /about-us/ URLs, so ignore stale search hits). Strategy: the landing /about/our-board/board-meetings/ lists UPCOMING dates (papers appear the Friday before) plus the ~11 most recent past meetings; the full back-catalogue from 2014 is one long page at /about/our-board/board-meetings/board-meeting-archive/. Each past meeting is its own page at /board-meeting-archive/trust-board-meeting-&lt;month&gt;-&lt;year&gt;/ with a 'Meeting downloads' block - but DO NOT construct those slugs, they are inconsistent (March 2026 is trust-board-meeting-march_2026 with an underscore; May 2023 carries a -2 suffix). Scrape hrefs instead. IMPORTANT: on the two most recent meeting pages the Elementor PDF buttons render with NO href attribute at all, so a link-scraper finds zero PDFs for the newest meetings; the reliable route is the WordPress REST media API at /wp-json/wp/v2/media?search=PUBLIC-TRUST-BOARD&amp;per_page=100&amp;orderby=date&amp;order=desc&amp;_fields=source_url,date. Server-rendered WordPress, no JS needed, but the edge resets TLS connections on roughly 60-90% of attempts (ECONNRESET / curl exit 35) and WebFetch fails every time; use a browser User-Agent with a 10-15 attempt retry loop, or the r.jina.ai reader proxy as a fallback. Upload folder does not match meeting month (Jan and Mar 2026 briefings both sit under /uploads/2026/04/). Bi-monthly cadence: Jan, Mar, May, Jul, Sep, Nov, second Thursday. FETCH WARNING (2026-08-01): every route tried this run (requests, local Playwright, browser-UA curl, server-side WebFetch) was connection-reset on /about/our-board/ paths even though the site root answered 200 -- the domain sits behind DDoSX bot mitigation. The page itself is live (Google index shows the landing and a July 2026 meeting archive page). Retry later or from another egress; do not repoint the URL on a reset alone. Refreshed 2026-10-10: the edge answered plain browser-UA curl first time (200, 104KB) with no reset, and the newest (10 Sep 2026) meeting block DID carry a real href to /wp-content/uploads/2026/09/FINAL-PUBLIC-TRUST-BOARD-PACK-10.09.26-2.pdf - so try the landing's hrefs first and fall back to the REST media API only when the buttons render without href.</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Re-checked 2026-08-08: URL unchanged and confirmed live - search index returns /about/our-board/board-meetings/ as the current page plus a board-meeting-archive child holding the July 2026 meeting, and a Jan 2026 pack at /wp-content/uploads/2026/01/. Every fetch route reset at the network layer today (requests, local Playwright, WebFetch), so this is a fetch block, not a stale URL; no change made.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200 first try, 104KB): landing's September 2026 meeting block links FINAL-PUBLIC-TRUST-BOARD-PACK-10.09.26-2.pdf directly plus archive pages for Jul, May, Mar and Jan 2026.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; September contains 'Board of Directors meeting pack, September 2026.pdf'.</t>
+          <t>Re-verified 2026-10-10 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; September contains 'Board of Directors meeting pack, September 2026.pdf' plus a background-reading pack.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.sath.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.sath.nhs.uk/about-us/trust-information/board-papers/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (348 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>URL PATCHED 2026-10-10: the old /about-us/board-papers/ path now 301s to /about-us/trust-information/board-papers/ (same page, same content). Strategy: one very long landing page listing every meeting back to 2017 with three files per meeting - '00 ... Agenda', '01 ... COMBINED PAPERS' (the main pack) and '02 ... INFORMATION PACK' - under /wp-content/uploads/YYYY/MM/. Many 2026 meetings are 'Boards in Common' (BiC) meetings in public shared with the partner trust; their '01 ... BOARDS IN COMMON ... COMBINED PAPERS' file is the board pack to use. Static fetch works (plain curl 200, no WAF). Harvest the '01' combined-papers PDF per date; skip the '00' agenda-only and '02' information-pack files and the stand-alone committee summaries and BAF documents. Pattern A. Refreshed 2026-10-10: newest pack 8 October 2026.</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>01 PUBLIC BOARD DD.MM.YY COMBINED PAPERS;BOARDS IN COMMON MEETING in PUBLIC ... COMBINED PAPERS;/wp-content/uploads/YYYY/MM/</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>02 ... INFORMATION PACK;00 ... Agenda;Committee Summary;Board Assurance Framework;Minutes only</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=348, year_archives=2, meeting_subpages=1.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 543KB after the 301): ~1,800 PDF links; newest 01-PUBLIC-BOARD-08.10.26-COMBINED-PAPERS.pdf and 02 information pack under /wp-content/uploads/2026/10/, with Aug, Jul, May, Mar and Jan 2026 before it.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via server-side WebFetch (archive.org route not needed this run): agenda and papers /media/&lt;id&gt;/ links for 28 Jan, 29 Apr and 22 Jul 2026. Local requests still get the 403 WAF page.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (archive.org route not needed this run): agenda and papers /media/&lt;id&gt;/ links for 28 Jan, 29 Apr and 22 Jul 2026 (papers 7.9MB). Local requests still get the 403 WAF page.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Current URL is live and correct. The 'Our Board and Leadership' page uses a year-tabbed interface (2018-2026) listing each Public Board of Directors meeting; clicking a date reveals a single combined 'papers' PDF hosted in /wp-content/uploads/YYYY/MM/. Crawl the landing page, harvest all .pdf links under wp-content/uploads, and match on date or 'Board-of-Directors'/'Board' in filename. WebFetch works fine here (no WAF). Original failure was transient.</t>
+          <t>Current URL is live and correct. The 'Our Board and Leadership' page uses a year-tabbed interface (2018-2026) listing each Public Board of Directors meeting; clicking a date reveals a single combined 'papers' PDF hosted in /wp-content/uploads/YYYY/MM/. Crawl the landing page, harvest all .pdf links under wp-content/uploads, and match on date or 'Board-of-Directors'/'Board' in filename. WebFetch works fine here (no WAF). Original failure was transient. Re-verified 2026-10-10: local browser-UA curl got the generic '403 - Forbidden' page (also seen on ashfordstpeters, royalcornwallhospitals and swpboard that morning) while WebFetch rendered the page and its 2026 packs normally - so a WAF does exist in front of the site; try WebFetch on a local 403.</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 292KB): five 2026 combined packs under /wp-content/uploads/2026/, newest 2 September 2026.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): combined packs 6 May, 1 Jul and 2 Sep 2026 under /wp-content/uploads/2026/; next meeting 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (29 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page, one per meeting, as Drupal /sites/default/files/YYYY-MM/Board of Directors (Public) DD.MM.YY Binder.pdf links (dozens back to earlier years). Static fetch works (plain curl 200, no WAF). Prefer the 'Binder' file for each date (an 'Updated' / 'Final update' variant supersedes the original); treat stand-alone items such as 'Safe staffing and establishments' addenda as supplementary. Pattern A. Refreshed 2026-10-10: newest binder 2 September 2026.</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -5783,17 +5783,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Board of Directors (Public) DD.MM.YY Binder;/sites/default/files/YYYY-MM/</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Addendum;Safe staffing;Minutes only;Council of Governors</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=29, year_archives=0, meeting_subpages=0.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 83KB): 'Board of Directors (Public) DD.MM.YY Binder' PDFs for 16 Jan, 6 Mar, 8 May, 1 Jul and 2 Sep 2026 under /sites/default/files/YYYY-MM/.</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; static HTML holds every enclosure PDF for Jan-Jul 2026 plus the 8 September 2026 agenda; WebFetch got 403.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; static HTML now holds the 8 September 2026 agenda plus its lettered papers (A-W) alongside Jan-Jul 2026.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 104KB): five BoardPapers/2026/Combined_..._WEBSITE.pdf packs (Jan, Mar, May, Jul, 10 Sep 2026).</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 104KB): Combined_..._WEBSITE.pdf packs under BoardPapers/2026/ including 9 July and 10 September 2026.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Current URL is live and correct; reported 'broken' was transient/WAF. WordPress site under About us &gt; How we're run &gt; Our Trust Board &gt; Meetings and papers. Page archives meetings chronologically back to 2008, each with agenda+papers PDF and minutes PDF hosted at /wp-content/uploads/YYYY/MM/. Latest pack 29 September 2026 (re-verified 2026-10-03). Retry WebFetch on 403; no JS rendering needed.</t>
+          <t>Current URL is live and correct; reported 'broken' was transient/WAF. WordPress site under About us &gt; How we're run &gt; Our Trust Board &gt; Meetings and papers. Page archives meetings chronologically back to 2008, each with agenda+papers PDF and minutes PDF hosted at /wp-content/uploads/YYYY/MM/. Latest pack 29 September 2026 (re-verified 2026-10-03). Retry WebFetch on 403; no JS rendering needed. Note (2026-10-10): the Sucuri edge now returns Content-Encoding: br even when the client sends Accept-Encoding: identity, so a fetcher without brotli support sees ~24KB of binary and zero links - decode brotli (or use WebFetch, which handled it) rather than treating the page as empty.</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 477KB): 13 /wp-content/uploads/2026 PDFs, newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch: six 2026 packs, newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf. Local curl got 200 but a brotli-only body it could not decode (see access notes).</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local curl: the group page links the 7 Oct 2026 Group Board full pack (19MB PDF); the 5 Aug 2026 and 1 Apr 2026 group packs also verified, while the old QEH page has nothing after Sep 2025.</t>
+          <t>Re-verified 2026-10-10 by local curl (200): group page links the 7 October 2026 Group Board full pack (/assets/5772c785/group_board_meeting_in_public_07.10.26_-_full_pack_4.pdf) and supplementary documents; next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local curl: 2026 year page lists events 11 Mar, 10 Jun, 9 Sep and 9 Dec 2026; the 9 Sep 2026 event page's Item_00-_Board_held_in_public_-_9_Sept_2026.pdf 302s to media.cuh.nhs.uk.</t>
+          <t>Re-verified 2026-10-10 by local curl: landing links the 2026 year page, which lists event pages for 11 Mar, 10 Jun, 9 Sep and 9 Dec 2026.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Legacy ASP CMS but fully live and current; papers are now published as the BSW Hospitals Group Board. The landing /about/trustboard/index.asp lists forthcoming meetings (to 4 March 2027 as of 2026-10-03) and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp, and the PDFs sit only on those month pages, never on the landing. The old single-file name /documents/Combined_paper_pack.pdf is no longer used (404 for 2026_09). Recent months (2026_07 and 2026_09 confirmed) link two files: documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (the main pack) and documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Reading_Room.pdf. Scrape the PDF hrefs off each month page rather than guessing filenames. All pages render statically and plain browser-UA requests and WebFetch both work, so no Playwright is needed. To find the newest pack, read the landing for the latest YYYY_MM, then harvest that month page's PDF links. Papers carry a press embargo until after the meeting.</t>
+          <t>Legacy ASP CMS but fully live and current; papers are now published as the BSW Hospitals Group Board. The landing /about/trustboard/index.asp lists forthcoming meetings (to 4 March 2027 as of 2026-10-03) and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp, and the PDFs sit only on those month pages, never on the landing. The old single-file name /documents/Combined_paper_pack.pdf is no longer used (404 for 2026_09). Recent months (2026_07 and 2026_09 confirmed) link two files: documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (the main pack) and documents/YYYY_MM_DD_BSW_Hospitals_Group_Board_PUBLIC_Reading_Room.pdf. Scrape the PDF hrefs off each month page rather than guessing filenames. All pages render statically and plain browser-UA requests and WebFetch both work, so no Playwright is needed. To find the newest pack, read the landing for the latest YYYY_MM, then harvest that month page's PDF links. Papers carry a press embargo until after the meeting. 2026-10-10: the landing now also links a group_board/2026_27 folder - RUH papers are published as the 'BSW Hospitals Group Board' combined pack (2026_09_03_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf), so match on 'Group_Board' as well as 'Trust Board'.</t>
         </is>
       </c>
       <c r="J101" t="b">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl: the 2026_09 month page links 2026_09_03_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (200, 27.4MB) plus a Reading_Room PDF; the documented Combined_paper_pack.pdf name now 404s.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl: landing links the 2026_09 month page, whose 'Combined Paper Pack' is 2026_09_03_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (plus a Reading Room PDF); next meeting 5 Nov 2026 and a new group_board/2026_27 folder is linked.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works.</t>
+          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works. Re-verified 2026-10-10: the main-domain landing refused local browser-UA curl with a generic '403 - Forbidden' page (WebFetch fine) while the doclibrary subdomain still served BoardMeetings2627.aspx to plain curl - so when the landing blocks, go straight to the doclibrary year page.</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl: BoardMeetings2627.aspx lists AgendaPacks for 7 May, July, extraordinary July and 3 Sep 2026 (AgendaPackTrustBoardPublic3September26.pdf), plus the 17 Sep 2026 Annual Public Meeting.</t>
+          <t>Re-verified 2026-10-10: WebFetch reached the landing (local browser-UA curl got a generic '403 - Forbidden' page this run) and local curl reached doclibrary BoardMeetings2627.aspx (200), listing Agenda Packs for 7 May, 2 Jul, extraordinary Jul and 3 Sep 2026 plus the 17 Sep 2026 Annual Public Meeting pack.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via server-side WebFetch (archive.org route not needed this run): /media/ meeting packs for 28 Jan, 25 Mar, 27 May, 29 Jul and 30 Sep 2026; 25 Nov 2026 upcoming. Local requests get 403.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (archive.org route not needed this run): /media/ meeting packs for 28 Jan, 25 Mar, 27 May, 29 Jul and 30 Sep 2026 (rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf); 25 Nov 2026 upcoming. Local requests get 403.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: the /publications/ landing is a media browser; follow the 'Board papers' folder (/publications?media_folder=47&amp;root_folder=Board%20papers), then the year folder (2024 = media_folder=49, 2025 = 53, 2026 = 334 - scrape the folder ids, do not hardcode), where each meeting has '&lt;month&gt;-&lt;year&gt;-board-papers.pdf' served from /download/&lt;slug&gt;.pdf?ver=&lt;n&gt; plus a '&lt;month&gt;-&lt;year&gt;-supplementary-board-papers.pdf'. Bi-monthly public board (Jan, Mar, May, Jul, Sep, Nov). Static fetch works (plain curl 200, no WAF). Prefer the main board-papers file; treat supplementary packs as secondary. Pattern B (three hops). Refreshed 2026-10-10: newest pack September 2026.</t>
         </is>
       </c>
       <c r="J113" t="b">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>/download/&lt;month&gt;-&lt;year&gt;-board-papers.pdf;board-papers.pdf;media_folder year folders</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>supplementary-board-papers;Minutes only</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=0.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200): /publications -&gt; 'Board papers' folder (media_folder=47) -&gt; 2026 folder (media_folder=334) lists /download/&lt;month&gt;-2026-board-papers.pdf for Jan, Mar, May, Jul and September 2026 plus supplementary packs.</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 102KB): agenda-and-papers packs for 29 Jan, 18 Mar, 13 May, 18 Jun and 16 Jul 2026; 30 Sep 2026 papers not yet posted, next meeting 19 Nov 2026.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl connection-reset): agenda-and-papers packs for 29 Jan, 18 Mar, 13 May, 18 Jun and 16 Jul 2026; the 30 Sep 2026 meeting is listed but its papers are still not posted; next meeting 19 Nov 2026.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 155KB): 42 /download_file/view/&lt;uuid&gt;/668 'Agenda and papers' links; 2026/27 group lists 2 Apr, 4 Jun and 6 Aug 2026.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 156KB): 43 /download_file/view/&lt;uuid&gt;/668 'Agenda and papers' links; 2026/27 group now lists 2 Apr, 4 Jun, 6 Aug and 8 Oct 2026.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: the 'Our Trust Board' landing carries the current year's meeting dates with a direct combined pack per meeting, served either as /application/files/&lt;ids&gt;/&lt;Date&gt;_-_Trust_Board_Papers.pdf or as a /download_file/&lt;uuid&gt;/9 handler link (June 2026 uses the latter), plus year links for earlier archives. Static fetch works (plain curl 200, no WAF). Prefer the 'Trust Board Papers' / 'Trust Board in Public ... Meeting Papers' pack; skip the Declarations of Interest report and any Part B / confidential items. Pattern A with year archives (B). Refreshed 2026-10-10: newest pack 30 September 2026.</t>
         </is>
       </c>
       <c r="J147" t="b">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>_Trust_Board_Papers.pdf;Trust_Board_in_Public_&lt;date&gt;_-_Meeting_Papers;/application/files/;/download_file/&lt;uuid&gt;/9</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=3, year_archives=3, meeting_subpages=0.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 119KB): dated packs on the landing for 28 Jan, 25 Mar, Jun, Aug and 30 Sep 2026 (Trust_Board_in_Public_30_September_2026_-_Meeting_Papers_v1.pdf).</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 293KB): 77 /download_file/view/{id}/875 links; newest meeting with papers 2 Sep 2026, upcoming dates to 3 Mar 2027.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 293KB): 79 /download_file/view/{id}/875 links; newest meeting with papers 2 Sep 2026, upcoming 4 Nov 2026, 13 Jan and 3 Mar 2027.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 143KB): four /media/board/Papers/2026/ public bundles (Feb, Apr, Jun, Aug 2026).</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 143KB): four /media/board/Papers/2026/ public bundles (Feb, Apr, Jun, Aug 2026); no October bundle yet.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via server-side WebFetch (local curl 403): Meeting-in-Public PDFs for 7 May, 2 Jul and 3 Sep 2026; next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl hit the Cloudflare challenge): Meeting-in-Public PDFs for 5 Mar, 7 May, 2 Jul and 3 Sep 2026; next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 54KB): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack; older packs in the navigate/758/9379 folder (the expected thin landing that trips papers_partial).</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 54KB): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack (the expected thin landing that trips papers_partial).</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via server-side WebFetch (local curl 403): the 'Board papers and publications' accordion lists meeting books for 26 Mar, 21 May and 16 Jul 2026 under /media/; no September 2026 book yet.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl 403): meeting books for 22 Jan, 26 Mar, 21 May and 16 Jul 2026 under /media/; still no September 2026 book.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 75KB): page 1 carries the 3 September 2026 Trust Board pack under /wp-content/uploads/2026/09/.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 75KB): page 1 carries the 3 September 2026 Trust Board pack (Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf, 20MB).</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -14181,7 +14181,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (42 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: the landing lists Trust Board AND Council of Governors meetings interleaved, newest first. Each Trust Board date has an agenda sub-page (/our-trust/trust-board-and-council-governor-meetings/trust-board-meeting-agenda-&lt;d-month-yyyy&gt;) and, once published, a combined 'Trust Board meeting papers' PDF served via /download_file/view/&lt;id&gt;/228 directly from the landing (occasional stand-alone items such as an Audit Committee annual report appear alongside). Static fetch works (plain curl 200, no WAF). Filter to anchors containing 'Trust Board' and skip 'Council of Governors' entries, CEO reports and the Annual Members' Meeting recording. Pattern A/C. Refreshed 2026-10-10: newest papers pack 1 July 2026, 2 September 2026 agenda page present.</t>
         </is>
       </c>
       <c r="J184" t="b">
@@ -14189,17 +14189,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>Trust Board meeting papers;/download_file/view/&lt;id&gt;/228;trust-board-meeting-agenda-&lt;d-month-yyyy&gt;</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Council of Governors;CEO report;Annual Members;Minutes only</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=17, year_archives=1, meeting_subpages=42.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 107KB): Trust Board agenda pages and 'Trust Board meeting papers' /download_file/view/&lt;id&gt;/228 packs for 7 Jan, 4 Mar, 6 May and 1 Jul 2026, plus the 2 September 2026 agenda page; Council of Governors items interleaved.</t>
         </is>
       </c>
       <c r="P184" t="inlineStr"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 102KB): newest packs 01.10.2026 and 03.09.2026 at the top, 2026 packs back to 05.03.2026.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 103KB): newest packs 01.10.2026 and 03.09.2026 at the top, 2026 packs back to 05.03.2026.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 via local headless Playwright (curl and WebFetch 403): /sept26 summary links the 30 Sep 2026 PUBLIC_Agenda_Pack_BoD_30_09_26_v2.pdf.</t>
+          <t>Re-verified 2026-10-10 via local headless Playwright (curl hit the Cloudflare challenge, WebFetch 403): /board lists summaries for 28 Jan, 25 Mar (/mar26), 27 May, 29 Jul and 30 Sep 2026 (/sept26).</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-10-03: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~850-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them. Re-verified 2026-09-12: the POST action=dlp_load_posts admin-ajax recipe still works with no nonce or cookie. This run the ids were dlp_2d9d010977ed5dba_1 (empty), dlp_c5c27bbaddfd4cd9_1 (the archive, 22 dated entries, newest 'Board papers - 3 September 2026') and dlp_ae972c33f72aee98_2. Note the NUMERIC SUFFIX moves too - the archive table was _2 last run and _1 this run - so identify the table by which id returns dated board-paper rows, never by hash and never by suffix position.</t>
+          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them. Re-verified 2026-09-12: the POST action=dlp_load_posts admin-ajax recipe still works with no nonce or cookie. This run the ids were dlp_2d9d010977ed5dba_1 (empty), dlp_c5c27bbaddfd4cd9_1 (the archive, 22 dated entries, newest 'Board papers - 3 September 2026') and dlp_ae972c33f72aee98_2. Note the NUMERIC SUFFIX moves too - the archive table was _2 last run and _1 this run - so identify the table by which id returns dated board-paper rows, never by hash and never by suffix position. 2026-10-10: the table-id suffixes no longer identify the tables (the 26-row archive now sits under a _1 id and the terms-of-reference table under _2), so identify each table by its row content, not its suffix.</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03: the documented admin-ajax dlp_load_posts recipe still returns the archive without nonce or cookie (26 rows, newest 'SCAS public Board papers - 3 September 2026'); next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-10: the admin-ajax dlp_load_posts recipe still returns the archive without nonce or cookie (26 rows, newest 'SCAS public Board papers - 3 September 2026'); current-year table empty between meetings; next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 48KB; the validator's connection reset is the usual intermittent WAF): newest pack /documents/518-board-paper-24-september-2026/file, no later pack yet.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl with --retry (200 after one connection reset): newest pack still /documents/518-board-paper-24-september-2026/file.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 99KB): 'Meeting papers' dropdown lists 16 Sep, 23 Jul, 9 Jul and 14 May 2026; forthcoming meetings 12 Nov 2026 and 21 Jan 2027.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): Meeting papers dropdown lists 16 Sep, 23 Jul and earlier 2026 meetings; forthcoming 12 Nov 2026.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): /board-meetings lists 2026 meetings through Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run, no 403 page): /board-meetings lists Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 266KB; validator's SSL error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/, plus the 28 Jul and 4 Jun 2026 packs.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator SSL error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (63 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: the landing lists each public Board of Directors meeting by date with one link to its papers, served through the CMS download handler /download_file/view/&lt;uuid&gt;/238 (no .pdf suffix, so don't filter on extension). Link text is just the meeting date (e.g. '14th October 2026'), so take the date from the anchor text. Some meetings also link a SoundCloud audio recording, which is not a pack. Static fetch works with a browser User-Agent; the page carries an Incapsula script tag but served full HTML on 2026-10-17. Roughly quarterly meetings.</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>download_file/view/&lt;uuid&gt;/238;anchor text = meeting date</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>soundcloud.com;Council of Governors</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=63, year_archives=0, meeting_subpages=4.</t>
+          <t>2026-10-17 local browser-UA curl (200): dated download_file/view/&lt;uuid&gt;/238 links for 11 Feb, 8 Apr, 8 Jul and 14 Oct 2026; next 8 Dec 2026.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200): the 2026 folder (/navigate/13049/53923) now holds meeting folders 12 Feb, 9 Apr, 11 Jun, 13 Aug and 8 October 2026 (/navigate/13814/53923).</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator SSL error is local): 2026 folder lists meetings to 8 October 2026, next 10 December 2026.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (57 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: LCHS now publishes its papers as the Lincolnshire Community and Hospitals Group (joint with United Lincolnshire Teaching Hospitals), so the pack titles name the group rather than LCHS alone, e.g. 'Lincolnshire Community and Hopsitals Group board papers Sept' (note the site's own misspelling). Packs are direct links on the landing via the CMS handler /download_file/&lt;id&gt;/201 (no .pdf suffix). The page also carries unrelated policy and patient-information links (ICB policies, Doctors of the World) - keep only links whose text mentions board papers or the Annual Public Meeting. Static fetch works with a browser User-Agent despite an Incapsula script tag in the HTML.</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Group board papers;download_file/&lt;id&gt;/201;board papers &lt;Month&gt;</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>policy;Doctors of the World;translated;Annual Public Meeting (not a board pack)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=57, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Lincolnshire Community and Hospitals Group board papers Sept' (download_file/3849/201) plus the 2026 Annual Public Meeting pack.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Wayback is no help here: no Wayback snapshot of the landing was available either.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: no Wayback snapshot of the landing was available either. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Pattern B+F (wrong-url-fixed): old DB url /meetings-and-events/board-meetings only lists future dates ('No upcoming events') and links onward to the real archive at /about-us/publications/Board-of-Directors-papers-minutes, so point the crawler at the archive. The archive is organised by year tabs/sections (2026, 2025, 2024...). Within each year are per-meeting download links served via /download_file/{guid}/{n} (no readable extension) titled e.g. 'Public SWFT and GEH Boards Combined Meeting Pack - 07.10.2025' — take the single largest combined meeting-pack PDF per date. Quirk: South Warwickshire (SWFT) now meets as a JOINT board in common with George Eliot Hospital (GEH); the only public pack is the combined SWFT/GEH pack, so do not filter it out as a Joint board. Download URLs lack a .pdf suffix.</t>
+          <t>Pattern B+F (wrong-url-fixed): old DB url /meetings-and-events/board-meetings only lists future dates ('No upcoming events') and links onward to the real archive at /about-us/publications/Board-of-Directors-papers-minutes, so point the crawler at the archive. The archive is organised by year tabs/sections (2026, 2025, 2024...). Within each year are per-meeting download links served via /download_file/{guid}/{n} (no readable extension) titled e.g. 'Public SWFT and GEH Boards Combined Meeting Pack - 07.10.2025' — take the single largest combined meeting-pack PDF per date. Quirk: South Warwickshire (SWFT) now meets as a JOINT board in common with George Eliot Hospital (GEH); the only public pack is the combined SWFT/GEH pack, so do not filter it out as a Joint board. Download URLs lack a .pdf suffix. Re-verified 2026-10-17: the 7 October 2026 combined SWFT/GEH pack is the newest; the same combined pack is mirrored on GEH (RLT) as download_file/&lt;id&gt;/280.</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Archive page lists a dated 2025 combined board pack (07.10.2025) plus year sections; 2026/27 joint board dates listed with packs to follow.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Public SWFT and GEH Boards Combined Meeting Pack - 07.10.2026' (download_file/&lt;uuid&gt;/797); next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 44KB; validator saw a connection reset): combined public board packs for 2 Apr, 4 Jun, 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl after two connection resets (200 on third attempt): combined public board packs for 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (31 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: George Eliot (GEH) meets as a joint board in common with South Warwickshire (SWFT). The landing is a Concrete CMS document library (sortable, paginated with ccm_paging_p_* query params) listing 'Public Joint Board Combined Meeting Pack DD.MM.YYYY' files and separate numbered minutes, all via /download_file/&lt;id&gt;/280 (no .pdf suffix). Take the 'Combined Meeting Pack' per date and skip the minutes. The default sort is by date added, newest first; page 2 holds older items. Static fetch works. The same combined pack is also published on SWFT's site.</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>Public Joint Board Combined Meeting Pack;download_file/&lt;id&gt;/280</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Public Minutes of Joint Board;video recordings archive</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=26, year_archives=0, meeting_subpages=31.</t>
+          <t>2026-10-17 local browser-UA curl (200): Public Joint Board Combined Meeting Packs for 2 Sep and 7 Oct 2026 (download_file/&lt;id&gt;/280) plus minutes; next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Pattern A/F. Old URL https://www.bwc.nhs.uk/board-of-directors/ is only the board-member directory (validator saw no papers). Changed to the dedicated papers page https://www.bwc.nhs.uk/board-meetings-and-minutes which lists a single combined 'Board Meeting Pack - &lt;Month YYYY&gt;' PDF per meeting (bi-monthly: Jan, Mar, May, Jul, Sep, Nov), served from the trust's own /download/ path with ?ver=&amp;doc= query params. Crawler should take the largest 'Board Meeting Pack' link per month; ignore separate appendix/'Reading Room' files. Static WebFetch reaches the listing and PDFs.</t>
+          <t>Pattern A/F. Old URL https://www.bwc.nhs.uk/board-of-directors/ is only the board-member directory (validator saw no papers). Changed to the dedicated papers page https://www.bwc.nhs.uk/board-meetings-and-minutes which lists a single combined 'Board Meeting Pack - &lt;Month YYYY&gt;' PDF per meeting (bi-monthly: Jan, Mar, May, Jul, Sep, Nov), served from the trust's own /download/ path with ?ver=&amp;doc= query params. Crawler should take the largest 'Board Meeting Pack' link per month; ignore separate appendix/'Reading Room' files. Static WebFetch reaches the listing and PDFs. Re-verified 2026-10-17: packs titled 'Board Meeting Pack - &lt;Month YYYY&gt;' via Jadu-style /download/&lt;slug&gt;.pdf?ver=&lt;n&gt;&amp;doc=docm93jijm4n&lt;id&gt;.pdf, newest September 2026 with a separate 'Public Board Reading Room' PDF; www.bwc.nhs.uk 301s to bwc.nhs.uk.</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Confirmed combined public Board Meeting Pack PDFs for Jan, Mar and May 2026 (plus full 2025 set) on bwc.nhs.uk /download/ paths.</t>
+          <t>2026-10-17 local browser-UA curl: www. 301s to bwc.nhs.uk; 'Board Meeting Pack - July 2026' and '- September 2026' plus a September 2026 Public Board Reading Room.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; September contains 'Board of Directors meeting pack, September 2026.pdf' plus a background-reading pack.</t>
+          <t>Re-verified 2026-10-17 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; no October folder yet.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: year archives. The stored landing 301-redirects to /our-trust/trust-board-meetings-2023/, a year page that links its sibling year pages (/our-trust/trust-board-meetings-2024/, -2025/, -2026/). Go straight to the current year page (/our-trust/trust-board-meetings-&lt;YYYY&gt;/). Each meeting's public papers are split into several parts ('Public Trust Board Papers - October 2026 (Part 1)' to Part 4) served via /~documents/route%3A/download/&lt;id&gt;/ with no .pdf suffix - collect every part for a meeting to get the full pack. Older years used /~documents/documents/&lt;slug&gt;/?layout=default. Static fetch works. Also linked are Foundation Group Board KPI papers, which are part of the pack.</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>Public Trust Board Papers;(Part N);~documents/route%3A/download/</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Minutes only;Confidential</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=1.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 301s to the 2023 year page; /our-trust/trust-board-meetings-2026/ lists Public Trust Board Papers October 2026 Parts 1-4 (~documents/route:/download/4277-4280) plus earlier 2026 meetings.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (18 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: direct PDFs on the landing. Each meeting row reads '&lt;DD Month YYYY&gt; - Trust Board pack' and links a single combined pack via /download/&lt;slug&gt;.pdf?ver=&lt;n&gt;&amp;doc=docm93jijm4n&lt;id&gt;.pdf (Jadu-style download URL - keep the full query string). Bi-monthly public board. The newest meeting's pack can appear a few days after the date; the 15 September 2026 entry was listed without a pack link on 2026-10-17. Static fetch works.</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>Trust Board pack;public-trust-board-paper-pack;docm93jijm4n</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>minutes;Trust.Board@ mailto</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=27, year_archives=0, meeting_subpages=18.</t>
+          <t>2026-10-17 local browser-UA curl (200): '&lt;date&gt; - Trust Board pack' PDFs for 20 Jan, 17 Mar, 19 May and 21 Jul 2026; 15 Sep 2026 listed; next 17 Nov 2026.</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (59 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: the Board of Directors page itself carries the papers - a 'Public Board Meeting Pack &lt;Month YYYY&gt;' link per meeting via /download_file/view/&lt;id&gt;/240 (no .pdf suffix), sometimes duplicated under a bare '&lt;Month YYYY&gt;' label. The same page has the register of interests, director bios and unrelated leaflets (e.g. Choose Well guide under /application/files/), and links to 'blog-board-...' news posts that summarise each meeting - these are not packs. Static fetch works.</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -4467,17 +4467,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Public Board Meeting Pack;download_file/view/&lt;id&gt;/240</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Register of Interests;blog-board;Choose_Well;Annual General Meeting</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Our Board of Directors page live with year-grouped packs, latest July 2026 via /download_file/view/16137/240. The local connection-reset was a WAF false positive.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Public Board Meeting Pack September 2026' (download_file/view/16567/240); next meeting 22 Oct 2026.</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (archive.org route not needed this run): agenda and papers /media/&lt;id&gt;/ links for 28 Jan, 29 Apr and 22 Jul 2026 (papers 7.9MB). Local requests still get the 403 WAF page.</t>
+          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403 WAF page): agenda and papers for the 21 October 2026 meeting now posted (/media/15187 agenda, /media/15188 papers) alongside 28 Jan, 29 Apr and 22 Jul 2026.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 66KB; WebFetch got ECONNRESET): group board PDFs for 8 Jan, 8 May, 9 Jul and 11 Sep 2026 under /wp-content/uploads/.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl with --retry (200): group board PDFs for 9 Jul 2026 and 11 Sep 2026 (/wp-content/uploads/2026/09/11-September-2026-1.pdf).</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Pattern A (dated PDFs on landing) + F (wrong-url-fixed). Old DB url /our-board is just a board overview; the actual papers live at /board-papers-and-agendas. Epsom and St Helier now boards jointly as the 'gesh Group' (with Epsom and St Helier + St George's), so recent packs are titled 'gesh Group Board (public)' with a month/year; this group board is the trust's public board and is the only board pack published here, so it is the correct target. Crawler should take the most recent dated 'gesh Group Board (public)' PDF under /download/. Older years are in year-based archive folders. Static WebFetch reaches it.</t>
+          <t>Pattern A (dated PDFs on landing) + F (wrong-url-fixed). Old DB url /our-board is just a board overview; the actual papers live at /board-papers-and-agendas. Epsom and St Helier now boards jointly as the 'gesh Group' (with Epsom and St Helier + St George's), so recent packs are titled 'gesh Group Board (public)' with a month/year; this group board is the trust's public board and is the only board pack published here, so it is the correct target. Crawler should take the most recent dated 'gesh Group Board (public)' PDF under /download/. Older years are in year-based archive folders. Static WebFetch reaches it. Re-verified 2026-10-17: Epsom and St Helier publishes the GESH Group Board (joint with St George's) - 'gesh Group Board Public &lt;date&gt;.pdf' via /download/...?doc=docm93jijm4n&lt;id&gt;.pdf, newest 11 September 2026; older years sit in ?smbfolder=&lt;id&gt; sub-folders.</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Confirmed dated public group board packs from 1 May 2025 through 8 May 2026 as direct PDF downloads.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'gesh Group Board Public 11 September 2026.pdf' plus 5 Mar, 8 May and 9 Jul 2026.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Live archive at /publications/board-papers-and-committee-tor. Confirmed PDFs 28 May 2026, 30 Apr 2026, 26 Mar 2026 (Trust Board) + Board-in-Common 29 Apr 2026 + 22 Oct 2025.</t>
+          <t>2026-10-17 local browser-UA curl (200): board agenda and papers to 24 Sep 2026 (download_file/view/5196/785 Board in Common pack) with annexes; next 21 Oct and 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Read-only fallback that worked: the Wayback Machine id_ snapshot (https://web.archive.org/web/20260805085630id_/https://www.bradfordhospitals.nhs.uk/our-trust/bod-meetings/, served gzip, so decompress) returned the real page - snapshot 2026-08-05 shows the 23 July 2026 boardbook (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf), dates 24 Sep and 25 Nov 2026, and a previous-meetings-2026 page. It lags the live site, so use it to learn the archive layout and pack URL patterns, then fetch the packs themselves by the normal routes.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-08-05 shows the 23 July 2026 boardbook (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf), dates 24 Sep and 25 Nov 2026, and a previous-meetings-2026 page. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): combined packs 6 May, 1 Jul and 2 Sep 2026 under /wp-content/uploads/2026/; next meeting 4 Nov 2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run, no 403 page): 2 September 2026 Public Board of Directors papers under /wp-content/uploads/2026/09/; next meeting 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; static HTML now holds the 8 September 2026 agenda plus its lettered papers (A-W) alongside Jan-Jul 2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; 2026 page holds the 8 September 2026 lettered papers (113 paper links).</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 104KB): Combined_..._WEBSITE.pdf packs under BoardPapers/2026/ including 9 July and 10 September 2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): Combined_-_Public_Board_of_Directors_-_10_September_2026_WEBSITE.pdf under BoardPapers/2026/.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch: six 2026 packs, newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf. Local curl got 200 but a brotli-only body it could not decode (see access notes).</t>
+          <t>Re-verified 2026-10-17 by local curl with --compressed (200, decoded fine this run): newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6740,12 +6740,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.bdct.nhs.uk/about-us/board-meetings-and-papers/</t>
+          <t>https://www.bdct.nhs.uk/about-us/our-trust/our-board/board-meetings-and-papers/</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (89 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: direct PDFs on the landing (URL updated 2026-10-17 to the 301 target /about-us/our-trust/our-board/board-meetings-and-papers/). One combined pack per meeting under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/ with link text 'Public Board - &lt;D Month YYYY&gt;' (typos such as 'Pubic Board' occur, so match loosely) and version-suffixed filenames (e.g. Public-Board-10-September-2026-v.3.pdf). Upload folder month can precede the meeting month. Static fetch works with a browser User-Agent despite an Incapsula script tag in the HTML.</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -6753,17 +6753,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Public Board;Board held in Public;/wp-content/uploads/</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>minutes;Council of Governors</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=89, year_archives=0, meeting_subpages=1.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 301s to /about-us/our-trust/our-board/board-meetings-and-papers/ (URL updated); 'Public Board' PDFs for 2 Apr, 4 Jun, 23 Jul and 10 Sep 2026; next 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.sheffieldpartnership.nhs.uk/about-us/board-directors/meeting-minutes-and-agendas</t>
+          <t>https://www.sheffieldpartnership.nhs.uk/about-us/board-directors/board-directors-meeting-minutes-and-agendas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Pattern A/F (wrong-url-fixed): the trust rebranded and the old shsc.nhs.uk domain 301-redirects to sheffieldpartnership.nhs.uk. The old DB url pointed at the directors bio page (/about-us/board-directors) which only lists members and meeting dates plus a link 'Agenda papers for meetings can be found here'. The correct landing page is the child /about-us/board-directors/meeting-minutes-and-agendas, where each meeting is listed newest-first with individual links to an 'Agenda' PDF and 'Unconfirmed minutes' PDF stored under /sites/default/files/YYYY-MM/. There are no combined packs — a crawler follows each per-meeting Agenda/minutes PDF link directly. Quirk: filenames are URL-encoded with spaces (e.g. '00 Agenda Public BoD May 2026 .pdf').</t>
+          <t>Pattern A/F (wrong-url-fixed): the trust rebranded and the old shsc.nhs.uk domain 301-redirects to sheffieldpartnership.nhs.uk. The old DB url pointed at the directors bio page (/about-us/board-directors) which only lists members and meeting dates plus a link 'Agenda papers for meetings can be found here'. The correct landing page is the child /about-us/board-directors/meeting-minutes-and-agendas, where each meeting is listed newest-first with individual links to an 'Agenda' PDF and 'Unconfirmed minutes' PDF stored under /sites/default/files/YYYY-MM/. There are no combined packs — a crawler follows each per-meeting Agenda/minutes PDF link directly. Quirk: filenames are URL-encoded with spaces (e.g. '00 Agenda Public BoD May 2026 .pdf'). Re-verified 2026-10-17: the stored URL now 301-redirects to /about-us/board-directors/board-directors-meeting-minutes-and-agendas (URL updated). The page lists itemised papers per meeting under /sites/default/files/&lt;YYYY-MM&gt;/ with numbered filenames (00 Agenda Public BoD Sept 2026 F.pdf, 08 ... Chief executive briefing, 09 ... Patient safety and learning report); there is no single combined pack, so collect the numbered items.</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Confirmed dated agenda/minutes PDFs for the 28 May 2026 public Board of Directors meeting plus March 2026, January 2026 and November 2025 on the meeting-minutes-and-agendas page on the live sheffieldpartnership.nhs.uk domain.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 301s to /board-directors-meeting-minutes-and-agendas (URL updated); September 2026 public BoD papers under /sites/default/files/2026-09/ (00 Agenda Public BoD Sept 2026 F.pdf plus numbered items).</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local curl (200): group page links the 7 October 2026 Group Board full pack (/assets/5772c785/group_board_meeting_in_public_07.10.26_-_full_pack_4.pdf) and supplementary documents; next 2 Dec 2026.</t>
+          <t>Re-verified 2026-10-17 by local curl (200): 7 October 2026 Group Board full pack still the newest (group_board_meeting_in_public_07.10.26_-_full_pack_4.pdf).</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl: landing links the 2026_09 month page, whose 'Combined Paper Pack' is 2026_09_03_BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers.pdf (plus a Reading Room PDF); next meeting 5 Nov 2026 and a new group_board/2026_27 folder is linked.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl: landing links the 2026_09 month page (BSW Hospitals Group Board pack); next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (14 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: Dorset HealthCare meets as a Board in Common (with University Hospitals Dorset), and the trust-board landing links the current year's packs directly: 'Trust Board - Board in Common agenda and papers, &lt;Month YYYY&gt;' via /download_file/view/&lt;uuid&gt;/282 (no .pdf suffix). Older years sit on /about-us/trust-board/trust-board-agendas-and-papers-archive. The first download link on the page is a board structure document, not a pack. Static fetch works.</t>
         </is>
       </c>
       <c r="J102" t="b">
@@ -8133,17 +8133,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Board in Common agenda and papers;download_file/view/&lt;uuid&gt;/282</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>structure and responsibilities of the Board;register of directors interests</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=14, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Trust Board - Board in Common agenda and papers' for June, August and October 2026 via download_file/view/&lt;uuid&gt;/282.</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works. Re-verified 2026-10-10: the main-domain landing refused local browser-UA curl with a generic '403 - Forbidden' page (WebFetch fine) while the doclibrary subdomain still served BoardMeetings2627.aspx to plain curl - so when the landing blocks, go straight to the doclibrary year page.</t>
+          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works. Re-verified 2026-10-10: the main-domain landing refused local browser-UA curl with a generic '403 - Forbidden' page (WebFetch fine) while the doclibrary subdomain still served BoardMeetings2627.aspx to plain curl - so when the landing blocks, go straight to the doclibrary year page. Route check 2026-10-17: the landing loaded by plain browser-UA curl again, but doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/Board/BoardMeetings2627.aspx returned 404 ("The resource cannot be found"), so take the current doclibrary link from the landing page each run rather than hardcoding that path.</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10: WebFetch reached the landing (local browser-UA curl got a generic '403 - Forbidden' page this run) and local curl reached doclibrary BoardMeetings2627.aspx (200), listing Agenda Packs for 7 May, 2 Jul, extraordinary Jul and 3 Sep 2026 plus the 17 Sep 2026 Annual Public Meeting pack.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (landing 200 this run): lists 2026 meetings through 3 and 17 Sep 2026 with next 5 Nov 2026. The doclibrary BoardMeetings2627.aspx path now returns 404 - see access notes.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (archive.org route not needed this run): /media/ meeting packs for 28 Jan, 25 Mar, 27 May, 29 Jul and 30 Sep 2026 (rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf); 25 Nov 2026 upcoming. Local requests get 403.</t>
+          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403): 30 Sep 2026 pack rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf is the newest; archive.org route not needed.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (25 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: the Board and Governors page has anchored sections (#board, #meetings, #papers). The next or most recent meeting's pack is linked as 'View the papers for the next meeting here'; earlier meetings are listed by date ('Thursday 28 May 2026') under #papers. Packs are combined PDFs under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/, with inconsistent filenames (COMBINED-Papers-Trust-PUBLIC-Board-Session-&lt;DDMMYY&gt;.pdf, PUBLIC-Trust-Board-&lt;date&gt;-combined.pdf, GHC-PUBLIC-Trust-Board-...), so key on the link text rather than the filename. Some older years are published as .zip bundles. Static fetch works.</t>
         </is>
       </c>
       <c r="J111" t="b">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>PUBLIC Trust Board;COMBINED-Papers;View the papers for the next meeting</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Council of Governors;governors;.zip (older bundles)</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=25, year_archives=0, meeting_subpages=1.</t>
+          <t>2026-10-17 local browser-UA curl (200): COMBINED-Papers-Trust-PUBLIC-Board-Session-011026.pdf (1 Oct 2026) plus 29 Jan, 26 Mar and 28 May 2026 packs; next 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -9353,35 +9353,35 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Strategy: /about-us/trust-board/trust-board-meetings is correct (archive at /about-us/trust-board/archived-board-papers; also hosts former North Middlesex board papers). Site WAF returns 403/500 to non-browser fetchers. Pattern E anti-bot — use a browser/Playwright; bi-monthly meetings.</t>
+          <t>Strategy: /about-us/trust-board/trust-board-meetings is correct; the current year's packs are listed directly as 'Trust board papers: &lt;D Month YYYY&gt;' via /download_file/&lt;uuid&gt;/794 (no .pdf suffix), and older years are on /about-us/trust-board/archived-board-papers (which also hosts former North Middlesex papers). ACCESS: the site's WAF has returned 403/500 to non-browser fetchers in the past, but on 2026-10-17 a plain browser-UA static fetch got the full HTML, so needs_playwright was dropped to false - try static first and fall back to Playwright only if the 403/500 returns. Bi-monthly meetings.</t>
         </is>
       </c>
       <c r="J119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Board papers;Agenda</t>
+          <t>Trust board papers:;download_file/&lt;uuid&gt;/794</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Council of Governors;North Middlesex (archived)</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned HTTP 403, matching the recorded anti-bot behaviour; the shallow check returned HTTP 200 so the URL stands. Browser/Playwright remains the working route.</t>
+          <t>2026-10-17 local browser-UA curl (200, no WAF): 'Trust board papers: 2 September 2026' plus 4 Feb, 1 Apr and 6 Jun 2026 via download_file/&lt;uuid&gt;/794; next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: Chelsea and Westminster has no separate public board pack - it meets as part of the NW London Acute Provider Collaborative Board in Common (see group_board / group_board_url). The trust URL 302s to /about-us/organisation/board-of-directors, a bios page with no packs; the trust's own /about-us/organisation/trust-meetings page holds only legacy (2022-era) papers. Go to https://www.nwl-acute-provider-group.nhs.uk/publications: each meeting has 'Download the agenda and meeting papers' (/media/&lt;id&gt;/agenda-and-papers-nwl-apg-board-in-common-&lt;month&gt;-&lt;year&gt;-final.pdf) plus a separate reading-room PDF. Quarterly meetings (20 Jan, 28 Apr, 28 Jul and 20 Oct 2026). Static fetch works.</t>
         </is>
       </c>
       <c r="J123" t="b">
@@ -9689,17 +9689,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>agenda-and-papers-nwl-apg-board-in-common;Download the agenda and meeting papers</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>reading-room;register-of-interests;orthopaedic</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=2.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 302s to /about-us/organisation/board-of-directors (bios, no packs); the group board publications page lists the 20 October 2026 Board in Common agenda and papers and reading room.</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (706KB) with dated packs through July 2026; server-side WebFetch returned only the nav shell.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'UCLH Board Papers September 2026' (download_file/&lt;uuid&gt;/680) plus June and July 2026; next 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (34 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: direct packs on the landing - one 'Trust Board Meeting - &lt;Weekday D Month YYYY&gt;' link per meeting via /download_file/view/&lt;id&gt;/208 (no .pdf suffix). Older years are on /about-us/corporate-information/board-meeting-archives. Bi-monthly. Static fetch works.</t>
         </is>
       </c>
       <c r="J127" t="b">
@@ -9999,17 +9999,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Trust Board Meeting -;download_file/view/&lt;id&gt;/208</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>minutes;Council of Governors</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=34, year_archives=0, meeting_subpages=1.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Trust Board Meeting - Thursday &lt;date&gt;' packs for 5 Mar, 7 May, 2 Jul and 3 Sep 2026 via download_file/view/&lt;id&gt;/208; next 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl connection-reset): agenda-and-papers packs for 29 Jan, 18 Mar, 13 May, 18 Jun and 16 Jul 2026; the 30 Sep 2026 meeting is listed but its papers are still not posted; next meeting 19 Nov 2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200 after a reset): papers to July 2026 (10.3MB); the 30 Sep 2026 meeting is still listed without papers; next 19 Nov 2026.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (55 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: direct packs on the landing. Two streams: (a) West London's own 'Trust Board papers Part 1 - &lt;Month YYYY&gt;' (Part 1 is the public session) and (b) 'Board in Common papers - &lt;Month YYYY&gt;' held jointly with CNWL and CLCH. Links go through the CMS handler in two URL shapes, /download_file/view/&lt;id&gt;/656 and /download_file/&lt;id&gt;/0, both without a .pdf suffix. Keep both streams. Static fetch works.</t>
         </is>
       </c>
       <c r="J131" t="b">
@@ -10291,17 +10291,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Trust Board papers Part 1;Board in Common papers;download_file/</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Part 2;Annual General Meeting</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=55, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Trust Board papers Part 1 - September 2026' (download_file/4535/0) plus March and June 2026 and the April 2026 Board in Common papers.</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 156KB): 43 /download_file/view/&lt;uuid&gt;/668 'Agenda and papers' links; 2026/27 group now lists 2 Apr, 4 Jun, 6 Aug and 8 Oct 2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 2026/27 group lists 8 October 2026 - Agenda and papers at the top.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (53 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: direct PDFs on the landing, one per meeting with the date and file size as link text (e.g. '23 September 2026 (27.47MB)'), under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/. Filenames vary (Meeting-Book-Board-of-Directors-public-session, Public-Agenda-Pack, ...), so key on the date in the link text. Extraordinary meetings appear in the same list (one 2026 filename wrongly says 25Jun25). Packs are large (11-28MB). Static fetch works.</t>
         </is>
       </c>
       <c r="J141" t="b">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Meeting Book;Public Agenda Pack;(NN.NNMB)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>minutes;Council of Governors</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=53, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl (200): meeting books for 11 Jun, 25 Jun (extraordinary), 13 Aug and 23 Sep 2026 (2026-09-23-Meeting-Book-Board-of-Directors-public-session-V2.pdf, 27MB).</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Read-only fallback that worked: the Wayback Machine id_ snapshot (https://web.archive.org/web/20260805095545id_/https://www.fhft.nhs.uk/about-us/how-we-are-run/trust-board, served gzip, so decompress) returned the real page - snapshot 2026-08-05 shows meeting dates through 11 Sep and 6 Nov 2026 with /download_file/&lt;uuid&gt;/2265 pack links. It lags the live site, so use it to learn the archive layout and pack URL patterns, then fetch the packs themselves by the normal routes.</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-08-05 shows meeting dates through 11 Sep and 6 Nov 2026 with /download_file/&lt;uuid&gt;/2265 pack links. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 293KB): 79 /download_file/view/{id}/875 links; newest meeting with papers 2 Sep 2026, upcoming 4 Nov 2026, 13 Jan and 3 Mar 2027.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): newest meeting with papers 2 Sep 2026; upcoming 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 143KB): four /media/board/Papers/2026/ public bundles (Feb, Apr, Jun, Aug 2026); no October bundle yet.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): October 2026 public meeting bundle now posted under /media/board/Papers/2026/ (Board of Directors - public meeting bundle - October 2026).</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12644,12 +12644,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://eput.nhs.uk/about-us/board-of-directors/board-meetings/board-papers/</t>
+          <t>https://www.eput.nhs.uk/about/board/board-papers/</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (28 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: direct PDFs on the landing (URL updated 2026-10-17 to the 301 target /about/board/board-papers/). Every meeting row links 'Agenda &amp; Papers' under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/, so the link text gives no date. Take the date from the row text or filename, and note that several months reuse the same filename (Board_of_Directors_Meeting_Part_1.pdf), so the upload folder is the only date signal for those. Part 1 is the public session. Static fetch works.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -12657,17 +12657,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Agenda &amp; Papers;Board of Directors Part 1;/wp-content/uploads/</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Part 2;Council of Governors</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=28, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 301s to www.eput.nhs.uk/about/board/board-papers/ (URL updated); 'Agenda &amp; Papers' PDFs incl. Board-of-Directors-Part-1-Meeting-Papers-07.10.2026.pdf.</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl hit the Cloudflare challenge): Meeting-in-Public PDFs for 5 Mar, 7 May, 2 Jul and 3 Sep 2026; next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl Cloudflare challenge): Meeting-in-Public PDFs to 3 Sep 2026 (0-Meeting-in-Public-03.09.2026-compressed.pdf); next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 54KB): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack (the expected thin landing that trips papers_partial).</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack.</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Board-meetings landing lists dated combined public board packs for May 2026, March 2026 and January 2026 as direct PDFs.</t>
+          <t>2026-10-17 local browser-UA curl (200): Public-board-papers-9-Sept-2026.pdf plus 8 Jul and 13 May 2026 under /wp-content/uploads/2026/; next 11 Nov 2026.</t>
         </is>
       </c>
       <c r="P170" t="inlineStr"/>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local curl 403): meeting books for 22 Jan, 26 Mar, 21 May and 16 Jul 2026 under /media/; still no September 2026 book.</t>
+          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403): meeting books to 16 Jul 2026 under /media/; still no September 2026 book.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (97 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: the 'Our board' page combines director bios with a 'Board meeting papers 2026' section. Each meeting has 'Public Board Main Papers &lt;D Month YYYY&gt;' (the pack to prefer) and often 'Public Board Supporting Papers &lt;date&gt;', via /download/&lt;slug&gt;?ver=&lt;n&gt;&amp;doc=docm93jijm4n&lt;id&gt;.&lt;ext&gt; (Jadu-style). The same page carries the register of interests and AGM agendas/minutes (sometimes .docx), which are not board packs. Papers before 2015 are on request from the Assistant Trust Secretary. Static fetch works.</t>
         </is>
       </c>
       <c r="J172" t="b">
@@ -13279,17 +13279,17 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>Public Board Main Papers;Public Board Supporting Papers;docm93jijm4n</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Register of Interests;AGM;/our-board/&lt;person&gt; bio pages</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=13, year_archives=0, meeting_subpages=97.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Board meeting papers 2026' section with 'Public Board Main Papers 13 October 2026' and 'Public Board Supporting Papers 13 October 2026'; next 8 Dec 2026.</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 75KB): page 1 carries the 3 September 2026 Trust Board pack (Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf, 20MB).</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 3 September 2026 Trust Board pack (Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf) at the top.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01: browser-UA curl returns HTTP 200 and the landing carries dozens of inline /download_file/view/&lt;uuid&gt;/1221 pack links (server-side WebFetch got 403). papers_partial is a false negative from the extension-less download handler.</t>
+          <t>2026-10-17 local browser-UA curl (200): 'Agenda and papers' via download_file/view/&lt;uuid&gt;/1221 for meetings to 7 Oct 2026; next 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 103KB): newest packs 01.10.2026 and 03.09.2026 at the top, 2026 packs back to 05.03.2026.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): newest packs 01.10.2026 and 03.09.2026 via download_file/&lt;uuid&gt;/1439.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via local headless Playwright (curl hit the Cloudflare challenge, WebFetch 403): /board lists summaries for 28 Jan, 25 Mar (/mar26), 27 May, 29 Jul and 30 Sep 2026 (/sept26).</t>
+          <t>Re-verified 2026-10-17 via local headless Playwright (curl hit the Cloudflare challenge): /board lists summaries to 30 Sep 2026 (/sept26).</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Wayback is no help here: the 2026-10-01 snapshot captured the Incapsula shell, so Wayback is not a reliable fallback for this domain.</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: the 2026-10-01 snapshot captured the Incapsula shell, so Wayback is not a reliable fallback for this domain. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~841-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Read-only fallback that worked: the Wayback Machine id_ snapshot (https://web.archive.org/web/20260917192614id_/https://elht.nhs.uk/about-us/our-trust-board/board-meetings-including-agenda-and-papers, served gzip, so decompress) returned the real page - snapshot 2026-09-17 shows the meeting list with 16 Sep, 30 Sep and 11 Nov 2026 and /download_file/&lt;id&gt;/191 pack links. It lags the live site, so use it to learn the archive layout and pack URL patterns, then fetch the packs themselves by the normal routes.</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-10-10: URL resolves (HTTP 200, no redirect) but every route tried this run was refused - local browser-UA curl and local headless Playwright stayed on the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Routing block on this machine's fetch path, not a withdrawal of papers; previously recorded working routes stand and should be tried first.</t>
+          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-09-17 shows the meeting list with 16 Sep, 30 Sep and 11 Nov 2026 and /download_file/&lt;id&gt;/191 pack links. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them. Re-verified 2026-09-12: the POST action=dlp_load_posts admin-ajax recipe still works with no nonce or cookie. This run the ids were dlp_2d9d010977ed5dba_1 (empty), dlp_c5c27bbaddfd4cd9_1 (the archive, 22 dated entries, newest 'Board papers - 3 September 2026') and dlp_ae972c33f72aee98_2. Note the NUMERIC SUFFIX moves too - the archive table was _2 last run and _1 this run - so identify the table by which id returns dated board-paper rows, never by hash and never by suffix position. 2026-10-10: the table-id suffixes no longer identify the tables (the 26-row archive now sits under a _1 id and the terms-of-reference table under _2), so identify each table by its row content, not its suffix.</t>
+          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them. Re-verified 2026-09-12: the POST action=dlp_load_posts admin-ajax recipe still works with no nonce or cookie. This run the ids were dlp_2d9d010977ed5dba_1 (empty), dlp_c5c27bbaddfd4cd9_1 (the archive, 22 dated entries, newest 'Board papers - 3 September 2026') and dlp_ae972c33f72aee98_2. Note the NUMERIC SUFFIX moves too - the archive table was _2 last run and _1 this run - so identify the table by which id returns dated board-paper rows, never by hash and never by suffix position. 2026-10-10: the table-id suffixes no longer identify the tables (the 26-row archive now sits under a _1 id and the terms-of-reference table under _2), so identify each table by its row content, not its suffix. Re-verified 2026-10-17: the ids changed again - this run TWO ids carried the _1 suffix (dlp_2d9d010977ed5dba_1 empty current-year table, dlp_3c751b4101d5e487_1 the 26-row archive) and the terms-of-reference table was dlp_ee178b9cc4a81f32_2, so POST every id found on the page and keep whichever returns dated board-paper rows.</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10: the admin-ajax dlp_load_posts recipe still returns the archive without nonce or cookie (26 rows, newest 'SCAS public Board papers - 3 September 2026'); current-year table empty between meetings; next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-17: admin-ajax dlp_load_posts recipe still works with no nonce or cookie; archive table (26 rows) newest 'SCAS public Board papers - 3 September 2026'; current-year table empty.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl with --retry (200 after one connection reset): newest pack still /documents/518-board-paper-24-september-2026/file.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl with --retry (200; scanner saw a connection reset): newest pack still /documents/518-board-paper-24-september-2026/file; next meeting 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): Meeting papers dropdown lists 16 Sep, 23 Jul and earlier 2026 meetings; forthcoming 12 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): Meeting papers dropdown newest 16 September 2026, then 23 Jul and 9 Jul 2026; forthcoming 12 Nov 2026.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run, no 403 page): /board-meetings lists Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /board-meetings newest Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026 and 2025 year-archive pages each list multiple dated public board meetings with agenda and paper PDFs as static download_file links.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): board-papers/2026 year page holds 107 download_file/view/&lt;id&gt;/2198 links; landing lists next meetings 15 Oct and 10 Dec 2026.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator SSL error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200; validator error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/; next 3 Dec 2026.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Current URL is live and correct; the reported 'broken' status was a transient/WAF block. WebFetch loaded fine. Page is titled 'Meetings in public' under Trust board, lists 2026 public meeting dates and a '2026 agenda papers' section with PDFs hosted at /wp-content/uploads/YYYY/MM/. Older papers under the 'Archive agenda papers' link. Standard WordPress site; retry WebFetch on 403, no JS rendering required.</t>
+          <t>Current URL is live and correct; the reported 'broken' status was a transient/WAF block. WebFetch loaded fine. Page is titled 'Meetings in public' under Trust board, lists 2026 public meeting dates and a '2026 agenda papers' section with PDFs hosted at /wp-content/uploads/YYYY/MM/. Older papers under the 'Archive agenda papers' link. Standard WordPress site; retry WebFetch on 403, no JS rendering required. Re-verified 2026-10-24: plain browser-UA curl also reaches the page (200, 9 dated 2026 PDFs) - the validator's "broken" was a transient local block, not a dead URL. Filenames follow &lt;D-Month-YYYY&gt;--Trust-Board-meeting-in-public.pdf (Feb, Apr, Aug, Sep and 20 Oct 2026 present).</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; newest entry '18 August 2026 - Trust Board meeting in public', papers posted a week ahead of each meeting.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200; validator "broken" was a transient local block): 2026 papers to 20-October-2026--Trust-Board-meeting-in-public.pdf under /wp-content/uploads/2026/10/.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward 2026/27 timetable (12 Feb, 9 Apr, 11 Jun, 13 Aug, 8 Oct, 10 Dec 2026, 11 Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The papers sit three hops down in a Concrete CMS document library: landing -&gt; 'Previous meetings' / '2025' / '2026' year folder (/navigate/{folderId}/53923; 2026 = /navigate/13049/53923) -&gt; one dated folder per meeting (e.g. '13 August 2026' = /navigate/13654/53923) -&gt; numbered per-item papers ('1) Public Board of Directors Agenda - 13 August 2026', '2.1) Chief Executive Report...') served as /download_file/{uuid}/382 links with no .pdf extension. There is no single combined pack, so collect every item in the meeting folder and take titles from the anchor/table text. Past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch and, as of 2026-10-03, also via local curl with a Chrome UA (the page carries an 'incapsula' string but serves normally). The validator's local SSL-verify failure is a local-path artefact, not a dead page. 2026-10-10: the 8 October 2026 meeting folder (/navigate/13814/53923) is now present in the 2026 year folder.</t>
+          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward 2026/27 timetable (12 Feb, 9 Apr, 11 Jun, 13 Aug, 8 Oct, 10 Dec 2026, 11 Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The papers sit three hops down in a Concrete CMS document library: landing -&gt; 'Previous meetings' / '2025' / '2026' year folder (/navigate/{folderId}/53923; 2026 = /navigate/13049/53923) -&gt; one dated folder per meeting (e.g. '13 August 2026' = /navigate/13654/53923) -&gt; numbered per-item papers ('1) Public Board of Directors Agenda - 13 August 2026', '2.1) Chief Executive Report...') served as /download_file/{uuid}/382 links with no .pdf extension. There is no single combined pack, so collect every item in the meeting folder and take titles from the anchor/table text. Past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch and, as of 2026-10-03, also via local curl with a Chrome UA (the page carries an 'incapsula' string but serves normally). The validator's local SSL-verify failure is a local-path artefact, not a dead page. 2026-10-10: the 8 October 2026 meeting folder (/navigate/13814/53923) is now present in the 2026 year folder. Note 2026-10-24: the /navigate/ folder paths are relative to the landing URL (landing + /navigate/13049/53923); the bare-domain form www.lpft.nhs.uk/navigate/13049/53923 returns 404.</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator SSL error is local): 2026 folder lists meetings to 8 October 2026, next 10 December 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 2026 folder lists meeting folders to 8 October 2026; next 10 December 2026.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Pattern A with a major quirk: dated meetings are listed directly on the landing page (Jan/Mar/May 2026; Jan/Mar/May/Jul/Sep/Nov 2025) but the papers are distributed as ZIP archives, not PDFs, via relative /download/...zip?ver=&amp;doc= links that resolve against https://www.hacw.nhs.uk. Each row also has a per-meeting summary sub-page (e.g. /board-may-26) and YouTube recording links. A crawler should grab the ZIP (filenames embed the meeting month, e.g. trust-board-papers-may-2026.zip) and unpack it to reach the individual board-pack documents; there is no plain combined PDF on the site. Static HTML, no JS needed. Future dated meetings (Jul/Sep/Nov 2026) are listed without papers yet.</t>
+          <t>Pattern A with a major quirk: dated meetings are listed directly on the landing page (Jan/Mar/May 2026; Jan/Mar/May/Jul/Sep/Nov 2025) but the papers are distributed as ZIP archives, not PDFs, via relative /download/...zip?ver=&amp;doc= links that resolve against https://www.hacw.nhs.uk. Each row also has a per-meeting summary sub-page (e.g. /board-may-26) and YouTube recording links. A crawler should grab the ZIP (filenames embed the meeting month, e.g. trust-board-papers-may-2026.zip) and unpack it to reach the individual board-pack documents; there is no plain combined PDF on the site. Static HTML, no JS needed. Future dated meetings (Jul/Sep/Nov 2026) are listed without papers yet. Note 2026-10-24: the two newest download.cfm links carry .pdf doc names (docm93jijm4n14609.pdf, ...14615.pdf) rather than .zip, so accept both extensions.</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Landing page lists 2025 and 2026 board meetings each with a downloadable ZIP papers archive (e.g. trust-board-papers-may-2026.zip).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing lists the 17 September 2026 meeting with /download.cfm?doc=...&amp;ver= links; next 19 Nov 2026.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: no Wayback snapshot of the landing was available either. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~844-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2024-04-06, so no useful archive fallback. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl after two connection resets (200 on third attempt): combined public board packs for 6 Aug and 1 Oct 2026 under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest pack Public Trust Board Combined Papers 1 October 2026 v2 under /download/clientfiles/files/.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.mpft.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.mpft.nhs.uk/about-us/board-papers</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Pattern A: dated board-pack PDFs are linked directly on the landing page, grouped by year, as single combined Trust Board Papers documents (2026: 09 Apr, 12 Feb; 2025: 11 Dec, 09 Oct, 14 Aug, 12 Jun, 27 Mar, 30 Jan). The meeting date is in the link text (YYYY-MM-DD MPFT Trust Board Papers) but URLs are opaque /download_file/{uuid}/256 with no date in them. Some months also have a separate short Trust Board Summary Document alongside the full pack; prefer the larger combined Papers file. Static HTML, no JS required.</t>
+          <t>Pattern A: dated board-pack PDFs are linked directly on the landing page, grouped by year, as single combined Trust Board Papers documents (2026: 09 Apr, 12 Feb; 2025: 11 Dec, 09 Oct, 14 Aug, 12 Jun, 27 Mar, 30 Jan). The meeting date is in the link text (YYYY-MM-DD MPFT Trust Board Papers) but URLs are opaque /download_file/{uuid}/256 with no date in them. Some months also have a separate short Trust Board Summary Document alongside the full pack; prefer the larger combined Papers file. Static HTML, no JS required. Update 2026-10-24: the trailing-slash URL now 301-redirects to /about-us/board-papers (URL updated). Packs are /download_file/&lt;uuid&gt;/256 handler links (no .pdf suffix) labelled 'YYYY-MM-DD MPFT Trust Board Papers', each with a separate 'YYYY-MM MPFT Trust Board Summary Document' - prefer the Papers file. Latest 8 October 2026; next 10 Dec 2026. The HTML contains 'incapsula' strings but serves normally to browser-UA curl.</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Landing page directly lists combined Trust Board Papers PDFs for multiple 2025 and 2026 meetings via download_file links.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl and WebFetch: trailing-slash URL 301s to /about-us/board-papers (DB updated); newest '2026-10-08 MPFT Trust Board Papers' via /download_file/&lt;uuid&gt;/256.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; no October folder yet.</t>
+          <t>Re-verified 2026-10-24 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; no October folder yet.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Landing /our-trust/trust-board/public-trust-board-papers/ lists per-year sub-pages (2021-2026), e.g. /public-trust-board-papers-2026/. Each year page lists meetings by month linking to per-meeting sub-pages under /trust-board-paper/{slug}/, and those hold the actual PDFs in /wp-content/uploads/{yyyy}/{mm}/. The trust meets bi-monthly. Static fetch works at every level. Two PDF styles: some meetings publish one combined board book (e.g. May 2026 = 26-05-20_BoardAGENDA_pblc_papers.pdf, ~25MB, prefer this single pack), others publish split numbered papers (000-Agenda, 001-Minutes...). To reach current papers: landing -&gt; 2026 year page -&gt; latest month meeting page -&gt; download the combined boardbook PDF (or all numbered PDFs). Filter out board-meeting-dates, board-members, sub-committees pages.</t>
+          <t>Landing /our-trust/trust-board/public-trust-board-papers/ lists per-year sub-pages (2021-2026), e.g. /public-trust-board-papers-2026/. Each year page lists meetings by month linking to per-meeting sub-pages under /trust-board-paper/{slug}/, and those hold the actual PDFs in /wp-content/uploads/{yyyy}/{mm}/. The trust meets bi-monthly. Static fetch works at every level. Two PDF styles: some meetings publish one combined board book (e.g. May 2026 = 26-05-20_BoardAGENDA_pblc_papers.pdf, ~25MB, prefer this single pack), others publish split numbered papers (000-Agenda, 001-Minutes...). To reach current papers: landing -&gt; 2026 year page -&gt; latest month meeting page -&gt; download the combined boardbook PDF (or all numbered PDFs). Filter out board-meeting-dates, board-members, sub-committees pages. Note 2026-10-24: the September 2026 entry on the 2026 year page links straight to a PDF (/wp-content/uploads/2026/09/26-09-16-Group-Board_Agenda_PAPERSV2.pdf - a Group Board pack) instead of a /trust-board-paper/&lt;slug&gt;/ sub-page, so harvest both forms.</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026 year page resolves to per-meeting pages with live 2026 board-pack PDFs (May 2026 combined agenda confirmed, HTTP 200 application/pdf).</t>
+          <t>Re-verified 2026-10-24 via WebFetch and by local browser-UA curl: 2026 year page lists January, May, July and September 2026; September is a direct Group Board PDF (26-09-16-Group-Board_Agenda_PAPERSV2.pdf).</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403 WAF page): agenda and papers for the 21 October 2026 meeting now posted (/media/15187 agenda, /media/15188 papers) alongside 28 Jan, 29 Apr and 22 Jul 2026.</t>
+          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl got the 403 WAF page): 21 October 2026 agenda (/media/15187) and papers (/media/15188) alongside 22 Jul and 29 Apr 2026.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl with --retry (200): group board PDFs for 9 Jul 2026 and 11 Sep 2026 (/wp-content/uploads/2026/09/11-September-2026-1.pdf).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): group board PDFs to 11 Sep 2026 (/wp-content/uploads/2026/09/11-September-2026-1.pdf).</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 32 dated entries to July 2026, newest /wp-content/uploads/2026/07/KCH-Public-Board-pack-15-July-2026-v2.pdf.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): KCH-Public-Board-pack-16-September-2026-v3.pdf newest under /wp-content/uploads/2026/09/.</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; landing carries year archives 2020-2026 with 'Board papers 2026' current.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): board-papers-2026 page newest 0-260924-tb-part-i-meeting-pack-v10.pdf (24 Sep 2026) under /mediaLocal/.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-08-05 shows the 23 July 2026 boardbook (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf), dates 24 Sep and 25 Nov 2026, and a previous-meetings-2026 page. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~843-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2026-08-05 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Confirmed dated agendas for 25 February 2026 and 25 March 2026 plus 2024/25 archive on the new yorkhospitals.nhs.uk domain.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /seecmsfile/?id= agenda links for meetings to 30 Sep 2026; 28 Oct 2026 listed next.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run, no 403 page): 2 September 2026 Public Board of Directors papers under /wp-content/uploads/2026/09/; next meeting 4 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf newest; next meeting 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Via the WPFD AJAX endpoint each 2025-26 month sub-folder returns one combined board pack and the June 2026 download URL was verified live (HTTP 200, application/pdf, 4.7MB).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing lists 2026 meetings (3 Feb to 8 Sep, next 3 Nov 2026); WPFD file tree is still JS-rendered, so packs were not enumerated statically.</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; 2026 page holds the 8 September 2026 lettered papers (113 paper links).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; 2026 page holds 124 clientfiles paper links through the 8 September 2026 meeting; next 3 Nov 2026.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Pattern B (year archives) + Boards-in-Common. Northern Lincolnshire and Goole runs Trust Boards-in-Common with Hull (HUTH) under the NHS Humber Health Partnership; combined packs are published on the NLG site. Landing lists year cards ("Board papers 2026", "Board papers 2025", ...); click a year card (e.g. https://www.nlg.nhs.uk/resources/board-papers-2026/) to reach a table of one combined PDF per bi-monthly meeting under /wp-content/uploads/. The previous DB URL (/resources/board-papers-archive-2021/) still resolves but is a stale year-specific page; this hub auto-surfaces the current year. Prefer the largest combined "Board papers {Month} {Year}" PDF; these cover both NLG and Hull.</t>
+          <t>Pattern B (year archives) + Boards-in-Common. Northern Lincolnshire and Goole runs Trust Boards-in-Common with Hull (HUTH) under the NHS Humber Health Partnership; combined packs are published on the NLG site. Landing lists year cards ("Board papers 2026", "Board papers 2025", ...); click a year card (e.g. https://www.nlg.nhs.uk/resources/board-papers-2026/) to reach a table of one combined PDF per bi-monthly meeting under /wp-content/uploads/. The previous DB URL (/resources/board-papers-archive-2021/) still resolves but is a stale year-specific page; this hub auto-surfaces the current year. Prefer the largest combined "Board papers {Month} {Year}" PDF; these cover both NLG and Hull. Note 2026-10-24: 2026 packs all sit under /wp-content/uploads/2025/10/ regardless of meeting month (e.g. Board-papers-October-2026-1.pdf, September-2026-board-papers-updated.pdf), so date packs by filename, not upload folder.</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Live NLG Boards-in-Common hub lists 2026 year card with Feb/Mar/Apr/May 2026 combined packs; replaced stale 2021 archive URL.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): board-papers-2026 page newest Board-papers-October-2026-1.pdf.</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): Combined_-_Public_Board_of_Directors_-_10_September_2026_WEBSITE.pdf under BoardPapers/2026/.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200, 104KB): Combined_-_Public_Board_of_Directors_-_10_September_2026_WEBSITE.pdf under BoardPapers/2026/.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Document section lists 2026 board pack sub-pages (May/March/January 2026) each linking the meeting's combined agenda pack, plus matching minutes entries.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing links /documents/board-of-directors-packs-september-2026/ as the newest pack page.</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local curl with --compressed (200, decoded fine this run): newest Public-Trust-Board-agenda-and-papers-29.09.26.pdf.</t>
+          <t>Re-verified 2026-10-24 by local curl with --compressed (200): Public-agenda-and-papers-27.10.26.pdf already posted under /wp-content/uploads/2026/10/ ahead of the 27 Oct 2026 meeting.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local curl (200): 7 October 2026 Group Board full pack still the newest (group_board_meeting_in_public_07.10.26_-_full_pack_4.pdf).</t>
+          <t>Re-verified 2026-10-24 by local curl (200): 7 October 2026 Group Board full pack still the newest; next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Landing page directly lists dated meetings with agenda and item PDFs for 28 Jan, 18 Mar, 1 Apr and 20 May 2026 plus Sep and Nov 2025.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200, 166KB): 30 September 2026 trust board in public agenda (00-2026-09-30-...) and item PDFs under /media/; next 18 Nov 2026.</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
@@ -7960,12 +7960,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.dchft.nhs.uk/about-us/trust-board/trust-board-meetings/</t>
+          <t>https://dchft.nhs.uk/about-us/trust-board/trust-board-meetings/</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Pattern A. From the landing /about-us/trust-board/ a crawler follows the one-click child 'Trust Board Meetings' link to /about-us/trust-board/trust-board-meetings/, which lists each public meeting by date with a direct link to the full Part 1 paper pack PDF hosted under /wp-content/uploads/YYYY/MM/. Dorset County Hospital now meets as part of a Dorset 'Board in Common', so recent packs are named 'Board-in-Common-Part-1-Paper-Pack' alongside older 'Board-of-Directors-part-1-papers' naming; both are the trust's own board papers. The original landing /about-us/trust-board/ shows no papers itself (validator was right) but the dated PDFs live one click down on the meetings sub-page. Only Part 1 (public) packs are published; Part 2 is confidential.</t>
+          <t>Pattern A. From the landing /about-us/trust-board/ a crawler follows the one-click child 'Trust Board Meetings' link to /about-us/trust-board/trust-board-meetings/, which lists each public meeting by date with a direct link to the full Part 1 paper pack PDF hosted under /wp-content/uploads/YYYY/MM/. Dorset County Hospital now meets as part of a Dorset 'Board in Common', so recent packs are named 'Board-in-Common-Part-1-Paper-Pack' alongside older 'Board-of-Directors-part-1-papers' naming; both are the trust's own board papers. The original landing /about-us/trust-board/ shows no papers itself (validator was right) but the dated PDFs live one click down on the meetings sub-page. Only Part 1 (public) packs are published; Part 2 is confidential. Update 2026-10-24: the www.dchft.nhs.uk form now 301-redirects to the bare domain dchft.nhs.uk (URL updated to the redirect target). Packs are now Board-in-Common Part 1 PDFs (e.g. Oct-26-Board-of-Directors-in-Common-Part-1.pdf, Board-in-Common-Part-1-Paper-Pack-17-June-2026.pdf), so match on 'Board-in-Common' / 'in-Common-Part-1' as well as 'Paper Pack'.</t>
         </is>
       </c>
       <c r="J100" t="b">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Trust Board Meetings sub-page lists dated 2025 and 2026 Part 1 board paper pack PDFs (e.g. Feb, Apr, Jun, Aug, Oct, Dec 2025 and Feb, Apr 2026).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl: www. URL 301s to dchft.nhs.uk (DB updated); newest Oct-26-Board-of-Directors-in-Common-Part-1.pdf under /wp-content/uploads/2026/10/.</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl: landing links the 2026_09 month page (BSW Hospitals Group Board pack); next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing links the 2026_09 month page and group_board/2026_27; next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works. Re-verified 2026-10-10: the main-domain landing refused local browser-UA curl with a generic '403 - Forbidden' page (WebFetch fine) while the doclibrary subdomain still served BoardMeetings2627.aspx to plain curl - so when the landing blocks, go straight to the doclibrary year page. Route check 2026-10-17: the landing loaded by plain browser-UA curl again, but doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/Board/BoardMeetings2627.aspx returned 404 ("The resource cannot be found"), so take the current doclibrary link from the landing page each run rather than hardcoding that path.</t>
+          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain. Update 2026-10-03: the landing's 2026/27 link is wrapped in an Outlook safelinks URL (gbr01.safelinks.protection.outlook.com) - unwrap it. The real year page is doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx (the /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/BoardMeetings2627.aspx form 404s); the PDFs themselves remain under .../ChiefExecutive/TrustBoard/Minutes/{2627}/{YYYYMM}/. Local browser-UA curl also works. Re-verified 2026-10-10: the main-domain landing refused local browser-UA curl with a generic '403 - Forbidden' page (WebFetch fine) while the doclibrary subdomain still served BoardMeetings2627.aspx to plain curl - so when the landing blocks, go straight to the doclibrary year page. Route check 2026-10-17: the landing loaded by plain browser-UA curl again, but doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/Board/BoardMeetings2627.aspx returned 404 ("The resource cannot be found"), so take the current doclibrary link from the landing page each run rather than hardcoding that path. Route check 2026-10-24: the safelinks-wrapped link on the landing unwraps to doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx, which returned 200 to plain browser-UA curl - it is only the .../Board/BoardMeetings2627.aspx variant that 404s. Newest pack Minutes/2627/202609/AgendaPackTrustBoardPublic3September26.pdf.</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (landing 200 this run): lists 2026 meetings through 3 and 17 Sep 2026 with next 5 Nov 2026. The doclibrary BoardMeetings2627.aspx path now returns 404 - see access notes.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl: landing 200; the unwrapped doclibrary year page (.../Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx) returned 200 with AgendaPackTrustBoardPublic3September26.pdf the newest pack.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403): 30 Sep 2026 pack rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf is the newest; archive.org route not needed.</t>
+          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl 403 Access Denied): 30 Sep 2026 pack rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf newest; 25 Nov 2026 upcoming.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -9289,13 +9289,39 @@
           <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>London North West University Healthcare does not publish a standalone public trust board pack; it meets in the North West London Acute Provider Group 'Board in Common' (with Chelsea and Westminster, Hillingdon and Imperial), so its board papers are the group's Board-in-Common packs. The DB landing www.nwl-acute-provider-group.nhs.uk/publications is static HTML (plain browser-UA curl works, no Playwright, no WAF seen) and lists the Board-in-Common meeting dates (quarterly: 20 Jan, 28 Apr, 28 Jul and 20 Oct 2026) with a 'Download the agenda and meeting papers' PDF under /media/&lt;8-char-id&gt;/, e.g. /media/l5gle5tg/agenda-and-papers-nwl-apg-board-in-common-october-2026-final.pdf, plus a separate reading-room/appendices PDF. The page only surfaces the CURRENT pack link (older packs drop off), so a crawler must snapshot each run or fall back to the imperial.nhs.uk mirror for past meetings. Take the 'agenda-and-papers' pack; skip appendices/reading-room files, consultation documents and Part 2/confidential items. The old nwl-acute-provider-collaborative.nhs.uk domain now 301-redirects to this page.</t>
+        </is>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>agenda-and-papers;board-in-common;full pack</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>appendices;reading room;Part 2;confidential;consultation</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Verified 2026-10-24 by local browser-UA curl (200): provider-group /publications page carries the 20 October 2026 Board-in-Common pack (/media/l5gle5tg/agenda-and-papers-nwl-apg-board-in-common-october-2026-final.pdf).</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
@@ -9428,12 +9454,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.nwl-acute-provider-collaborative.nhs.uk/publications</t>
+          <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Hillingdon does not publish a standalone trust board; it sits in the North West London Acute Provider Collaborative 'Board in Common' (four acute trusts), so its current board papers are the group's Board-in-Common packs. The provider-group site (nwl-acute-provider-group.nhs.uk) only has a 'meet the board' page with no papers; the actual dated packs live on the NWL Acute Provider Collaborative site under /publications (and its /events meeting pages), as single 'full pack'/'agenda and papers' PDFs at /-/media/website/nwl-acute-provider-collaborative/documents/board-in-common/...-full-pack.pdf or agenda-and-papers--board-in-common-public--DDMMYYYY.pdf. The same PDFs are mirrored on imperial.nhs.uk. Confirmed 2026 public meetings: 20 Jan, 28 Apr, 28 Jul. Note imperial.nhs.uk and the collaborative pages may 403 to bare fetchers; fetch the PDF URLs directly or render. Prefer the public 'full pack' for the latest past meeting; ignore the parallel provider-group domain and 'Part 2/confidential' items.</t>
+          <t>Hillingdon does not publish a standalone trust board; it sits in the North West London Acute Provider Collaborative 'Board in Common' (four acute trusts), so its current board papers are the group's Board-in-Common packs. The provider-group site (nwl-acute-provider-group.nhs.uk) only has a 'meet the board' page with no papers; the actual dated packs live on the NWL Acute Provider Collaborative site under /publications (and its /events meeting pages), as single 'full pack'/'agenda and papers' PDFs at /-/media/website/nwl-acute-provider-collaborative/documents/board-in-common/...-full-pack.pdf or agenda-and-papers--board-in-common-public--DDMMYYYY.pdf. The same PDFs are mirrored on imperial.nhs.uk. Confirmed 2026 public meetings: 20 Jan, 28 Apr, 28 Jul. Note imperial.nhs.uk and the collaborative pages may 403 to bare fetchers; fetch the PDF URLs directly or render. Prefer the public 'full pack' for the latest past meeting; ignore the parallel provider-group domain and 'Part 2/confidential' items. Pattern F 2026-10-24: www.nwl-acute-provider-collaborative.nhs.uk/publications now 301-redirects to www.nwl-acute-provider-group.nhs.uk/publications (URL updated to the redirect target). That provider-group page now DOES carry the Board-in-Common packs (/media/&lt;id&gt;/agenda-and-papers-nwl-apg-board-in-common-&lt;month&gt;-&lt;year&gt;-final.pdf; latest 20 October 2026), so the earlier advice to ignore the provider-group domain is superseded - it is now the live source. Only the current pack is linked; use the imperial.nhs.uk mirror for older meetings.</t>
         </is>
       </c>
       <c r="J120" t="b">
@@ -9451,7 +9477,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9461,7 +9487,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Board-in-Common full-pack PDFs for 20 Jan 2026 and 28 Apr 2026 (covering Hillingdon) are published on the NWL Acute Provider Collaborative site.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl: the old collaborative /publications URL 301s to www.nwl-acute-provider-group.nhs.uk/publications (DB updated), which carries the 20 October 2026 Board-in-Common pack.</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -10089,7 +10115,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10099,7 +10125,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200 after a reset): papers to July 2026 (10.3MB); the 30 Sep 2026 meeting is still listed without papers; next 19 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200 after a reset): papers to 16 July 2026; the 30 Sep 2026 meeting is still listed without papers (fourth week); next 19 Nov 2026.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -10527,7 +10553,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10537,7 +10563,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 2026/27 group lists 8 October 2026 - Agenda and papers at the top.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 2026/27 group lists 8 October 2026 - Agenda and papers at the top.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -10607,7 +10633,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10617,7 +10643,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Static page lists dated combined Agenda+Papers board-pack PDFs for 2025 and 2026; sampled May 2026 link returned a multi-MB PDF.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 17 dated 2026 download_file/view/&lt;id&gt;/268 pack links; next meeting 25 Nov 2026.</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -11345,7 +11371,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11355,7 +11381,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-08-05 shows meeting dates through 11 Sep and 6 Nov 2026 with /download_file/&lt;uuid&gt;/2265 pack links. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~845-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2026-08-05 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11929,7 +11955,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11939,7 +11965,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Year sub-pages list per-meeting document folders for 2025 and 2026; the March 2026 folder contains the numbered agenda and papers PDFs (00-22).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 2026 year page lists document folders January to u-trust-board-papers-september-2026.</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -12143,7 +12169,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12153,7 +12179,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): newest meeting with papers 2 Sep 2026; upcoming 4 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest meeting with papers 2 Sep 2026; upcoming 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12391,7 +12417,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12401,7 +12427,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): October 2026 public meeting bundle now posted under /media/board/Papers/2026/ (Board of Directors - public meeting bundle - October 2026).</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): October 2026 public meeting bundle under /media/board/Papers/2026/; next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12823,7 +12849,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12833,7 +12859,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Landing page links to single combined Meeting Book PDFs for all 2025 meetings and the Feb and May 2026 meetings; the Feb 2026 document slug resolved directly to a multi-page PDF.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): Meeting-Book-Meeting-of-the-Board-of-Directors-in-Public-29-July-2026-compressed.pdf newest; next 4 Nov 2026.</t>
         </is>
       </c>
       <c r="P166" t="inlineStr"/>
@@ -12903,7 +12929,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12913,7 +12939,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl Cloudflare challenge): Meeting-in-Public PDFs to 3 Sep 2026 (0-Meeting-in-Public-03.09.2026-compressed.pdf); next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl got the Cloudflare challenge): 0-Meeting-in-Public-03.09.2026-compressed.pdf newest; next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -13049,7 +13075,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13059,7 +13085,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack.</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13209,7 +13235,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13219,7 +13245,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via server-side WebFetch (local curl 403): meeting books to 16 Jul 2026 under /media/; still no September 2026 book.</t>
+          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl 403): meeting books to 16 Jul 2026 under /media/; still no September 2026 book.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13565,7 +13591,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13575,7 +13601,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 3 September 2026 Trust Board pack (Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf) at the top.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 3 September 2026 Trust Board pack still at the top of page 1.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -14333,7 +14359,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14343,7 +14369,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): newest packs 01.10.2026 and 03.09.2026 via download_file/&lt;uuid&gt;/1439.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest packs 01 10 2026 and 03.09.2026 via download_file/&lt;uuid&gt;/1439.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14501,7 +14527,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14511,7 +14537,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 via local headless Playwright (curl hit the Cloudflare challenge): /board lists summaries to 30 Sep 2026 (/sept26).</t>
+          <t>Re-verified 2026-10-24 via local headless Playwright (curl got the Cloudflare challenge, WebFetch 403): /board lists summaries to 30 Sep 2026 (/sept26).</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14581,7 +14607,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14591,7 +14617,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: the 2026-10-01 snapshot captured the Incapsula shell, so Wayback is not a reliable fallback for this domain. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~842-byte Incapsula shell and server-side WebFetch returned an empty body. Wayback newest snapshot (2026-10-01) is the Incapsula shell. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14715,7 +14741,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14725,7 +14751,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-10-17: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl and local headless Playwright got the ~880-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Wayback: snapshot 2026-09-17 shows the meeting list with 16 Sep, 30 Sep and 11 Nov 2026 and /download_file/&lt;id&gt;/191 pack links. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~847-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot still 2026-09-17 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15146,12 +15172,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.wmas.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.wmas.nhs.uk/about-us/publications/?category=board-papers</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Pattern C: the landing page lists per-meeting publication sub-pages under /publications/, with SEPARATE Agenda and Minutes entries per dated meeting (e.g. 'WMAS Board Meeting Agenda - Wednesday 25th March 2026' and a matching Minutes page). All listings are in static HTML, no JS needed. Quirk: the agenda sub-page renders the agenda as HTML text listing numbered 'Paper 01..nn' items but does NOT publish downloadable PDFs of those papers - it instructs readers to email to request the full board papers. So a crawler can capture the agenda/minutes text but full board-pack PDFs are generally not available for download; prefer the Agenda sub-page for each dated meeting and skip Minutes-only pages when packs are wanted.</t>
+          <t>Pattern C: the landing page lists per-meeting publication sub-pages under /publications/, with SEPARATE Agenda and Minutes entries per dated meeting (e.g. 'WMAS Board Meeting Agenda - Wednesday 25th March 2026' and a matching Minutes page). All listings are in static HTML, no JS needed. Quirk: the agenda sub-page renders the agenda as HTML text listing numbered 'Paper 01..nn' items but does NOT publish downloadable PDFs of those papers - it instructs readers to email to request the full board papers. So a crawler can capture the agenda/minutes text but full board-pack PDFs are generally not available for download; prefer the Agenda sub-page for each dated meeting and skip Minutes-only pages when packs are wanted. Update 2026-10-24: /about-us/board-papers/ now 301-redirects (via /about/publications/) to /about-us/publications/?category=board-papers (URL updated to the final target; paginates with &amp;page_no=N). The newest entry, /publications/board-of-directors-agenda-october-2026/ (28 Oct 2026), carries no downloadable file - it tells readers to request the papers from the Trust Secretary - so a missing pack here is publication practice, not a fetch failure.</t>
         </is>
       </c>
       <c r="J197" t="b">
@@ -15169,7 +15195,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -15179,7 +15205,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Dated 2025 and 2026 agenda and minutes sub-pages are listed and reachable, but agenda pages show paper titles only and direct readers to email for the actual board-pack PDFs.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl and WebFetch: old URL 301s to the publications listing (DB updated); newest entry 'Board of Directors Meeting Agenda - Wednesday 28th October 2026', which offers no download - papers are on request from the Trust Secretary.</t>
         </is>
       </c>
       <c r="P197" t="inlineStr"/>
@@ -15409,7 +15435,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15419,7 +15445,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17: admin-ajax dlp_load_posts recipe still works with no nonce or cookie; archive table (26 rows) newest 'SCAS public Board papers - 3 September 2026'; current-year table empty.</t>
+          <t>Re-verified 2026-10-24: admin-ajax dlp_load_posts recipe still works with no nonce or cookie; ids unchanged from last week (archive table dlp_3c751b4101d5e487_1, 26 rows, newest 'SCAS public Board papers - 3 September 2026'); current-year table empty; next 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl with --retry (200; scanner saw a connection reset): newest pack still /documents/518-board-paper-24-september-2026/file; next meeting 26 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): newest pack /documents/518-board-paper-24-september-2026/file (scanner and validator saw connection resets; first curl attempt also failed); next 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): Meeting papers dropdown newest 16 September 2026, then 23 Jul and 9 Jul 2026; forthcoming 12 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): meeting dates through 23 October 2026 listed on the page; forthcoming 12 Nov 2026.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /board-meetings newest Trust Board 23 September 2026 (/board-meetings/3767-trust-board-23rd-september-2026).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): newest Trust Board 23 September 2026, then 22 Jul and 3 Jun 2026 (scanner saw an HTTP/2 protocol error, a transient local block).</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200; validator error is a local-path artefact): 1 October 2026 pack board-of-directors-meeting-pack-01.10.26.pdf under september2026/; next 3 Dec 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 75 PDF links incl. board-of-directors-meeting-pack-01.10.26.pdf under september2026/; next 3 Dec 2026 (validator SSL error is a local-path artefact).</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 2026 folder lists meeting folders to 8 October 2026; next 10 December 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): forward timetable to 10 Dec 2026 on the landing (8 Oct 2026 meeting folder per last week); validator SSL error is local.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Inline dated PDFs present for the 11 June 2026 Boards in Common meeting (agenda + committee reports); older packs via the 'previous Trust Board meetings' publication-scheme link.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 20 PDFs under /wp-content/uploads/2026/10/ incl. 1-agenda-public-TB-08.10.26.pdf.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026 packs listed for 27 Jan, 24 Mar, 19 May 2026; 2025 sample 'Agenda and papers' = /download_file/view/6958/222 (14 Jan 2025).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026 meetings 27 Jan, 24 Mar, 19 May, 21 Jul, 30 Sep listed with Agenda and papers links; next 24 Nov 2026.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dated month links present under both 2025 and 2026 headings, e.g. 'January 2026 (Performance Report)' and 'August 2025', each a download_file/view PDF.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 'Agendas and Papers 2026' heading lists month links January to October 2026.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~844-byte Incapsula/hCaptcha shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2024-04-06, so no useful archive fallback. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-31: live routes refused again - local browser-UA curl, local headless Playwright and server-side WebFetch all got the ~850-byte Incapsula shell/blank body; no Wayback snapshot of the landing. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026 packs: 'Trust Board Papers – May 2026', 'March 2026', 'January 2026'; 2025 includes 'Trust Board Papers – November 2025' and 'September 2025'.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): group pack RWT_WHT_Group_Board_September_2026_Bundle_v1.pdf (hosted on royalwolverhampton.nhs.uk) plus July and May 2026 packs.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest pack Public Trust Board Combined Papers 1 October 2026 v2 under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl on retry (200; first attempts reset): newest pack Public Trust Board Combined Papers 1 October 2026 v2 under /download/clientfiles/files/.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via the share's WebDAV PROPFIND (207): 2026 holds January, March, June, July and September folders; no October folder yet.</t>
+          <t>Re-verified 2026-10-31 via the share's WebDAV PROPFIND: 2026 holds January, March, June, July and September folders; no October folder yet.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl got the 403 WAF page): 21 October 2026 agenda (/media/15187) and papers (/media/15188) alongside 22 Jul and 29 Apr 2026.</t>
+          <t>Re-verified 2026-10-31 via server-side WebFetch (local curl got the 403 WAF page): papers for 21 Oct, 22 Jul, 29 Apr and 28 Jan 2026 listed.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026: 'Trust Board Meeting, Tuesday 28 April 2026'; 2025: 'Trust Board 30 September 2025' and 'Trust Board 24 June 2025'.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026-10-27-trust-board-part-1-public-pack, 28 Jul and 28 Apr 2026 packs listed.</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): group board PDFs to 11 Sep 2026 (/wp-content/uploads/2026/09/11-September-2026-1.pdf).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): group board PDFs to 11 Sep 2026 (/wp-content/uploads/2026/09/11-September-2026-1.pdf).</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Read-only fallback that worked: the Wayback Machine id_ snapshot (https://web.archive.org/web/20260805085630id_/https://www.bradfordhospitals.nhs.uk/our-trust/bod-meetings/, served gzip, so decompress) returned the real page - snapshot 2026-08-05 shows the 23 July 2026 boardbook (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf), dates 24 Sep and 25 Nov 2026, and a previous-meetings-2026 page. It lags the live site, so use it to learn the archive layout and pack URL patterns, then fetch the packs themselves by the normal routes.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-12: still blocked on every route tried from here - local browser-UA requests returned only the ~845-byte Incapsula/hCaptcha challenge shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'. Route check 2026-09-26: server-side WebFetch returned an empty body again from this session, and the local static path stayed behind the Incapsula shell, so the cheap routes are INTERMITTENT rather than closed - still try WebFetch FIRST (it has reached this domain before and costs nothing) and only then escalate. This is a block on the fetch path from this machine, not evidence the trust has stopped publishing. Route check 2026-10-17: all live routes were blocked again (local curl, local Playwright, WebFetch). Read-only fallback that worked: the Wayback Machine id_ snapshot (https://web.archive.org/web/20260805085630id_/https://www.bradfordhospitals.nhs.uk/our-trust/bod-meetings/, served gzip, so decompress) returned the real page - snapshot 2026-08-05 shows the 23 July 2026 boardbook (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf), dates 24 Sep and 25 Nov 2026, and a previous-meetings-2026 page. It lags the live site, so use it to learn the archive layout and pack URL patterns, then fetch the packs themselves by the normal routes. UPDATE 2026-10-31: local headless Playwright (Chromium, wait_until=domcontentloaded then a few seconds) got through the Incapsula wall and rendered the real landing (85KB, 24 Sep 2026 Public-board-papers-24.9.26.pdf) and the media-enquiries/FOI pages, while curl and WebFetch were still shelled - so try local Playwright before falling back to Wayback.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~843-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2026-08-05 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
+          <t>Re-verified 2026-10-31 via local headless Playwright (domcontentloaded + 8s wait), which passed the Incapsula wall this week while browser-UA curl and server-side WebFetch still got the empty shell: landing links Public-board-papers-24.9.26.pdf under /wp-content/uploads/2026/09/.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf newest; next meeting 4 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf still newest; next meeting 4 Nov 2026 (scanner HTTP/2 error was transient).</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl: landing and /about-us/2026-board-papers/ both 200; 2026 page holds 124 clientfiles paper links through the 8 September 2026 meeting; next 3 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing lists 2026 meetings to 3 Nov 2026 and links /about-us/2026-board-papers/.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026 folder lists 'Public Board Papers - 27 May 2026', '25 March 2026', '28 January 2026'; 2025 folder includes 'Public Board Papers - 28 May 2025'.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): /about/trust-board/public-board-papers/ links 'Board Papers 2026' and 'Public Board Papers - 29 July 2026' PDF.</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NLG board-papers year page lists six 2025 Boards-in-Common combined PDFs (Feb-Dec 2025) plus a 'Board papers 2026' archive, explicitly covering Hull University Teaching Hospitals under the group structure.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): /resources/board-papers-2026/ lists Boards-in-Common packs February to October 2026.</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200, 104KB): Combined_-_Public_Board_of_Directors_-_10_September_2026_WEBSITE.pdf under BoardPapers/2026/.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 126 PDF links incl. Combined_-_Public_Board_of_Directors_*_2026_WEBSITE.pdf under BoardPapers/2026/.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local curl (200): 7 October 2026 Group Board full pack still the newest; next 2 Dec 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 7 October 2026 Group Board full pack plus 2 Nov 2026 agenda (group_board_in_public_agenda_-_02.11.26.pdf).</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -7011,17 +7011,17 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Confirmed year-folder structure on landing with current folders '2025 to 2026 Board meetings papers' and a '2026 to 2027' folder containing 'May 2026 ESNEFT board meeting papers'.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): '2026 to 2027 Board meetings papers' folder holds July and September 2026 ESNEFT board meeting papers sub-pages.</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>The /trust-board/ page only shows meeting dates plus declarations/gifts PDFs and links onward to 'Our Board Papers' at /our-board-papers/, which is the real archive. That archive is a JS 'media browser' widget with year folders (Board Papers 2022-2026); the year/document list and per-document PDF URLs are injected client-side, so a plain static fetch returns the folder shell with no PDF hrefs, it must be rendered (Playwright/headless) to enumerate the dated agenda/minutes/papers PDFs inside each year folder. Open the 2026 (and 2025) folder, then collect the per-meeting PDFs. Prefer the latest meeting's agenda/papers pack. Filter out 2022-2024 folders and the standing declarations/gifts-and-hospitality PDFs.</t>
+          <t>The /trust-board/ page only shows meeting dates plus declarations/gifts PDFs and links onward to 'Our Board Papers' at /our-board-papers/, which is the real archive. That archive is a JS 'media browser' widget with year folders (Board Papers 2022-2026); the year/document list and per-document PDF URLs are injected client-side, so a plain static fetch returns the folder shell with no PDF hrefs, it must be rendered (Playwright/headless) to enumerate the dated agenda/minutes/papers PDFs inside each year folder. Open the 2026 (and 2025) folder, then collect the per-meeting PDFs. Prefer the latest meeting's agenda/papers pack. Filter out 2022-2024 folders and the standing declarations/gifts-and-hospitality PDFs. UPDATE 2026-10-31: each year folder is also reachable by a plain static GET of /our-board-papers?media_folder={id}&amp;root_folder=Board%20Papers%20{year} (2026 = 1449, 2025 = 1218), which returns that folder's dated items without JS.</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Archive is a client-rendered media browser exposing 2025 and 2026 board-paper folders but no PDF hrefs in static HTML.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl: the media-browser folder URL /our-board-papers?media_folder=1449&amp;root_folder=Board%20Papers%202026 renders server-side and lists January, March, May, July and October 2026 items.</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Confirmed dated combined public board packs for 26 September 2025 and 25 July 2025 on the board-and-governors-meetings page, with a noted transition to Norfolk and Waveney Group Board meetings from April 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing now links the Norfolk and Waveney Group Board in public agenda for 2 November 2026 on nw-uhg.org.uk (the group board shared with RM1/RCX); JPUH page keeps Council of Governors packs (21 Jul 2026).</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Direct PDFs visible e.g. 'Public Board Meeting Book - 03.06.2026.pdf' (June 2026) and 'Public Board Meeting Papers 26112025.pdf' (Nov 2025).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 19 PDFs incl. 2026 meeting packs for Board of Directors in Public.</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing links the 2026_09 month page and group_board/2026_27; next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing carries Agenda &amp; Board Papers links and next meeting 5 Nov 2026.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl: landing 200; the unwrapped doclibrary year page (.../Internet/DocumentsLibrary/BoardMeetings/BoardMeetings2627.aspx) returned 200 with AgendaPackTrustBoardPublic3September26.pdf the newest pack.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing lists 2026 meetings to 5 Nov 2026 (scanner HTTP/2 error was transient); packs via the doclibrary year page as per access notes.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl 403 Access Denied): 30 Sep 2026 pack rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf newest; 25 Nov 2026 upcoming.</t>
+          <t>Re-verified 2026-10-31 via local headless Playwright (local curl 403 Access Denied): 30 Sep 2026 pack rduh-board-of-directors-public-20260930-meeting-pack-for-the-website.pdf and 29 Jul 2026 meeting book.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; papers grouped by financial year with 2026-2027 present, navigated via /navigate/{id}/35520 year links.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Trust Board Part 1 entries for January, May, July and September 2026; next 14 Oct 2026 listed.</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Corrected from wrong domain; new page shows 2025-2026 Trust Board Part A main + supplementary packs.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Trust Board Part A packs for March and July 2026 (/download/trust-board-part-a-july-2026pdf.pdf).</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -9565,17 +9565,17 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Inside the folder structure confirmed pack 'Trust Board (Public) Papers 15.01.26 (v2) For Website Reduced Size.pdf' (uploaded 16 Jan 2026); March/May 2026 folders present.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): share-my-box month folders January, May, June, July and November 2026 each hold 1 file (November = 5 Nov 2026 papers); September 2026 folder empty.</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Direct dated links e.g. 'Download the board papers for 21 May 2026' (doc 16288) and 'Download the board papers for 26 November 2025' (doc 16128).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 'Download the board papers for 25 September 2026' and 23 July 2026 links.</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Direct PDFs e.g. May 2026 (/download/may-2026-paperspdf.pdf) and November 2025 (/download/november-2025.pdf).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): public-board-pack-final-22-july-2026 plus January, March and May 2026 packs.</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 2026/27 group lists 8 October 2026 - Agenda and papers at the top.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026/27 group lists 8 October 2026 - Agenda and papers at the top.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Confirmed dated packs e.g. 'Public board papers - January 2026' (/download_file/3812/875) and 'Public board papers - November 2025' (/download_file/3764/875).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 'Public board papers' January, March, May and July 2026 listed; next 26 Nov 2026.</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~845-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot is still 2026-08-05 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-31: live routes refused again - local browser-UA curl and local headless Playwright got the ~845-byte Incapsula shell, server-side WebFetch returned a blank body; newest Wayback snapshot of the trust-board-and-meetings sub-page is 2026-05-08. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>13 in-window meetings via brute-force /board-meetings/{month-year}/ probe. May 2026 and March 2026 packs (15MB + 11MB) both have detectable BAF sections.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing links meeting pages january-2026 to november-2026; /board-meetings/september-2026/ holds Public-Board-of-Directors-30.09.26-meeting-papers-FINAL_compressed.pdf.</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest meeting with papers 2 Sep 2026; upcoming 4 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 80 PDF links; 2026 dates to 4 Nov 2026 listed (newest papers 2 Sep 2026 per last week).</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): October 2026 public meeting bundle under /media/board/Papers/2026/; next 2 Dec 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026 public bundles under /media/board/Papers/2026/ (Feb, Apr, Jun ... Oct 2026); next 2 Dec 2026.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2025 single-trust public packs on the Stockport page and a live June 2026 Joint Public Board Meeting Pack on the partnership site confirmed.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Stockport page packs to 26 March 2026; partnership site southeastsector-hcp.nhs.uk lists Joint Board dates through 3 Dec 2026 with download_file links.</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl got the Cloudflare challenge): 0-Meeting-in-Public-03.09.2026-compressed.pdf newest; next meeting 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 via local headless Playwright (curl got the Cloudflare challenge): 0-Meeting-in-Public-03.09.2026-compressed.pdf newest of 27 PDF links.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing carries the 'September 2026 board papers' download_file/&lt;uuid&gt;/368 pack.</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via server-side WebFetch (local curl 403): meeting books to 16 Jul 2026 under /media/; still no September 2026 book.</t>
+          <t>Re-verified 2026-10-31 via local headless Playwright (curl 403): meeting books to July 2026 under /media/; still no September 2026 book.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 3 September 2026 Trust Board pack still at the top of page 1.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Agenda-Documentation-Trust-Board-Public-3.9.26-Website-Version.pdf still at the top of page 1.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>On the 2025-26 sub-page, confirmed e.g. 'Board of Directors Bundle Part I (Public) - 29 January 2026' and '27 November 2025'.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026-27 folder (/navigate/13810/2001) holds bundles for 2 Jun, 30 Jul and 24 Sep 2026.</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2026-09-05: browser-UA curl returned HTTP 200 (85KB) with the year-tab document library intact - /navigate/4487/{id} tabs and /download_file/view/{id}/423 pack links, dates to September and November 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 2026 tab (/navigate/21268/4487) lists UHLG Board of Directors Public Packs 15 Jan to 17 Sep 2026.</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): newest packs 01 10 2026 and 03.09.2026 via download_file/&lt;uuid&gt;/1439.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): newest packs 'Public Board of Directors Meeting Papers 05 11 2026' and 01 10 2026 via download_file/&lt;uuid&gt;/1439.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 via local headless Playwright (curl got the Cloudflare challenge, WebFetch 403): /board lists summaries to 30 Sep 2026 (/sept26).</t>
+          <t>2026-10-31: all live routes refused this week - curl and local headless Playwright got the Cloudflare "Just a moment" challenge (403) and server-side WebFetch 403; last confirmed 2026-10-24 via local Playwright (summaries to 30 Sep 2026). Newest Wayback snapshot is 2026-03-12. Treat as a transient block; retry Playwright.</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14617,7 +14617,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~842-byte Incapsula shell and server-side WebFetch returned an empty body. Wayback newest snapshot (2026-10-01) is the Incapsula shell. Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-31: live routes refused again - local curl and local headless Playwright got the Incapsula shell, server-side WebFetch blank; the 2026-10-01 Wayback snapshot is also the Incapsula shell. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-10-24: URL resolves (HTTP 200) but live routes were refused again - local browser-UA curl got the ~847-byte Incapsula shell and server-side WebFetch returned an empty body. Newest Wayback snapshot still 2026-09-17 (layout reference only). Routing block on this machine, not a withdrawal of papers.</t>
+          <t>2026-10-31: live routes refused again - local curl and local headless Playwright got the Incapsula shell, server-side WebFetch blank; Wayback id_ snapshot 2026-09-17 shows the real page with meeting dates 16 Sep, 30 Sep and 11 Nov 2026. Routing block on this machine, not a withdrawal of papers.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Confirmed dated meeting links e.g. 'Public Board of Directors Meeting - Wednesday 28 January 2026' and 'Wednesday 1 October 2025', each resolving to its own publications sub-page of PDFs.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Group Board of Directors in Public 2 September 2026, 3 June and 1 April 2026 listed.</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Archive page lists dated board-paper sub-pages through to March/May 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): archive lists January, March, May and July 2026 board-papers sub-pages, plus September 2026 dates.</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Per-meeting sub-pages (e.g. 26 March 2026) host the full set of dated agenda-item PDFs under /media/.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 'Board Meeting 24 September 2026', 23 July and 21 May 2026 per-meeting pages listed.</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Dated 2025-2026 board reports are published as individual HTML report pages (no PDFs) reachable via the minutes-archive index.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Board_Papers_for_the_September_2026_Public_Board_Meeting PDF plus June and April 2026 packs on /assets/.</t>
         </is>
       </c>
       <c r="P198" t="inlineStr"/>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24: admin-ajax dlp_load_posts recipe still works with no nonce or cookie; ids unchanged from last week (archive table dlp_3c751b4101d5e487_1, 26 rows, newest 'SCAS public Board papers - 3 September 2026'); current-year table empty; next 5 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing lists 2026 meetings to 5 Nov 2026; archive via the admin-ajax dlp_load_posts recipe in access notes.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Flat landing page lists 2025-26 dated Board-in-Public agenda packs and a 7 May 2026 pack PDF downloaded successfully (exceeded 10MB fetch limit, confirming a real large PDF).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): Board of Directors in public September 2026, 2 July and 7 May 2026 agenda packs.</t>
         </is>
       </c>
       <c r="P201" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local curl: landing links the 2026 year page, which lists event pages for 11 Mar, 10 Jun, 9 Sep and 9 Dec 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200, 82KB; the shallow scanner saw a transient connection reset): landing links the year pages (deep validator: 6 year archives); 2026 dates incl. 4 September 2026 shown.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
